--- a/Übungen/Netzplan_Übung.xlsx
+++ b/Übungen/Netzplan_Übung.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Übung1" sheetId="1" state="visible" r:id="rId3"/>
@@ -24,12 +24,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="85">
   <si>
     <t xml:space="preserve">ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vorgänger</t>
   </si>
   <si>
     <t xml:space="preserve">Nachfolger</t>
@@ -62,16 +59,19 @@
     <t xml:space="preserve">I</t>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
+    <t xml:space="preserve">J</t>
   </si>
   <si>
-    <t xml:space="preserve">J</t>
+    <t xml:space="preserve"> </t>
   </si>
   <si>
     <t xml:space="preserve">K</t>
   </si>
   <si>
     <t xml:space="preserve">L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kritischer Pfad</t>
   </si>
   <si>
     <t xml:space="preserve">Anfangszeit</t>
@@ -149,25 +149,7 @@
     <t xml:space="preserve">Freier Puffer (FAZ-Nachfolger – FEZ)</t>
   </si>
   <si>
-    <t xml:space="preserve">Milestone 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PT = Aufwand in Personentagen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P =Anzahl eingesetzter Personen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">K = Kapazität</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 Personen</t>
+    <t xml:space="preserve">Vorgänger</t>
   </si>
   <si>
     <t xml:space="preserve">Datum</t>
@@ -303,14 +285,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="@"/>
-    <numFmt numFmtId="166" formatCode="0\ %"/>
-    <numFmt numFmtId="167" formatCode="[$-F800]dddd&quot;, &quot;mmmm\ dd&quot;, &quot;yyyy"/>
-    <numFmt numFmtId="168" formatCode="dd/mm/yy"/>
+    <numFmt numFmtId="166" formatCode="[$-F800]dddd&quot;, &quot;mmmm\ dd&quot;, &quot;yyyy"/>
+    <numFmt numFmtId="167" formatCode="dd/mm/yy"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -342,6 +323,14 @@
     <font>
       <sz val="10"/>
       <color theme="0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
@@ -402,12 +391,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF81D41A"/>
-        <bgColor rgb="FFA9D18E"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4"/>
         <bgColor rgb="FF666699"/>
       </patternFill>
@@ -415,7 +398,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5"/>
-        <bgColor rgb="FFFF8080"/>
+        <bgColor rgb="FFFF8000"/>
       </patternFill>
     </fill>
     <fill>
@@ -460,8 +443,14 @@
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF81D41A"/>
+        <bgColor rgb="FFA9D18E"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="8">
+  <borders count="7">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -480,42 +469,49 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="thin"/>
+      <bottom style="thin">
+        <color rgb="FFFF8000"/>
+      </bottom>
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
       <left/>
-      <right style="thin"/>
-      <top style="thin"/>
+      <right style="thin">
+        <color rgb="FFFF8000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFF8000"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
-      <right/>
-      <top style="thin"/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
-      <right style="thin"/>
+      <left/>
+      <right style="thin">
+        <color rgb="FFFF8000"/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
+      <left/>
       <right/>
-      <top/>
+      <top style="thin">
+        <color rgb="FFFF8000"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
-      <right/>
+      <left/>
+      <right style="thin">
+        <color rgb="FFFF8000"/>
+      </right>
       <top/>
-      <bottom style="thin"/>
+      <bottom style="thin">
+        <color rgb="FFFF8000"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -544,7 +540,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="42">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -561,19 +557,11 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -581,19 +569,31 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -605,8 +605,20 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -618,7 +630,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -629,39 +641,39 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="11" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="11" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -669,51 +681,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="13" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -721,11 +701,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -829,7 +809,7 @@
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF81D41A"/>
       <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFFF8000"/>
       <rgbColor rgb="FFED7D31"/>
       <rgbColor rgb="FF666699"/>
       <rgbColor rgb="FF969696"/>
@@ -1047,11 +1027,9 @@
       <c r="E1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2" t="s">
-        <v>3</v>
-      </c>
+      <c r="F1" s="0"/>
+      <c r="G1" s="0"/>
+      <c r="H1" s="0"/>
       <c r="I1" s="0"/>
       <c r="J1" s="0"/>
       <c r="K1" s="0"/>
@@ -1109,21 +1087,21 @@
     </row>
     <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
+      <c r="C2" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="D2" s="4"/>
-      <c r="E2" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="G2" s="5"/>
-      <c r="H2" s="3" t="n">
+      <c r="E2" s="3" t="n">
         <v>2</v>
       </c>
+      <c r="F2" s="0"/>
+      <c r="G2" s="0"/>
+      <c r="H2" s="0"/>
       <c r="I2" s="0"/>
       <c r="J2" s="0"/>
       <c r="K2" s="0"/>
@@ -1181,21 +1159,19 @@
     </row>
     <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="3" t="n">
+      <c r="B3" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="3" t="n">
         <v>8</v>
       </c>
+      <c r="F3" s="0"/>
+      <c r="G3" s="0"/>
+      <c r="H3" s="0"/>
       <c r="I3" s="0"/>
       <c r="J3" s="0"/>
       <c r="K3" s="0"/>
@@ -1253,23 +1229,21 @@
     </row>
     <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="5" t="s">
+      <c r="C4" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="D4" s="4"/>
+      <c r="E4" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="G4" s="5"/>
-      <c r="H4" s="3" t="n">
-        <v>8</v>
-      </c>
+      <c r="F4" s="0"/>
+      <c r="G4" s="0"/>
+      <c r="H4" s="0"/>
       <c r="I4" s="0"/>
       <c r="J4" s="0"/>
       <c r="K4" s="0"/>
@@ -1327,21 +1301,19 @@
     </row>
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="3" t="n">
         <v>6</v>
       </c>
+      <c r="F5" s="0"/>
+      <c r="G5" s="0"/>
+      <c r="H5" s="0"/>
       <c r="I5" s="0"/>
       <c r="J5" s="0"/>
       <c r="K5" s="0"/>
@@ -1399,21 +1371,19 @@
     </row>
     <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="3" t="n">
+      <c r="B6" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="3" t="n">
         <v>8</v>
       </c>
+      <c r="F6" s="0"/>
+      <c r="G6" s="0"/>
+      <c r="H6" s="0"/>
       <c r="I6" s="0"/>
       <c r="J6" s="0"/>
       <c r="K6" s="0"/>
@@ -1471,21 +1441,19 @@
     </row>
     <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="B7" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="3" t="n">
-        <v>8</v>
-      </c>
+      <c r="F7" s="0"/>
+      <c r="G7" s="0"/>
+      <c r="H7" s="0"/>
       <c r="I7" s="0"/>
       <c r="J7" s="0"/>
       <c r="K7" s="0"/>
@@ -1543,25 +1511,21 @@
     </row>
     <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C8" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D8" s="6"/>
-      <c r="E8" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G8" s="5"/>
-      <c r="H8" s="3" t="n">
+      <c r="D8" s="4"/>
+      <c r="E8" s="3" t="n">
         <v>5</v>
       </c>
+      <c r="F8" s="0"/>
+      <c r="G8" s="0"/>
+      <c r="H8" s="0"/>
       <c r="I8" s="0"/>
       <c r="J8" s="0"/>
       <c r="K8" s="0"/>
@@ -1619,21 +1583,19 @@
     </row>
     <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="3" t="n">
         <v>6</v>
       </c>
+      <c r="F9" s="0"/>
+      <c r="G9" s="0"/>
+      <c r="H9" s="0"/>
       <c r="I9" s="0"/>
       <c r="J9" s="0"/>
       <c r="K9" s="0"/>
@@ -1691,21 +1653,19 @@
     </row>
     <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="3" t="n">
         <v>5</v>
       </c>
+      <c r="F10" s="0"/>
+      <c r="G10" s="0"/>
+      <c r="H10" s="0"/>
       <c r="I10" s="0"/>
       <c r="J10" s="0"/>
       <c r="K10" s="0"/>
@@ -1763,21 +1723,19 @@
     </row>
     <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="3" t="n">
         <v>8</v>
       </c>
+      <c r="F11" s="0"/>
+      <c r="G11" s="0"/>
+      <c r="H11" s="0"/>
       <c r="I11" s="0"/>
       <c r="J11" s="0"/>
       <c r="K11" s="0"/>
@@ -1835,23 +1793,19 @@
     </row>
     <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D12" s="6"/>
-      <c r="E12" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="3" t="n">
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="3" t="n">
         <v>2</v>
       </c>
+      <c r="F12" s="0"/>
+      <c r="G12" s="0"/>
+      <c r="H12" s="0"/>
       <c r="I12" s="0"/>
       <c r="J12" s="0"/>
       <c r="K12" s="0"/>
@@ -1909,21 +1863,17 @@
     </row>
     <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C13" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D13" s="6"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="3" t="n">
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="3" t="n">
         <v>4</v>
       </c>
+      <c r="F13" s="0"/>
+      <c r="G13" s="0"/>
+      <c r="H13" s="0"/>
       <c r="I13" s="0"/>
       <c r="J13" s="0"/>
       <c r="K13" s="0"/>
@@ -2041,34 +1991,58 @@
       <c r="BJ14" s="0"/>
     </row>
     <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="7"/>
-      <c r="B15" s="8"/>
-      <c r="C15" s="9"/>
+      <c r="A15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="B15" s="6"/>
+      <c r="C15" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="D15" s="0"/>
       <c r="E15" s="0"/>
-      <c r="F15" s="0"/>
-      <c r="G15" s="0"/>
-      <c r="H15" s="0"/>
+      <c r="F15" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G15" s="6"/>
+      <c r="H15" s="7" t="n">
+        <v>10</v>
+      </c>
       <c r="I15" s="0"/>
       <c r="J15" s="0"/>
-      <c r="K15" s="0"/>
-      <c r="L15" s="0"/>
-      <c r="M15" s="0"/>
+      <c r="K15" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="L15" s="6"/>
+      <c r="M15" s="7" t="n">
+        <v>16</v>
+      </c>
       <c r="N15" s="0"/>
       <c r="O15" s="0"/>
-      <c r="P15" s="0"/>
-      <c r="Q15" s="0"/>
-      <c r="R15" s="0"/>
+      <c r="P15" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q15" s="6"/>
+      <c r="R15" s="7" t="n">
+        <v>21</v>
+      </c>
       <c r="S15" s="0"/>
       <c r="T15" s="0"/>
-      <c r="U15" s="0"/>
-      <c r="V15" s="0"/>
-      <c r="W15" s="0"/>
+      <c r="U15" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="V15" s="6"/>
+      <c r="W15" s="7" t="n">
+        <v>29</v>
+      </c>
       <c r="X15" s="0"/>
       <c r="Y15" s="0"/>
-      <c r="Z15" s="0"/>
-      <c r="AA15" s="0"/>
-      <c r="AB15" s="0"/>
+      <c r="Z15" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA15" s="6"/>
+      <c r="AB15" s="7" t="n">
+        <v>33</v>
+      </c>
       <c r="AC15" s="0"/>
       <c r="AD15" s="0"/>
       <c r="AE15" s="0"/>
@@ -2105,45 +2079,57 @@
       <c r="BJ15" s="0"/>
     </row>
     <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="10" t="s">
+      <c r="A16" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="9"/>
+      <c r="F16" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="B16" s="10"/>
-      <c r="C16" s="10"/>
-      <c r="D16" s="0"/>
-      <c r="E16" s="0"/>
-      <c r="F16" s="0"/>
-      <c r="G16" s="0"/>
-      <c r="H16" s="0"/>
-      <c r="I16" s="0"/>
-      <c r="J16" s="0"/>
-      <c r="K16" s="0"/>
-      <c r="L16" s="0"/>
-      <c r="M16" s="0"/>
-      <c r="N16" s="0"/>
-      <c r="O16" s="0"/>
-      <c r="P16" s="0"/>
-      <c r="Q16" s="0"/>
-      <c r="R16" s="0"/>
-      <c r="S16" s="0"/>
-      <c r="T16" s="0"/>
-      <c r="U16" s="0"/>
-      <c r="V16" s="0"/>
-      <c r="W16" s="0"/>
-      <c r="X16" s="0"/>
-      <c r="Y16" s="0"/>
-      <c r="Z16" s="0"/>
-      <c r="AA16" s="0"/>
-      <c r="AB16" s="0"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="9"/>
+      <c r="J16" s="9"/>
+      <c r="K16" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="L16" s="8"/>
+      <c r="M16" s="8"/>
+      <c r="N16" s="9"/>
+      <c r="O16" s="9"/>
+      <c r="P16" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q16" s="8"/>
+      <c r="R16" s="8"/>
+      <c r="S16" s="9"/>
+      <c r="T16" s="9"/>
+      <c r="U16" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="V16" s="8"/>
+      <c r="W16" s="8"/>
+      <c r="X16" s="9"/>
+      <c r="Y16" s="9"/>
+      <c r="Z16" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="AA16" s="8"/>
+      <c r="AB16" s="8"/>
       <c r="AC16" s="0"/>
-      <c r="AD16" s="0"/>
-      <c r="AE16" s="0"/>
-      <c r="AF16" s="0"/>
-      <c r="AG16" s="0"/>
-      <c r="AH16" s="0"/>
-      <c r="AI16" s="0"/>
-      <c r="AJ16" s="0"/>
-      <c r="AK16" s="0"/>
+      <c r="AD16" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="AE16" s="10"/>
+      <c r="AF16" s="10"/>
+      <c r="AG16" s="10"/>
+      <c r="AH16" s="10"/>
+      <c r="AI16" s="10"/>
+      <c r="AJ16" s="10"/>
+      <c r="AK16" s="10"/>
       <c r="AL16" s="0"/>
       <c r="AM16" s="0"/>
       <c r="AN16" s="0"/>
@@ -2172,36 +2158,69 @@
     </row>
     <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="n">
-        <f aca="false">VLOOKUP(A16,$A$2:$H$13,8)</f>
         <v>2</v>
       </c>
-      <c r="B17" s="12"/>
-      <c r="C17" s="13"/>
+      <c r="B17" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="13" t="n">
+        <v>0</v>
+      </c>
       <c r="D17" s="0"/>
       <c r="E17" s="0"/>
-      <c r="F17" s="0"/>
-      <c r="G17" s="0"/>
-      <c r="H17" s="0"/>
+      <c r="F17" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="G17" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="13" t="n">
+        <v>0</v>
+      </c>
       <c r="I17" s="0"/>
       <c r="J17" s="0"/>
-      <c r="K17" s="0"/>
-      <c r="L17" s="0"/>
-      <c r="M17" s="0"/>
+      <c r="K17" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="L17" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="13" t="n">
+        <v>0</v>
+      </c>
       <c r="N17" s="0"/>
       <c r="O17" s="0"/>
-      <c r="P17" s="0"/>
-      <c r="Q17" s="0"/>
-      <c r="R17" s="0"/>
+      <c r="P17" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q17" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" s="13" t="n">
+        <v>0</v>
+      </c>
       <c r="S17" s="0"/>
       <c r="T17" s="0"/>
-      <c r="U17" s="0"/>
-      <c r="V17" s="0"/>
-      <c r="W17" s="0"/>
+      <c r="U17" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="V17" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" s="13" t="n">
+        <v>0</v>
+      </c>
       <c r="X17" s="0"/>
       <c r="Y17" s="0"/>
-      <c r="Z17" s="0"/>
-      <c r="AA17" s="0"/>
-      <c r="AB17" s="0"/>
+      <c r="Z17" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA17" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" s="13" t="n">
+        <v>0</v>
+      </c>
       <c r="AC17" s="0"/>
       <c r="AD17" s="0"/>
       <c r="AE17" s="0"/>
@@ -2238,34 +2257,58 @@
       <c r="BJ17" s="0"/>
     </row>
     <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="14"/>
-      <c r="B18" s="8"/>
-      <c r="C18" s="15"/>
-      <c r="D18" s="0"/>
+      <c r="A18" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="B18" s="6"/>
+      <c r="C18" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" s="16"/>
       <c r="E18" s="0"/>
-      <c r="F18" s="0"/>
-      <c r="G18" s="0"/>
-      <c r="H18" s="0"/>
+      <c r="F18" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G18" s="6"/>
+      <c r="H18" s="15" t="n">
+        <v>10</v>
+      </c>
       <c r="I18" s="0"/>
       <c r="J18" s="0"/>
-      <c r="K18" s="0"/>
-      <c r="L18" s="0"/>
-      <c r="M18" s="0"/>
+      <c r="K18" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="L18" s="6"/>
+      <c r="M18" s="15" t="n">
+        <v>16</v>
+      </c>
       <c r="N18" s="0"/>
       <c r="O18" s="0"/>
-      <c r="P18" s="0"/>
-      <c r="Q18" s="0"/>
-      <c r="R18" s="0"/>
+      <c r="P18" s="14" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q18" s="6"/>
+      <c r="R18" s="15" t="n">
+        <v>21</v>
+      </c>
       <c r="S18" s="0"/>
       <c r="T18" s="0"/>
-      <c r="U18" s="0"/>
-      <c r="V18" s="0"/>
-      <c r="W18" s="0"/>
-      <c r="X18" s="0"/>
-      <c r="Y18" s="0"/>
-      <c r="Z18" s="0"/>
-      <c r="AA18" s="0"/>
-      <c r="AB18" s="0"/>
+      <c r="U18" s="14" t="n">
+        <v>21</v>
+      </c>
+      <c r="V18" s="6"/>
+      <c r="W18" s="15" t="n">
+        <v>29</v>
+      </c>
+      <c r="X18" s="17"/>
+      <c r="Y18" s="18"/>
+      <c r="Z18" s="14" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA18" s="6"/>
+      <c r="AB18" s="15" t="n">
+        <v>33</v>
+      </c>
       <c r="AC18" s="0"/>
       <c r="AD18" s="0"/>
       <c r="AE18" s="0"/>
@@ -2302,7 +2345,7 @@
       <c r="BJ18" s="0"/>
     </row>
     <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D19" s="0"/>
+      <c r="D19" s="17"/>
       <c r="E19" s="0"/>
       <c r="F19" s="0"/>
       <c r="G19" s="0"/>
@@ -2322,7 +2365,7 @@
       <c r="U19" s="0"/>
       <c r="V19" s="0"/>
       <c r="W19" s="0"/>
-      <c r="X19" s="0"/>
+      <c r="X19" s="17"/>
       <c r="Y19" s="0"/>
       <c r="Z19" s="0"/>
       <c r="AA19" s="0"/>
@@ -2363,7 +2406,7 @@
       <c r="BJ19" s="0"/>
     </row>
     <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D20" s="0"/>
+      <c r="D20" s="17"/>
       <c r="E20" s="0"/>
       <c r="F20" s="0"/>
       <c r="G20" s="0"/>
@@ -2383,7 +2426,7 @@
       <c r="U20" s="0"/>
       <c r="V20" s="0"/>
       <c r="W20" s="0"/>
-      <c r="X20" s="0"/>
+      <c r="X20" s="17"/>
       <c r="Y20" s="0"/>
       <c r="Z20" s="0"/>
       <c r="AA20" s="0"/>
@@ -2424,27 +2467,43 @@
       <c r="BJ20" s="0"/>
     </row>
     <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D21" s="0"/>
+      <c r="D21" s="17"/>
       <c r="E21" s="0"/>
-      <c r="F21" s="0"/>
-      <c r="G21" s="0"/>
-      <c r="H21" s="0"/>
+      <c r="F21" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G21" s="6"/>
+      <c r="H21" s="7" t="n">
+        <v>10</v>
+      </c>
       <c r="I21" s="0"/>
       <c r="J21" s="0"/>
-      <c r="K21" s="0"/>
-      <c r="L21" s="0"/>
-      <c r="M21" s="0"/>
+      <c r="K21" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="L21" s="6"/>
+      <c r="M21" s="7" t="n">
+        <v>18</v>
+      </c>
       <c r="N21" s="0"/>
       <c r="O21" s="0"/>
-      <c r="P21" s="0"/>
-      <c r="Q21" s="0"/>
-      <c r="R21" s="0"/>
+      <c r="P21" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q21" s="6"/>
+      <c r="R21" s="7" t="n">
+        <v>24</v>
+      </c>
       <c r="S21" s="0"/>
       <c r="T21" s="0"/>
-      <c r="U21" s="0"/>
-      <c r="V21" s="0"/>
-      <c r="W21" s="0"/>
-      <c r="X21" s="0"/>
+      <c r="U21" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="V21" s="6"/>
+      <c r="W21" s="7" t="n">
+        <v>26</v>
+      </c>
+      <c r="X21" s="17"/>
       <c r="Y21" s="0"/>
       <c r="Z21" s="0"/>
       <c r="AA21" s="0"/>
@@ -2485,27 +2544,35 @@
       <c r="BJ21" s="0"/>
     </row>
     <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D22" s="0"/>
-      <c r="E22" s="0"/>
-      <c r="F22" s="0"/>
-      <c r="G22" s="0"/>
-      <c r="H22" s="0"/>
-      <c r="I22" s="0"/>
-      <c r="J22" s="0"/>
-      <c r="K22" s="0"/>
-      <c r="L22" s="0"/>
-      <c r="M22" s="0"/>
-      <c r="N22" s="0"/>
-      <c r="O22" s="0"/>
-      <c r="P22" s="0"/>
-      <c r="Q22" s="0"/>
-      <c r="R22" s="0"/>
-      <c r="S22" s="0"/>
-      <c r="T22" s="0"/>
-      <c r="U22" s="0"/>
-      <c r="V22" s="0"/>
-      <c r="W22" s="0"/>
-      <c r="X22" s="0"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="9"/>
+      <c r="F22" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="G22" s="8"/>
+      <c r="H22" s="8"/>
+      <c r="I22" s="9"/>
+      <c r="J22" s="9"/>
+      <c r="K22" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="L22" s="8"/>
+      <c r="M22" s="8"/>
+      <c r="N22" s="9"/>
+      <c r="O22" s="9"/>
+      <c r="P22" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q22" s="8"/>
+      <c r="R22" s="8"/>
+      <c r="S22" s="9"/>
+      <c r="T22" s="9"/>
+      <c r="U22" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="V22" s="8"/>
+      <c r="W22" s="8"/>
+      <c r="X22" s="19"/>
       <c r="Y22" s="0"/>
       <c r="Z22" s="0"/>
       <c r="AA22" s="0"/>
@@ -2548,24 +2615,48 @@
     <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D23" s="0"/>
       <c r="E23" s="0"/>
-      <c r="F23" s="0"/>
-      <c r="G23" s="0"/>
-      <c r="H23" s="0"/>
+      <c r="F23" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="G23" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="H23" s="13" t="n">
+        <v>0</v>
+      </c>
       <c r="I23" s="0"/>
       <c r="J23" s="0"/>
-      <c r="K23" s="0"/>
-      <c r="L23" s="0"/>
-      <c r="M23" s="0"/>
+      <c r="K23" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="L23" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="M23" s="13" t="n">
+        <v>0</v>
+      </c>
       <c r="N23" s="0"/>
       <c r="O23" s="0"/>
-      <c r="P23" s="0"/>
-      <c r="Q23" s="0"/>
-      <c r="R23" s="0"/>
+      <c r="P23" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q23" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="R23" s="13" t="n">
+        <v>0</v>
+      </c>
       <c r="S23" s="0"/>
       <c r="T23" s="0"/>
-      <c r="U23" s="0"/>
-      <c r="V23" s="0"/>
-      <c r="W23" s="0"/>
+      <c r="U23" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="V23" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="W23" s="13" t="n">
+        <v>3</v>
+      </c>
       <c r="X23" s="0"/>
       <c r="Y23" s="0"/>
       <c r="Z23" s="0"/>
@@ -2609,24 +2700,40 @@
     <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D24" s="0"/>
       <c r="E24" s="0"/>
-      <c r="F24" s="0"/>
-      <c r="G24" s="0"/>
-      <c r="H24" s="0"/>
-      <c r="I24" s="0"/>
+      <c r="F24" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="G24" s="6"/>
+      <c r="H24" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="I24" s="16"/>
       <c r="J24" s="0"/>
-      <c r="K24" s="0"/>
-      <c r="L24" s="0"/>
-      <c r="M24" s="0"/>
+      <c r="K24" s="14" t="n">
+        <v>13</v>
+      </c>
+      <c r="L24" s="6"/>
+      <c r="M24" s="15" t="n">
+        <v>21</v>
+      </c>
       <c r="N24" s="0"/>
       <c r="O24" s="0"/>
-      <c r="P24" s="0"/>
-      <c r="Q24" s="0"/>
-      <c r="R24" s="0"/>
-      <c r="S24" s="0"/>
-      <c r="T24" s="0"/>
-      <c r="U24" s="0"/>
-      <c r="V24" s="0"/>
-      <c r="W24" s="0"/>
+      <c r="P24" s="14" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q24" s="6"/>
+      <c r="R24" s="15" t="n">
+        <v>27</v>
+      </c>
+      <c r="S24" s="17"/>
+      <c r="T24" s="18"/>
+      <c r="U24" s="14" t="n">
+        <v>27</v>
+      </c>
+      <c r="V24" s="6"/>
+      <c r="W24" s="15" t="n">
+        <v>29</v>
+      </c>
       <c r="X24" s="0"/>
       <c r="Y24" s="0"/>
       <c r="Z24" s="0"/>
@@ -2673,7 +2780,7 @@
       <c r="F25" s="0"/>
       <c r="G25" s="0"/>
       <c r="H25" s="0"/>
-      <c r="I25" s="0"/>
+      <c r="I25" s="17"/>
       <c r="J25" s="0"/>
       <c r="K25" s="0"/>
       <c r="L25" s="0"/>
@@ -2683,7 +2790,7 @@
       <c r="P25" s="0"/>
       <c r="Q25" s="0"/>
       <c r="R25" s="0"/>
-      <c r="S25" s="0"/>
+      <c r="S25" s="17"/>
       <c r="T25" s="0"/>
       <c r="U25" s="0"/>
       <c r="V25" s="0"/>
@@ -2734,7 +2841,7 @@
       <c r="F26" s="0"/>
       <c r="G26" s="0"/>
       <c r="H26" s="0"/>
-      <c r="I26" s="0"/>
+      <c r="I26" s="17"/>
       <c r="J26" s="0"/>
       <c r="K26" s="0"/>
       <c r="L26" s="0"/>
@@ -2744,7 +2851,7 @@
       <c r="P26" s="0"/>
       <c r="Q26" s="0"/>
       <c r="R26" s="0"/>
-      <c r="S26" s="0"/>
+      <c r="S26" s="17"/>
       <c r="T26" s="0"/>
       <c r="U26" s="0"/>
       <c r="V26" s="0"/>
@@ -2790,17 +2897,25 @@
       <c r="BJ26" s="0"/>
     </row>
     <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I27" s="0"/>
+      <c r="I27" s="17"/>
       <c r="J27" s="0"/>
-      <c r="K27" s="0"/>
-      <c r="L27" s="0"/>
-      <c r="M27" s="0"/>
+      <c r="K27" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="L27" s="6"/>
+      <c r="M27" s="7" t="n">
+        <v>18</v>
+      </c>
       <c r="N27" s="0"/>
       <c r="O27" s="0"/>
-      <c r="P27" s="0"/>
-      <c r="Q27" s="0"/>
-      <c r="R27" s="0"/>
-      <c r="S27" s="0"/>
+      <c r="P27" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q27" s="6"/>
+      <c r="R27" s="7" t="n">
+        <v>23</v>
+      </c>
+      <c r="S27" s="17"/>
       <c r="T27" s="0"/>
       <c r="U27" s="0"/>
       <c r="V27" s="0"/>
@@ -2846,17 +2961,21 @@
       <c r="BJ27" s="0"/>
     </row>
     <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I28" s="0"/>
-      <c r="J28" s="0"/>
-      <c r="K28" s="0"/>
-      <c r="L28" s="0"/>
-      <c r="M28" s="0"/>
-      <c r="N28" s="0"/>
-      <c r="O28" s="0"/>
-      <c r="P28" s="0"/>
-      <c r="Q28" s="0"/>
-      <c r="R28" s="0"/>
-      <c r="S28" s="0"/>
+      <c r="I28" s="17"/>
+      <c r="J28" s="9"/>
+      <c r="K28" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="L28" s="8"/>
+      <c r="M28" s="8"/>
+      <c r="N28" s="9"/>
+      <c r="O28" s="9"/>
+      <c r="P28" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q28" s="8"/>
+      <c r="R28" s="8"/>
+      <c r="S28" s="19"/>
       <c r="T28" s="0"/>
       <c r="U28" s="0"/>
       <c r="V28" s="0"/>
@@ -2904,14 +3023,26 @@
     <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I29" s="0"/>
       <c r="J29" s="0"/>
-      <c r="K29" s="0"/>
-      <c r="L29" s="0"/>
-      <c r="M29" s="0"/>
+      <c r="K29" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="L29" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="M29" s="13" t="n">
+        <v>0</v>
+      </c>
       <c r="N29" s="0"/>
       <c r="O29" s="0"/>
-      <c r="P29" s="0"/>
-      <c r="Q29" s="0"/>
-      <c r="R29" s="0"/>
+      <c r="P29" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q29" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="R29" s="13" t="n">
+        <v>1</v>
+      </c>
       <c r="S29" s="0"/>
       <c r="T29" s="0"/>
       <c r="U29" s="0"/>
@@ -2960,14 +3091,22 @@
     <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I30" s="0"/>
       <c r="J30" s="0"/>
-      <c r="K30" s="0"/>
-      <c r="L30" s="0"/>
-      <c r="M30" s="0"/>
+      <c r="K30" s="14" t="n">
+        <v>14</v>
+      </c>
+      <c r="L30" s="6"/>
+      <c r="M30" s="15" t="n">
+        <v>22</v>
+      </c>
       <c r="N30" s="0"/>
       <c r="O30" s="0"/>
-      <c r="P30" s="0"/>
-      <c r="Q30" s="0"/>
-      <c r="R30" s="0"/>
+      <c r="P30" s="14" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q30" s="6"/>
+      <c r="R30" s="15" t="n">
+        <v>27</v>
+      </c>
       <c r="S30" s="0"/>
       <c r="T30" s="0"/>
       <c r="U30" s="0"/>
@@ -3126,57 +3265,60 @@
       <c r="BJ32" s="0"/>
     </row>
     <row r="35" customFormat="false" ht="52.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="16" t="s">
+      <c r="A35" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="C35" s="17" t="s">
+      <c r="C35" s="21" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="7" t="s">
+      <c r="A36" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B36" s="8"/>
-      <c r="C36" s="9" t="s">
+      <c r="B36" s="6"/>
+      <c r="C36" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D36" s="18" t="s">
+      <c r="D36" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="H36" s="19" t="s">
+      <c r="E36" s="22"/>
+      <c r="F36" s="22"/>
+      <c r="G36" s="22"/>
+      <c r="H36" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="I36" s="19"/>
-      <c r="J36" s="19"/>
-      <c r="K36" s="19"/>
-      <c r="L36" s="19"/>
-      <c r="M36" s="19"/>
-      <c r="N36" s="19"/>
-      <c r="O36" s="19"/>
-      <c r="P36" s="19"/>
+      <c r="I36" s="23"/>
+      <c r="J36" s="23"/>
+      <c r="K36" s="23"/>
+      <c r="L36" s="23"/>
+      <c r="M36" s="23"/>
+      <c r="N36" s="23"/>
+      <c r="O36" s="23"/>
+      <c r="P36" s="23"/>
     </row>
     <row r="37" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="10" t="s">
+      <c r="A37" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B37" s="10"/>
-      <c r="C37" s="10"/>
-      <c r="H37" s="19" t="s">
+      <c r="B37" s="8"/>
+      <c r="C37" s="8"/>
+      <c r="H37" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="I37" s="19"/>
-      <c r="J37" s="19"/>
-      <c r="K37" s="19"/>
-      <c r="L37" s="19"/>
-      <c r="M37" s="19"/>
-      <c r="N37" s="19"/>
-      <c r="O37" s="19"/>
-      <c r="P37" s="19"/>
+      <c r="I37" s="23"/>
+      <c r="J37" s="23"/>
+      <c r="K37" s="23"/>
+      <c r="L37" s="23"/>
+      <c r="M37" s="23"/>
+      <c r="N37" s="23"/>
+      <c r="O37" s="23"/>
+      <c r="P37" s="23"/>
     </row>
     <row r="38" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="11" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B38" s="12" t="s">
         <v>23</v>
@@ -3184,263 +3326,283 @@
       <c r="C38" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="D38" s="18" t="s">
+      <c r="D38" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="H38" s="19" t="s">
+      <c r="E38" s="22"/>
+      <c r="F38" s="22"/>
+      <c r="G38" s="22"/>
+      <c r="H38" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="I38" s="19"/>
-      <c r="J38" s="19"/>
-      <c r="K38" s="19"/>
-      <c r="L38" s="19"/>
-      <c r="M38" s="19"/>
-      <c r="N38" s="19"/>
-      <c r="O38" s="19"/>
-      <c r="P38" s="19"/>
+      <c r="I38" s="23"/>
+      <c r="J38" s="23"/>
+      <c r="K38" s="23"/>
+      <c r="L38" s="23"/>
+      <c r="M38" s="23"/>
+      <c r="N38" s="23"/>
+      <c r="O38" s="23"/>
+      <c r="P38" s="23"/>
     </row>
     <row r="39" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="B39" s="8"/>
+      <c r="B39" s="6"/>
       <c r="C39" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="D39" s="18" t="s">
+      <c r="D39" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="H39" s="19" t="s">
+      <c r="E39" s="22"/>
+      <c r="F39" s="22"/>
+      <c r="G39" s="22"/>
+      <c r="H39" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="I39" s="19"/>
-      <c r="J39" s="19"/>
-      <c r="K39" s="19"/>
-      <c r="L39" s="19"/>
-      <c r="M39" s="19"/>
-      <c r="N39" s="19"/>
-      <c r="O39" s="19"/>
-      <c r="P39" s="19"/>
+      <c r="I39" s="23"/>
+      <c r="J39" s="23"/>
+      <c r="K39" s="23"/>
+      <c r="L39" s="23"/>
+      <c r="M39" s="23"/>
+      <c r="N39" s="23"/>
+      <c r="O39" s="23"/>
+      <c r="P39" s="23"/>
     </row>
     <row r="40" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I40" s="20" t="s">
+      <c r="I40" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="J40" s="20"/>
-      <c r="K40" s="20"/>
-      <c r="L40" s="20"/>
-      <c r="M40" s="20"/>
-      <c r="N40" s="20"/>
-      <c r="O40" s="20"/>
+      <c r="J40" s="24"/>
+      <c r="K40" s="24"/>
+      <c r="L40" s="24"/>
+      <c r="M40" s="24"/>
+      <c r="N40" s="24"/>
+      <c r="O40" s="24"/>
     </row>
     <row r="41" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H41" s="20" t="s">
+      <c r="H41" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="I41" s="20"/>
-      <c r="J41" s="20"/>
-      <c r="K41" s="20"/>
-      <c r="L41" s="20"/>
-      <c r="M41" s="20"/>
-      <c r="N41" s="20"/>
-      <c r="O41" s="20"/>
-      <c r="P41" s="20"/>
+      <c r="I41" s="24"/>
+      <c r="J41" s="24"/>
+      <c r="K41" s="24"/>
+      <c r="L41" s="24"/>
+      <c r="M41" s="24"/>
+      <c r="N41" s="24"/>
+      <c r="O41" s="24"/>
+      <c r="P41" s="24"/>
     </row>
     <row r="54" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="21"/>
-      <c r="B54" s="22"/>
-      <c r="C54" s="22"/>
-      <c r="D54" s="22"/>
-      <c r="E54" s="22"/>
-      <c r="F54" s="22"/>
-      <c r="G54" s="22"/>
-      <c r="H54" s="22"/>
+      <c r="A54" s="25"/>
+      <c r="B54" s="26"/>
+      <c r="C54" s="26"/>
+      <c r="D54" s="26"/>
+      <c r="E54" s="26"/>
+      <c r="F54" s="26"/>
+      <c r="G54" s="26"/>
+      <c r="H54" s="26"/>
     </row>
     <row r="55" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="21"/>
-      <c r="B55" s="23" t="s">
+      <c r="A55" s="25"/>
+      <c r="B55" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="C55" s="23"/>
-      <c r="D55" s="23" t="s">
+      <c r="C55" s="27"/>
+      <c r="D55" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="E55" s="23"/>
-      <c r="F55" s="23"/>
-      <c r="G55" s="23"/>
-      <c r="H55" s="23"/>
+      <c r="E55" s="27"/>
+      <c r="F55" s="27"/>
+      <c r="G55" s="27"/>
+      <c r="H55" s="27"/>
     </row>
     <row r="56" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="21"/>
-      <c r="B56" s="24" t="s">
+      <c r="A56" s="25"/>
+      <c r="B56" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="C56" s="24"/>
-      <c r="D56" s="24"/>
-      <c r="E56" s="23"/>
-      <c r="F56" s="25" t="s">
+      <c r="C56" s="28"/>
+      <c r="D56" s="28"/>
+      <c r="E56" s="27"/>
+      <c r="F56" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="G56" s="25"/>
-      <c r="H56" s="25"/>
+      <c r="G56" s="29"/>
+      <c r="H56" s="29"/>
     </row>
     <row r="57" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="21"/>
-      <c r="B57" s="26" t="s">
-        <v>3</v>
-      </c>
-      <c r="C57" s="27" t="s">
+      <c r="A57" s="25"/>
+      <c r="B57" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="C57" s="31" t="s">
         <v>23</v>
       </c>
-      <c r="D57" s="26" t="s">
+      <c r="D57" s="30" t="s">
         <v>24</v>
       </c>
-      <c r="E57" s="23"/>
-      <c r="F57" s="23"/>
-      <c r="G57" s="23"/>
-      <c r="H57" s="23"/>
+      <c r="E57" s="27"/>
+      <c r="F57" s="27"/>
+      <c r="G57" s="27"/>
+      <c r="H57" s="27"/>
     </row>
     <row r="58" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="21"/>
-      <c r="B58" s="23" t="s">
+      <c r="A58" s="25"/>
+      <c r="B58" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="C58" s="23"/>
-      <c r="D58" s="23" t="s">
+      <c r="C58" s="27"/>
+      <c r="D58" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="E58" s="23"/>
-      <c r="F58" s="23"/>
-      <c r="G58" s="23"/>
-      <c r="H58" s="23"/>
+      <c r="E58" s="27"/>
+      <c r="F58" s="27"/>
+      <c r="G58" s="27"/>
+      <c r="H58" s="27"/>
     </row>
     <row r="59" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="21"/>
-      <c r="B59" s="23"/>
-      <c r="C59" s="23"/>
-      <c r="D59" s="23"/>
-      <c r="E59" s="23"/>
-      <c r="F59" s="23"/>
-      <c r="G59" s="23"/>
-      <c r="H59" s="23"/>
+      <c r="A59" s="25"/>
+      <c r="B59" s="27"/>
+      <c r="C59" s="27"/>
+      <c r="D59" s="27"/>
+      <c r="E59" s="27"/>
+      <c r="F59" s="27"/>
+      <c r="G59" s="27"/>
+      <c r="H59" s="27"/>
     </row>
     <row r="60" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="21"/>
-      <c r="B60" s="28" t="s">
+      <c r="A60" s="25"/>
+      <c r="B60" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="C60" s="23" t="s">
+      <c r="C60" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="D60" s="23"/>
-      <c r="E60" s="23"/>
-      <c r="F60" s="23"/>
-      <c r="G60" s="23"/>
-      <c r="H60" s="23"/>
+      <c r="D60" s="27"/>
+      <c r="E60" s="27"/>
+      <c r="F60" s="27"/>
+      <c r="G60" s="27"/>
+      <c r="H60" s="27"/>
     </row>
     <row r="61" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="21"/>
-      <c r="B61" s="28" t="s">
+      <c r="A61" s="25"/>
+      <c r="B61" s="32" t="s">
         <v>27</v>
       </c>
-      <c r="C61" s="23" t="s">
+      <c r="C61" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="D61" s="23"/>
-      <c r="E61" s="23"/>
-      <c r="F61" s="23"/>
-      <c r="G61" s="23"/>
-      <c r="H61" s="23"/>
+      <c r="D61" s="27"/>
+      <c r="E61" s="27"/>
+      <c r="F61" s="27"/>
+      <c r="G61" s="27"/>
+      <c r="H61" s="27"/>
     </row>
     <row r="62" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="21"/>
-      <c r="B62" s="28" t="s">
+      <c r="A62" s="25"/>
+      <c r="B62" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="C62" s="23" t="s">
+      <c r="C62" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="D62" s="23"/>
-      <c r="E62" s="23"/>
-      <c r="F62" s="23"/>
-      <c r="G62" s="23"/>
-      <c r="H62" s="23"/>
+      <c r="D62" s="27"/>
+      <c r="E62" s="27"/>
+      <c r="F62" s="27"/>
+      <c r="G62" s="27"/>
+      <c r="H62" s="27"/>
     </row>
     <row r="63" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="21"/>
-      <c r="B63" s="28" t="s">
+      <c r="A63" s="25"/>
+      <c r="B63" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="C63" s="23" t="s">
+      <c r="C63" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="D63" s="23"/>
-      <c r="E63" s="23"/>
-      <c r="F63" s="23"/>
-      <c r="G63" s="23"/>
-      <c r="H63" s="23"/>
+      <c r="D63" s="27"/>
+      <c r="E63" s="27"/>
+      <c r="F63" s="27"/>
+      <c r="G63" s="27"/>
+      <c r="H63" s="27"/>
     </row>
     <row r="64" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="21"/>
-      <c r="B64" s="26" t="s">
-        <v>3</v>
-      </c>
-      <c r="C64" s="23" t="s">
+      <c r="A64" s="25"/>
+      <c r="B64" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="C64" s="27" t="s">
         <v>38</v>
       </c>
-      <c r="D64" s="23"/>
-      <c r="E64" s="23"/>
-      <c r="F64" s="23"/>
-      <c r="G64" s="23"/>
-      <c r="H64" s="23"/>
+      <c r="D64" s="27"/>
+      <c r="E64" s="27"/>
+      <c r="F64" s="27"/>
+      <c r="G64" s="27"/>
+      <c r="H64" s="27"/>
     </row>
     <row r="65" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="21"/>
-      <c r="B65" s="27" t="s">
+      <c r="A65" s="25"/>
+      <c r="B65" s="31" t="s">
         <v>23</v>
       </c>
-      <c r="C65" s="23" t="s">
+      <c r="C65" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="D65" s="23"/>
-      <c r="E65" s="23"/>
-      <c r="F65" s="23"/>
-      <c r="G65" s="23"/>
-      <c r="H65" s="23"/>
+      <c r="D65" s="27"/>
+      <c r="E65" s="27"/>
+      <c r="F65" s="27"/>
+      <c r="G65" s="27"/>
+      <c r="H65" s="27"/>
     </row>
     <row r="66" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="21"/>
-      <c r="B66" s="29" t="s">
+      <c r="A66" s="25"/>
+      <c r="B66" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="C66" s="22" t="s">
+      <c r="C66" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="D66" s="22"/>
-      <c r="E66" s="22"/>
-      <c r="F66" s="22"/>
-      <c r="G66" s="22"/>
-      <c r="H66" s="22"/>
+      <c r="D66" s="26"/>
+      <c r="E66" s="26"/>
+      <c r="F66" s="26"/>
+      <c r="G66" s="26"/>
+      <c r="H66" s="26"/>
     </row>
     <row r="67" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="21"/>
-      <c r="B67" s="22"/>
-      <c r="C67" s="22"/>
-      <c r="D67" s="22"/>
-      <c r="E67" s="22"/>
-      <c r="F67" s="22"/>
-      <c r="G67" s="22"/>
-      <c r="H67" s="22"/>
+      <c r="A67" s="25"/>
+      <c r="B67" s="26"/>
+      <c r="C67" s="26"/>
+      <c r="D67" s="26"/>
+      <c r="E67" s="26"/>
+      <c r="F67" s="26"/>
+      <c r="G67" s="26"/>
+      <c r="H67" s="26"/>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="25">
     <mergeCell ref="B1:D1"/>
-    <mergeCell ref="E1:G1"/>
     <mergeCell ref="A16:C16"/>
+    <mergeCell ref="F16:H16"/>
+    <mergeCell ref="K16:M16"/>
+    <mergeCell ref="P16:R16"/>
+    <mergeCell ref="U16:W16"/>
+    <mergeCell ref="Z16:AB16"/>
+    <mergeCell ref="AD16:AK16"/>
+    <mergeCell ref="F22:H22"/>
+    <mergeCell ref="K22:M22"/>
+    <mergeCell ref="P22:R22"/>
+    <mergeCell ref="U22:W22"/>
+    <mergeCell ref="K28:M28"/>
+    <mergeCell ref="P28:R28"/>
+    <mergeCell ref="D36:G36"/>
     <mergeCell ref="H36:P36"/>
     <mergeCell ref="A37:C37"/>
     <mergeCell ref="H37:P37"/>
+    <mergeCell ref="D38:G38"/>
     <mergeCell ref="H38:P38"/>
+    <mergeCell ref="D39:G39"/>
     <mergeCell ref="H39:P39"/>
     <mergeCell ref="I40:O40"/>
     <mergeCell ref="H41:P41"/>
@@ -3451,7 +3613,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B17">
+  <conditionalFormatting sqref="B17 G17 G23 L17 L23 L29 Q17 Q23 Q29 V17 V23 AA17">
     <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>0</formula>
     </cfRule>
@@ -3474,7 +3636,7 @@
   <dimension ref="A1:BL28"/>
   <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="64" min="1" style="30" width="3.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="64" min="1" style="34" width="3.86"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3482,18 +3644,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2" t="s">
-        <v>3</v>
-      </c>
+      <c r="F1" s="0"/>
+      <c r="G1" s="0"/>
+      <c r="H1" s="0"/>
       <c r="I1" s="0"/>
       <c r="J1" s="0"/>
       <c r="K1" s="0"/>
@@ -3553,21 +3713,17 @@
     </row>
     <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="35"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="G2" s="5"/>
-      <c r="H2" s="3" t="n">
-        <v>6</v>
-      </c>
+      <c r="F2" s="0"/>
+      <c r="G2" s="0"/>
+      <c r="H2" s="0"/>
       <c r="I2" s="0"/>
       <c r="J2" s="0"/>
       <c r="K2" s="0"/>
@@ -3627,21 +3783,19 @@
     </row>
     <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="5" t="s">
+      <c r="B3" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="3" t="n">
+      <c r="C3" s="36"/>
+      <c r="D3" s="36"/>
+      <c r="E3" s="3" t="n">
         <v>7</v>
       </c>
+      <c r="F3" s="0"/>
+      <c r="G3" s="0"/>
+      <c r="H3" s="0"/>
       <c r="I3" s="0"/>
       <c r="J3" s="0"/>
       <c r="K3" s="0"/>
@@ -3701,23 +3855,19 @@
     </row>
     <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="36" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="36"/>
+      <c r="D4" s="36"/>
+      <c r="E4" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="F4" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="G4" s="5"/>
-      <c r="H4" s="3" t="n">
-        <v>7</v>
-      </c>
+      <c r="F4" s="0"/>
+      <c r="G4" s="0"/>
+      <c r="H4" s="0"/>
       <c r="I4" s="0"/>
       <c r="J4" s="0"/>
       <c r="K4" s="0"/>
@@ -3777,21 +3927,19 @@
     </row>
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="36" t="s">
         <v>4</v>
       </c>
+      <c r="C5" s="36"/>
+      <c r="D5" s="36"/>
+      <c r="E5" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F5" s="0"/>
+      <c r="G5" s="0"/>
+      <c r="H5" s="0"/>
       <c r="I5" s="0"/>
       <c r="J5" s="0"/>
       <c r="K5" s="0"/>
@@ -3851,21 +3999,19 @@
     </row>
     <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="3" t="n">
+      <c r="B6" s="36" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="36"/>
+      <c r="D6" s="36"/>
+      <c r="E6" s="3" t="n">
         <v>4</v>
       </c>
+      <c r="F6" s="0"/>
+      <c r="G6" s="0"/>
+      <c r="H6" s="0"/>
       <c r="I6" s="0"/>
       <c r="J6" s="0"/>
       <c r="K6" s="0"/>
@@ -3925,21 +4071,19 @@
     </row>
     <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B7" s="36" t="s">
         <v>5</v>
       </c>
+      <c r="C7" s="36"/>
+      <c r="D7" s="36"/>
+      <c r="E7" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" s="0"/>
+      <c r="G7" s="0"/>
+      <c r="H7" s="0"/>
       <c r="I7" s="0"/>
       <c r="J7" s="0"/>
       <c r="K7" s="0"/>
@@ -3999,25 +4143,21 @@
     </row>
     <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="36" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8" s="36" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="36"/>
+      <c r="E8" s="37" t="n">
         <v>3</v>
       </c>
-      <c r="C8" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="D8" s="6"/>
-      <c r="E8" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G8" s="5"/>
-      <c r="H8" s="31" t="n">
-        <v>3</v>
-      </c>
+      <c r="F8" s="0"/>
+      <c r="G8" s="0"/>
+      <c r="H8" s="0"/>
       <c r="I8" s="0"/>
       <c r="J8" s="0"/>
       <c r="K8" s="0"/>
@@ -4077,23 +4217,21 @@
     </row>
     <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="36" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="36" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9" s="6"/>
-      <c r="E9" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="3" t="n">
+      <c r="D9" s="36"/>
+      <c r="E9" s="3" t="n">
         <v>6</v>
       </c>
+      <c r="F9" s="0"/>
+      <c r="G9" s="0"/>
+      <c r="H9" s="0"/>
       <c r="I9" s="0"/>
       <c r="J9" s="0"/>
       <c r="K9" s="0"/>
@@ -4153,19 +4291,21 @@
     </row>
     <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="3" t="n">
+      <c r="B10" s="36" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="36"/>
+      <c r="E10" s="3" t="n">
         <v>2</v>
       </c>
+      <c r="F10" s="0"/>
+      <c r="G10" s="0"/>
+      <c r="H10" s="0"/>
       <c r="I10" s="0"/>
       <c r="J10" s="0"/>
       <c r="K10" s="0"/>
@@ -4247,116 +4387,191 @@
       <c r="X11" s="0"/>
     </row>
     <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="7"/>
-      <c r="B12" s="8"/>
-      <c r="C12" s="9"/>
+      <c r="A12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="B12" s="6"/>
+      <c r="C12" s="7" t="n">
+        <v>6</v>
+      </c>
       <c r="D12" s="0"/>
       <c r="E12" s="0"/>
-      <c r="F12" s="0"/>
-      <c r="G12" s="0"/>
-      <c r="H12" s="0"/>
+      <c r="F12" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="G12" s="6"/>
+      <c r="H12" s="7" t="n">
+        <v>13</v>
+      </c>
       <c r="I12" s="0"/>
       <c r="J12" s="0"/>
-      <c r="K12" s="0"/>
-      <c r="L12" s="0"/>
-      <c r="M12" s="0"/>
+      <c r="K12" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="L12" s="6"/>
+      <c r="M12" s="7" t="n">
+        <v>17</v>
+      </c>
       <c r="N12" s="0"/>
       <c r="O12" s="0"/>
-      <c r="P12" s="0"/>
-      <c r="Q12" s="0"/>
-      <c r="R12" s="0"/>
+      <c r="P12" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q12" s="6"/>
+      <c r="R12" s="7" t="n">
+        <v>20</v>
+      </c>
       <c r="S12" s="0"/>
       <c r="T12" s="0"/>
-      <c r="U12" s="0"/>
-      <c r="V12" s="0"/>
-      <c r="W12" s="0"/>
+      <c r="U12" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="V12" s="6"/>
+      <c r="W12" s="7" t="n">
+        <v>26</v>
+      </c>
       <c r="X12" s="0"/>
     </row>
     <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="10" t="s">
+      <c r="A13" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="B13" s="10"/>
-      <c r="C13" s="10"/>
-      <c r="D13" s="0"/>
-      <c r="E13" s="0"/>
-      <c r="F13" s="0"/>
-      <c r="G13" s="0"/>
-      <c r="H13" s="0"/>
-      <c r="I13" s="0"/>
-      <c r="J13" s="0"/>
-      <c r="K13" s="0"/>
-      <c r="L13" s="0"/>
-      <c r="M13" s="0"/>
-      <c r="N13" s="0"/>
-      <c r="O13" s="0"/>
-      <c r="P13" s="0"/>
-      <c r="Q13" s="0"/>
-      <c r="R13" s="0"/>
-      <c r="S13" s="0"/>
-      <c r="T13" s="0"/>
-      <c r="U13" s="0"/>
-      <c r="V13" s="0"/>
-      <c r="W13" s="0"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="9"/>
+      <c r="J13" s="9"/>
+      <c r="K13" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="L13" s="8"/>
+      <c r="M13" s="8"/>
+      <c r="N13" s="9"/>
+      <c r="O13" s="9"/>
+      <c r="P13" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q13" s="8"/>
+      <c r="R13" s="8"/>
+      <c r="S13" s="9"/>
+      <c r="T13" s="9"/>
+      <c r="U13" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="V13" s="8"/>
+      <c r="W13" s="8"/>
       <c r="X13" s="0"/>
     </row>
     <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="11" t="n">
-        <f aca="false">VLOOKUP(A13,$A$2:$H$10,8)</f>
         <v>6</v>
       </c>
-      <c r="B14" s="12"/>
-      <c r="C14" s="13"/>
+      <c r="B14" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="13" t="n">
+        <v>0</v>
+      </c>
       <c r="D14" s="0"/>
       <c r="E14" s="0"/>
-      <c r="F14" s="0"/>
-      <c r="G14" s="0"/>
-      <c r="H14" s="0"/>
+      <c r="F14" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="G14" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="H14" s="13" t="n">
+        <v>0</v>
+      </c>
       <c r="I14" s="0"/>
       <c r="J14" s="0"/>
-      <c r="K14" s="0"/>
-      <c r="L14" s="0"/>
-      <c r="M14" s="0"/>
+      <c r="K14" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="L14" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="M14" s="13" t="n">
+        <v>0</v>
+      </c>
       <c r="N14" s="0"/>
       <c r="O14" s="0"/>
-      <c r="P14" s="0"/>
-      <c r="Q14" s="0"/>
-      <c r="R14" s="0"/>
+      <c r="P14" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="R14" s="13" t="n">
+        <v>4</v>
+      </c>
       <c r="S14" s="0"/>
       <c r="T14" s="0"/>
-      <c r="U14" s="0"/>
-      <c r="V14" s="0"/>
-      <c r="W14" s="0"/>
+      <c r="U14" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="V14" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" s="13" t="n">
+        <v>0</v>
+      </c>
       <c r="X14" s="0"/>
     </row>
     <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="14"/>
-      <c r="B15" s="8"/>
-      <c r="C15" s="15"/>
-      <c r="D15" s="0"/>
+      <c r="A15" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="B15" s="6"/>
+      <c r="C15" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="D15" s="16"/>
       <c r="E15" s="0"/>
-      <c r="F15" s="0"/>
-      <c r="G15" s="0"/>
-      <c r="H15" s="0"/>
+      <c r="F15" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="G15" s="6"/>
+      <c r="H15" s="15" t="n">
+        <v>17</v>
+      </c>
       <c r="I15" s="0"/>
       <c r="J15" s="0"/>
-      <c r="K15" s="0"/>
-      <c r="L15" s="0"/>
-      <c r="M15" s="0"/>
+      <c r="K15" s="14" t="n">
+        <v>17</v>
+      </c>
+      <c r="L15" s="6"/>
+      <c r="M15" s="15" t="n">
+        <v>21</v>
+      </c>
       <c r="N15" s="0"/>
       <c r="O15" s="0"/>
-      <c r="P15" s="0"/>
-      <c r="Q15" s="0"/>
-      <c r="R15" s="0"/>
-      <c r="S15" s="0"/>
-      <c r="T15" s="0"/>
-      <c r="U15" s="0"/>
-      <c r="V15" s="0"/>
-      <c r="W15" s="0"/>
+      <c r="P15" s="14" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q15" s="6"/>
+      <c r="R15" s="15" t="n">
+        <v>24</v>
+      </c>
+      <c r="S15" s="17"/>
+      <c r="T15" s="18"/>
+      <c r="U15" s="14" t="n">
+        <v>24</v>
+      </c>
+      <c r="V15" s="6"/>
+      <c r="W15" s="15" t="n">
+        <v>26</v>
+      </c>
       <c r="X15" s="0"/>
     </row>
     <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D16" s="0"/>
+      <c r="D16" s="17"/>
       <c r="E16" s="0"/>
       <c r="F16" s="0"/>
       <c r="G16" s="0"/>
@@ -4371,7 +4586,7 @@
       <c r="P16" s="0"/>
       <c r="Q16" s="0"/>
       <c r="R16" s="0"/>
-      <c r="S16" s="0"/>
+      <c r="S16" s="17"/>
       <c r="T16" s="0"/>
       <c r="U16" s="0"/>
       <c r="V16" s="0"/>
@@ -4379,7 +4594,7 @@
       <c r="X16" s="0"/>
     </row>
     <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D17" s="0"/>
+      <c r="D17" s="17"/>
       <c r="E17" s="0"/>
       <c r="F17" s="0"/>
       <c r="G17" s="0"/>
@@ -4394,7 +4609,7 @@
       <c r="P17" s="0"/>
       <c r="Q17" s="0"/>
       <c r="R17" s="0"/>
-      <c r="S17" s="0"/>
+      <c r="S17" s="17"/>
       <c r="T17" s="0"/>
       <c r="U17" s="0"/>
       <c r="V17" s="0"/>
@@ -4402,22 +4617,34 @@
       <c r="X17" s="0"/>
     </row>
     <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D18" s="0"/>
+      <c r="D18" s="17"/>
       <c r="E18" s="0"/>
-      <c r="F18" s="0"/>
-      <c r="G18" s="0"/>
-      <c r="H18" s="0"/>
+      <c r="F18" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="G18" s="6"/>
+      <c r="H18" s="7" t="n">
+        <v>13</v>
+      </c>
       <c r="I18" s="0"/>
       <c r="J18" s="0"/>
-      <c r="K18" s="0"/>
-      <c r="L18" s="0"/>
-      <c r="M18" s="0"/>
+      <c r="K18" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="L18" s="6"/>
+      <c r="M18" s="7" t="n">
+        <v>17</v>
+      </c>
       <c r="N18" s="0"/>
       <c r="O18" s="0"/>
-      <c r="P18" s="0"/>
-      <c r="Q18" s="0"/>
-      <c r="R18" s="0"/>
-      <c r="S18" s="0"/>
+      <c r="P18" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q18" s="6"/>
+      <c r="R18" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="S18" s="17"/>
       <c r="T18" s="0"/>
       <c r="U18" s="0"/>
       <c r="V18" s="0"/>
@@ -4425,22 +4652,28 @@
       <c r="X18" s="0"/>
     </row>
     <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D19" s="0"/>
-      <c r="E19" s="0"/>
-      <c r="F19" s="0"/>
-      <c r="G19" s="0"/>
-      <c r="H19" s="0"/>
-      <c r="I19" s="0"/>
-      <c r="J19" s="0"/>
-      <c r="K19" s="0"/>
-      <c r="L19" s="0"/>
-      <c r="M19" s="0"/>
-      <c r="N19" s="0"/>
-      <c r="O19" s="0"/>
-      <c r="P19" s="0"/>
-      <c r="Q19" s="0"/>
-      <c r="R19" s="0"/>
-      <c r="S19" s="0"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="G19" s="8"/>
+      <c r="H19" s="8"/>
+      <c r="I19" s="9"/>
+      <c r="J19" s="9"/>
+      <c r="K19" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="L19" s="8"/>
+      <c r="M19" s="8"/>
+      <c r="N19" s="9"/>
+      <c r="O19" s="9"/>
+      <c r="P19" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q19" s="8"/>
+      <c r="R19" s="8"/>
+      <c r="S19" s="19"/>
       <c r="T19" s="0"/>
       <c r="U19" s="0"/>
       <c r="V19" s="0"/>
@@ -4450,19 +4683,37 @@
     <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D20" s="0"/>
       <c r="E20" s="0"/>
-      <c r="F20" s="0"/>
-      <c r="G20" s="0"/>
-      <c r="H20" s="0"/>
+      <c r="F20" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="G20" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="13" t="n">
+        <v>0</v>
+      </c>
       <c r="I20" s="0"/>
       <c r="J20" s="0"/>
-      <c r="K20" s="0"/>
-      <c r="L20" s="0"/>
-      <c r="M20" s="0"/>
+      <c r="K20" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="L20" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" s="13" t="n">
+        <v>1</v>
+      </c>
       <c r="N20" s="0"/>
       <c r="O20" s="0"/>
-      <c r="P20" s="0"/>
-      <c r="Q20" s="0"/>
-      <c r="R20" s="0"/>
+      <c r="P20" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q20" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" s="13" t="n">
+        <v>0</v>
+      </c>
       <c r="S20" s="0"/>
       <c r="T20" s="0"/>
       <c r="U20" s="0"/>
@@ -4473,19 +4724,31 @@
     <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D21" s="0"/>
       <c r="E21" s="0"/>
-      <c r="F21" s="0"/>
-      <c r="G21" s="0"/>
-      <c r="H21" s="0"/>
-      <c r="I21" s="0"/>
+      <c r="F21" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="G21" s="6"/>
+      <c r="H21" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="I21" s="16"/>
       <c r="J21" s="0"/>
-      <c r="K21" s="0"/>
-      <c r="L21" s="0"/>
-      <c r="M21" s="0"/>
-      <c r="N21" s="0"/>
-      <c r="O21" s="0"/>
-      <c r="P21" s="0"/>
-      <c r="Q21" s="0"/>
-      <c r="R21" s="0"/>
+      <c r="K21" s="14" t="n">
+        <v>14</v>
+      </c>
+      <c r="L21" s="6"/>
+      <c r="M21" s="15" t="n">
+        <v>18</v>
+      </c>
+      <c r="N21" s="17"/>
+      <c r="O21" s="18"/>
+      <c r="P21" s="14" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q21" s="6"/>
+      <c r="R21" s="15" t="n">
+        <v>24</v>
+      </c>
       <c r="S21" s="0"/>
       <c r="T21" s="0"/>
       <c r="U21" s="0"/>
@@ -4499,12 +4762,12 @@
       <c r="F22" s="0"/>
       <c r="G22" s="0"/>
       <c r="H22" s="0"/>
-      <c r="I22" s="0"/>
+      <c r="I22" s="17"/>
       <c r="J22" s="0"/>
       <c r="K22" s="0"/>
       <c r="L22" s="0"/>
       <c r="M22" s="0"/>
-      <c r="N22" s="0"/>
+      <c r="N22" s="17"/>
       <c r="O22" s="0"/>
       <c r="P22" s="0"/>
       <c r="Q22" s="0"/>
@@ -4522,12 +4785,12 @@
       <c r="F23" s="0"/>
       <c r="G23" s="0"/>
       <c r="H23" s="0"/>
-      <c r="I23" s="0"/>
+      <c r="I23" s="17"/>
       <c r="J23" s="0"/>
       <c r="K23" s="0"/>
       <c r="L23" s="0"/>
       <c r="M23" s="0"/>
-      <c r="N23" s="0"/>
+      <c r="N23" s="17"/>
       <c r="O23" s="0"/>
       <c r="P23" s="0"/>
       <c r="Q23" s="0"/>
@@ -4545,12 +4808,16 @@
       <c r="F24" s="0"/>
       <c r="G24" s="0"/>
       <c r="H24" s="0"/>
-      <c r="I24" s="0"/>
+      <c r="I24" s="17"/>
       <c r="J24" s="0"/>
-      <c r="K24" s="0"/>
-      <c r="L24" s="0"/>
-      <c r="M24" s="0"/>
-      <c r="N24" s="0"/>
+      <c r="K24" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="L24" s="6"/>
+      <c r="M24" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="N24" s="17"/>
       <c r="O24" s="0"/>
       <c r="P24" s="0"/>
       <c r="Q24" s="0"/>
@@ -4568,12 +4835,14 @@
       <c r="F25" s="0"/>
       <c r="G25" s="0"/>
       <c r="H25" s="0"/>
-      <c r="I25" s="0"/>
-      <c r="J25" s="0"/>
-      <c r="K25" s="0"/>
-      <c r="L25" s="0"/>
-      <c r="M25" s="0"/>
-      <c r="N25" s="0"/>
+      <c r="I25" s="17"/>
+      <c r="J25" s="9"/>
+      <c r="K25" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="L25" s="8"/>
+      <c r="M25" s="8"/>
+      <c r="N25" s="19"/>
       <c r="O25" s="0"/>
       <c r="P25" s="0"/>
       <c r="Q25" s="0"/>
@@ -4593,9 +4862,15 @@
       <c r="H26" s="0"/>
       <c r="I26" s="0"/>
       <c r="J26" s="0"/>
-      <c r="K26" s="0"/>
-      <c r="L26" s="0"/>
-      <c r="M26" s="0"/>
+      <c r="K26" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="L26" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" s="13" t="n">
+        <v>0</v>
+      </c>
       <c r="N26" s="0"/>
       <c r="O26" s="0"/>
       <c r="P26" s="0"/>
@@ -4616,9 +4891,13 @@
       <c r="H27" s="0"/>
       <c r="I27" s="0"/>
       <c r="J27" s="0"/>
-      <c r="K27" s="0"/>
-      <c r="L27" s="0"/>
-      <c r="M27" s="0"/>
+      <c r="K27" s="14" t="n">
+        <v>13</v>
+      </c>
+      <c r="L27" s="6"/>
+      <c r="M27" s="15" t="n">
+        <v>18</v>
+      </c>
       <c r="N27" s="0"/>
       <c r="O27" s="0"/>
       <c r="P27" s="0"/>
@@ -4655,17 +4934,24 @@
       <c r="X28" s="0"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="10">
     <mergeCell ref="B1:D1"/>
-    <mergeCell ref="E1:G1"/>
     <mergeCell ref="A13:C13"/>
+    <mergeCell ref="F13:H13"/>
+    <mergeCell ref="K13:M13"/>
+    <mergeCell ref="P13:R13"/>
+    <mergeCell ref="U13:W13"/>
+    <mergeCell ref="F19:H19"/>
+    <mergeCell ref="K19:M19"/>
+    <mergeCell ref="P19:R19"/>
+    <mergeCell ref="K25:M25"/>
   </mergeCells>
-  <conditionalFormatting sqref="B14">
+  <conditionalFormatting sqref="B14 G14 G20 L14 L20 L26 Q14 Q20 V14">
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H8">
+  <conditionalFormatting sqref="E8">
     <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
       <formula>0</formula>
     </cfRule>
@@ -4685,11 +4971,11 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:CR32"/>
+  <dimension ref="A1:CR1048576"/>
   <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="57" min="1" style="30" width="3.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="96" min="58" style="30" width="3.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="57" min="1" style="34" width="3.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="96" min="58" style="34" width="3.83"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4704,11 +4990,9 @@
       <c r="E1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2" t="s">
-        <v>3</v>
-      </c>
+      <c r="F1" s="0"/>
+      <c r="G1" s="0"/>
+      <c r="H1" s="0"/>
       <c r="I1" s="0"/>
       <c r="J1" s="0"/>
       <c r="K1" s="0"/>
@@ -4800,23 +5084,23 @@
     </row>
     <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="5" t="s">
+      <c r="C2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="H2" s="3" t="n">
+      <c r="D2" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="3" t="n">
         <v>15</v>
       </c>
+      <c r="F2" s="0"/>
+      <c r="G2" s="0"/>
+      <c r="H2" s="0"/>
       <c r="I2" s="0"/>
       <c r="J2" s="0"/>
       <c r="K2" s="0"/>
@@ -4908,21 +5192,19 @@
     </row>
     <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="3" t="n">
+      <c r="B3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="3" t="n">
         <v>6</v>
       </c>
+      <c r="F3" s="0"/>
+      <c r="G3" s="0"/>
+      <c r="H3" s="0"/>
       <c r="I3" s="0"/>
       <c r="J3" s="0"/>
       <c r="K3" s="0"/>
@@ -5014,21 +5296,19 @@
     </row>
     <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="3" t="n">
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="3" t="n">
         <v>14</v>
       </c>
+      <c r="F4" s="0"/>
+      <c r="G4" s="0"/>
+      <c r="H4" s="0"/>
       <c r="I4" s="0"/>
       <c r="J4" s="0"/>
       <c r="K4" s="0"/>
@@ -5120,21 +5400,19 @@
     </row>
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="3" t="n">
         <v>6</v>
       </c>
+      <c r="F5" s="0"/>
+      <c r="G5" s="0"/>
+      <c r="H5" s="0"/>
       <c r="I5" s="0"/>
       <c r="J5" s="0"/>
       <c r="K5" s="0"/>
@@ -5226,21 +5504,19 @@
     </row>
     <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="3" t="n">
+      <c r="B6" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="3" t="n">
         <v>15</v>
       </c>
+      <c r="F6" s="0"/>
+      <c r="G6" s="0"/>
+      <c r="H6" s="0"/>
       <c r="I6" s="0"/>
       <c r="J6" s="0"/>
       <c r="K6" s="0"/>
@@ -5332,21 +5608,19 @@
     </row>
     <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="3" t="n">
         <v>14</v>
       </c>
+      <c r="F7" s="0"/>
+      <c r="G7" s="0"/>
+      <c r="H7" s="0"/>
       <c r="I7" s="0"/>
       <c r="J7" s="0"/>
       <c r="K7" s="0"/>
@@ -5438,25 +5712,21 @@
     </row>
     <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D8" s="6"/>
-      <c r="E8" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G8" s="5"/>
-      <c r="H8" s="3" t="n">
+      <c r="D8" s="4"/>
+      <c r="E8" s="3" t="n">
         <v>7</v>
       </c>
+      <c r="F8" s="0"/>
+      <c r="G8" s="0"/>
+      <c r="H8" s="0"/>
       <c r="I8" s="0"/>
       <c r="J8" s="0"/>
       <c r="K8" s="0"/>
@@ -5547,16 +5817,20 @@
       <c r="CR8" s="0"/>
     </row>
     <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="32" t="s">
-        <v>41</v>
-      </c>
-      <c r="B9" s="32"/>
-      <c r="C9" s="32"/>
-      <c r="D9" s="32"/>
-      <c r="E9" s="32"/>
-      <c r="F9" s="32"/>
-      <c r="G9" s="32"/>
-      <c r="H9" s="32"/>
+      <c r="A9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="F9" s="0"/>
+      <c r="G9" s="0"/>
+      <c r="H9" s="0"/>
       <c r="I9" s="0"/>
       <c r="J9" s="0"/>
       <c r="K9" s="0"/>
@@ -5650,21 +5924,15 @@
       <c r="A10" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D10" s="6"/>
-      <c r="E10" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="3" t="n">
-        <v>15</v>
-      </c>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F10" s="0"/>
+      <c r="G10" s="0"/>
+      <c r="H10" s="0"/>
       <c r="I10" s="0"/>
       <c r="J10" s="0"/>
       <c r="K10" s="0"/>
@@ -5755,22 +6023,6 @@
       <c r="CR10" s="0"/>
     </row>
     <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D11" s="6"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="3" t="n">
-        <v>4</v>
-      </c>
       <c r="I11" s="0"/>
       <c r="J11" s="0"/>
       <c r="K11" s="0"/>
@@ -5861,6 +6113,14 @@
       <c r="CR11" s="0"/>
     </row>
     <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="5"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="0"/>
+      <c r="E12" s="0"/>
+      <c r="F12" s="0"/>
+      <c r="G12" s="0"/>
+      <c r="H12" s="0"/>
       <c r="I12" s="0"/>
       <c r="J12" s="0"/>
       <c r="K12" s="0"/>
@@ -5951,9 +6211,11 @@
       <c r="CR12" s="0"/>
     </row>
     <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="7"/>
+      <c r="A13" s="8" t="s">
+        <v>3</v>
+      </c>
       <c r="B13" s="8"/>
-      <c r="C13" s="9"/>
+      <c r="C13" s="8"/>
       <c r="D13" s="0"/>
       <c r="E13" s="0"/>
       <c r="F13" s="0"/>
@@ -6049,11 +6311,9 @@
       <c r="CR13" s="0"/>
     </row>
     <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
+      <c r="A14" s="11"/>
+      <c r="B14" s="12"/>
+      <c r="C14" s="13"/>
       <c r="D14" s="0"/>
       <c r="E14" s="0"/>
       <c r="F14" s="0"/>
@@ -6149,12 +6409,9 @@
       <c r="CR14" s="0"/>
     </row>
     <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="11" t="n">
-        <f aca="false">VLOOKUP(A14,$A$2:$H$11,8)</f>
-        <v>15</v>
-      </c>
-      <c r="B15" s="12"/>
-      <c r="C15" s="13"/>
+      <c r="A15" s="14"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="15"/>
       <c r="D15" s="0"/>
       <c r="E15" s="0"/>
       <c r="F15" s="0"/>
@@ -6250,9 +6507,6 @@
       <c r="CR15" s="0"/>
     </row>
     <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="14"/>
-      <c r="B16" s="8"/>
-      <c r="C16" s="15"/>
       <c r="D16" s="0"/>
       <c r="E16" s="0"/>
       <c r="F16" s="0"/>
@@ -7592,90 +7846,6 @@
       <c r="J30" s="0"/>
       <c r="K30" s="0"/>
       <c r="L30" s="0"/>
-      <c r="M30" s="0"/>
-      <c r="N30" s="0"/>
-      <c r="O30" s="0"/>
-      <c r="P30" s="0"/>
-      <c r="Q30" s="0"/>
-      <c r="R30" s="0"/>
-      <c r="S30" s="0"/>
-      <c r="T30" s="0"/>
-      <c r="U30" s="0"/>
-      <c r="V30" s="0"/>
-      <c r="W30" s="0"/>
-      <c r="X30" s="0"/>
-      <c r="Y30" s="0"/>
-      <c r="Z30" s="0"/>
-      <c r="AA30" s="0"/>
-      <c r="AB30" s="0"/>
-      <c r="AC30" s="0"/>
-      <c r="AD30" s="0"/>
-      <c r="AE30" s="0"/>
-      <c r="AF30" s="0"/>
-      <c r="AG30" s="0"/>
-      <c r="AH30" s="0"/>
-      <c r="AI30" s="0"/>
-      <c r="AJ30" s="0"/>
-      <c r="AK30" s="0"/>
-      <c r="AL30" s="0"/>
-      <c r="AM30" s="0"/>
-      <c r="AN30" s="0"/>
-      <c r="AO30" s="0"/>
-      <c r="AP30" s="0"/>
-      <c r="AQ30" s="0"/>
-      <c r="AR30" s="0"/>
-      <c r="AS30" s="0"/>
-      <c r="AT30" s="0"/>
-      <c r="AU30" s="0"/>
-      <c r="AV30" s="0"/>
-      <c r="AW30" s="0"/>
-      <c r="AX30" s="0"/>
-      <c r="AY30" s="0"/>
-      <c r="AZ30" s="0"/>
-      <c r="BA30" s="0"/>
-      <c r="BB30" s="0"/>
-      <c r="BC30" s="0"/>
-      <c r="BD30" s="0"/>
-      <c r="BE30" s="0"/>
-      <c r="BF30" s="0"/>
-      <c r="BG30" s="0"/>
-      <c r="BH30" s="0"/>
-      <c r="BI30" s="0"/>
-      <c r="BJ30" s="0"/>
-      <c r="BK30" s="0"/>
-      <c r="BL30" s="0"/>
-      <c r="BM30" s="0"/>
-      <c r="BN30" s="0"/>
-      <c r="BO30" s="0"/>
-      <c r="BP30" s="0"/>
-      <c r="BQ30" s="0"/>
-      <c r="BR30" s="0"/>
-      <c r="BS30" s="0"/>
-      <c r="BT30" s="0"/>
-      <c r="BU30" s="0"/>
-      <c r="BV30" s="0"/>
-      <c r="BW30" s="0"/>
-      <c r="BX30" s="0"/>
-      <c r="BY30" s="0"/>
-      <c r="BZ30" s="0"/>
-      <c r="CA30" s="0"/>
-      <c r="CB30" s="0"/>
-      <c r="CC30" s="0"/>
-      <c r="CD30" s="0"/>
-      <c r="CE30" s="0"/>
-      <c r="CF30" s="0"/>
-      <c r="CG30" s="0"/>
-      <c r="CH30" s="0"/>
-      <c r="CI30" s="0"/>
-      <c r="CJ30" s="0"/>
-      <c r="CK30" s="0"/>
-      <c r="CL30" s="0"/>
-      <c r="CM30" s="0"/>
-      <c r="CN30" s="0"/>
-      <c r="CO30" s="0"/>
-      <c r="CP30" s="0"/>
-      <c r="CQ30" s="0"/>
-      <c r="CR30" s="0"/>
     </row>
     <row r="31" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D31" s="0"/>
@@ -7688,25 +7858,13 @@
       <c r="K31" s="0"/>
       <c r="L31" s="0"/>
     </row>
-    <row r="32" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D32" s="0"/>
-      <c r="E32" s="0"/>
-      <c r="F32" s="0"/>
-      <c r="G32" s="0"/>
-      <c r="H32" s="0"/>
-      <c r="I32" s="0"/>
-      <c r="J32" s="0"/>
-      <c r="K32" s="0"/>
-      <c r="L32" s="0"/>
-    </row>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="2">
     <mergeCell ref="B1:D1"/>
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="A9:H9"/>
-    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="A13:C13"/>
   </mergeCells>
-  <conditionalFormatting sqref="B15">
+  <conditionalFormatting sqref="B14">
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>0</formula>
     </cfRule>
@@ -7726,14 +7884,14 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AB29"/>
+  <dimension ref="A1:BL32"/>
   <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="1" style="30" width="3.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="1" style="34" width="3.86"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="3.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="30" width="3.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="30" width="6.87"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="64" min="13" style="30" width="3.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="34" width="3.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="34" width="6.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="64" min="13" style="34" width="3.86"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7741,840 +7899,861 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="J1" s="33" t="s">
-        <v>42</v>
-      </c>
-      <c r="K1" s="33" t="s">
-        <v>43</v>
-      </c>
-      <c r="L1" s="33" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q1" s="30" t="s">
-        <v>44</v>
-      </c>
+      <c r="F1" s="0"/>
+      <c r="G1" s="0"/>
+      <c r="H1" s="0"/>
+      <c r="I1" s="0"/>
+      <c r="J1" s="0"/>
+      <c r="K1" s="0"/>
+      <c r="L1" s="0"/>
+      <c r="BJ1" s="0"/>
+      <c r="BK1" s="0"/>
+      <c r="BL1" s="0"/>
     </row>
     <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="G2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="3" t="n">
-        <f aca="false">ROUNDUP(J2/(K2*L2),0)</f>
-        <v>2</v>
-      </c>
-      <c r="J2" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="K2" s="3" t="n">
+      <c r="B2" s="35"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="L2" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q2" s="30" t="s">
-        <v>45</v>
-      </c>
+      <c r="F2" s="0"/>
+      <c r="G2" s="0"/>
+      <c r="H2" s="0"/>
+      <c r="I2" s="0"/>
+      <c r="J2" s="0"/>
+      <c r="K2" s="0"/>
+      <c r="L2" s="0"/>
+      <c r="BJ2" s="0"/>
+      <c r="BK2" s="0"/>
+      <c r="BL2" s="0"/>
     </row>
     <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="3" t="n">
-        <f aca="false">ROUNDUP(J3/(K3*L3),0)</f>
-        <v>15</v>
-      </c>
-      <c r="J3" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="K3" s="3" t="n">
+      <c r="B3" s="36" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="36"/>
+      <c r="D3" s="36"/>
+      <c r="E3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="L3" s="34" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="Q3" s="30" t="s">
-        <v>46</v>
-      </c>
+      <c r="F3" s="0"/>
+      <c r="G3" s="0"/>
+      <c r="H3" s="0"/>
+      <c r="I3" s="0"/>
+      <c r="J3" s="0"/>
+      <c r="K3" s="0"/>
+      <c r="L3" s="0"/>
+      <c r="BJ3" s="0"/>
+      <c r="BK3" s="0"/>
+      <c r="BL3" s="0"/>
     </row>
     <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="3" t="n">
-        <f aca="false">ROUNDUP(J4/(K4*L4),0)</f>
-        <v>7</v>
-      </c>
-      <c r="J4" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="K4" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B4" s="36" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="36"/>
+      <c r="D4" s="36"/>
+      <c r="E4" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="L4" s="34" t="n">
-        <v>1</v>
-      </c>
+      <c r="F4" s="0"/>
+      <c r="G4" s="0"/>
+      <c r="H4" s="0"/>
+      <c r="I4" s="0"/>
+      <c r="J4" s="0"/>
+      <c r="K4" s="0"/>
+      <c r="L4" s="0"/>
+      <c r="BJ4" s="0"/>
+      <c r="BK4" s="0"/>
+      <c r="BL4" s="0"/>
     </row>
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="3" t="n">
-        <f aca="false">ROUNDUP(J5/(K5*L5),0)</f>
-        <v>11</v>
-      </c>
-      <c r="J5" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="K5" s="3" t="n">
+      <c r="C5" s="36"/>
+      <c r="D5" s="36"/>
+      <c r="E5" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="L5" s="34" t="n">
-        <f aca="false">140%/K5</f>
-        <v>0.7</v>
-      </c>
-      <c r="Q5" s="30" t="s">
-        <v>47</v>
-      </c>
+      <c r="F5" s="0"/>
+      <c r="G5" s="0"/>
+      <c r="H5" s="0"/>
+      <c r="I5" s="0"/>
+      <c r="J5" s="0"/>
+      <c r="K5" s="0"/>
+      <c r="L5" s="0"/>
+      <c r="BJ5" s="0"/>
+      <c r="BK5" s="0"/>
+      <c r="BL5" s="0"/>
     </row>
     <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="3" t="n">
-        <f aca="false">ROUNDUP(J6/(K6*L6),0)</f>
-        <v>15</v>
-      </c>
-      <c r="J6" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="K6" s="3" t="n">
+      <c r="B6" s="36" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="36"/>
+      <c r="D6" s="36"/>
+      <c r="E6" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="L6" s="34" t="n">
-        <v>1</v>
-      </c>
+      <c r="F6" s="0"/>
+      <c r="G6" s="0"/>
+      <c r="H6" s="0"/>
+      <c r="I6" s="0"/>
+      <c r="J6" s="0"/>
+      <c r="K6" s="0"/>
+      <c r="L6" s="0"/>
+      <c r="BJ6" s="0"/>
+      <c r="BK6" s="0"/>
+      <c r="BL6" s="0"/>
     </row>
     <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="3" t="n">
-        <f aca="false">ROUNDUP(J7/(K7*L7),0)</f>
-        <v>10</v>
-      </c>
-      <c r="J7" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="K7" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B7" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="L7" s="34" t="n">
-        <f aca="false">140%/K7</f>
-        <v>0.7</v>
-      </c>
-      <c r="O7" s="3" t="n">
-        <f aca="false">J7/(K7*L7)</f>
-        <v>9.28571428571429</v>
-      </c>
+      <c r="C7" s="36"/>
+      <c r="D7" s="36"/>
+      <c r="E7" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" s="0"/>
+      <c r="G7" s="0"/>
+      <c r="H7" s="0"/>
+      <c r="I7" s="0"/>
+      <c r="J7" s="0"/>
+      <c r="K7" s="0"/>
+      <c r="L7" s="0"/>
+      <c r="BJ7" s="0"/>
+      <c r="BK7" s="0"/>
+      <c r="BL7" s="0"/>
     </row>
     <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="36" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="D8" s="6"/>
-      <c r="E8" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G8" s="5"/>
-      <c r="H8" s="3" t="n">
-        <f aca="false">ROUNDUP(J8/(K8*L8),0)</f>
-        <v>19</v>
-      </c>
-      <c r="J8" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="K8" s="3" t="n">
+      <c r="D8" s="36"/>
+      <c r="E8" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="L8" s="34" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="F8" s="0"/>
+      <c r="G8" s="0"/>
+      <c r="H8" s="0"/>
+      <c r="I8" s="0"/>
+      <c r="J8" s="0"/>
+      <c r="K8" s="0"/>
+      <c r="L8" s="0"/>
+      <c r="BJ8" s="0"/>
+      <c r="BK8" s="0"/>
+      <c r="BL8" s="0"/>
     </row>
     <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="36" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="36" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9" s="6"/>
-      <c r="E9" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="3" t="n">
-        <f aca="false">ROUNDUP(J9/(K9*L9),0)</f>
-        <v>7</v>
-      </c>
-      <c r="J9" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="K9" s="3" t="n">
+      <c r="D9" s="36"/>
+      <c r="E9" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="L9" s="34" t="n">
-        <v>1</v>
-      </c>
+      <c r="F9" s="0"/>
+      <c r="G9" s="0"/>
+      <c r="H9" s="0"/>
+      <c r="I9" s="0"/>
+      <c r="J9" s="0"/>
+      <c r="K9" s="0"/>
+      <c r="L9" s="0"/>
+      <c r="BJ9" s="0"/>
+      <c r="BK9" s="0"/>
+      <c r="BL9" s="0"/>
     </row>
     <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="3" t="n">
-        <f aca="false">ROUNDUP(J10/(K10*L10),0)</f>
         <v>10</v>
       </c>
-      <c r="J10" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="K10" s="3" t="n">
+      <c r="B10" s="36" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="36"/>
+      <c r="D10" s="36"/>
+      <c r="E10" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="L10" s="34" t="n">
-        <v>1</v>
-      </c>
+      <c r="F10" s="0"/>
+      <c r="G10" s="0"/>
+      <c r="H10" s="0"/>
+      <c r="I10" s="0"/>
+      <c r="J10" s="0"/>
+      <c r="K10" s="0"/>
+      <c r="L10" s="0"/>
+      <c r="BJ10" s="0"/>
+      <c r="BK10" s="0"/>
+      <c r="BL10" s="0"/>
     </row>
     <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="3" t="n">
-        <f aca="false">ROUNDUP(J11/(K11*L11),0)</f>
-        <v>10</v>
-      </c>
-      <c r="J11" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="K11" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="B11" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="36"/>
+      <c r="D11" s="36"/>
+      <c r="E11" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="L11" s="34" t="n">
-        <v>1</v>
-      </c>
+      <c r="F11" s="0"/>
+      <c r="G11" s="0"/>
+      <c r="H11" s="0"/>
+      <c r="I11" s="0"/>
+      <c r="J11" s="0"/>
+      <c r="K11" s="0"/>
+      <c r="L11" s="0"/>
+      <c r="BJ11" s="0"/>
+      <c r="BK11" s="0"/>
+      <c r="BL11" s="0"/>
     </row>
     <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="36" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D12" s="6"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="3" t="n">
-        <f aca="false">ROUNDUP(J12/(K12*L12),0)</f>
-        <v>2</v>
-      </c>
-      <c r="J12" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="K12" s="3" t="n">
+      <c r="D12" s="36"/>
+      <c r="E12" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="L12" s="34" t="n">
-        <v>1</v>
-      </c>
+      <c r="F12" s="0"/>
+      <c r="G12" s="0"/>
+      <c r="H12" s="0"/>
+      <c r="I12" s="0"/>
+      <c r="J12" s="0"/>
+      <c r="K12" s="0"/>
+      <c r="L12" s="0"/>
+      <c r="BJ12" s="0"/>
+      <c r="BK12" s="0"/>
+      <c r="BL12" s="0"/>
+    </row>
+    <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I13" s="0"/>
+      <c r="J13" s="0"/>
+      <c r="K13" s="0"/>
+      <c r="L13" s="0"/>
+      <c r="M13" s="0"/>
+      <c r="N13" s="0"/>
+      <c r="O13" s="0"/>
     </row>
     <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="B14" s="8"/>
-      <c r="C14" s="9" t="n">
-        <f aca="false">A14+A16</f>
-        <v>2</v>
-      </c>
-      <c r="F14" s="7" t="n">
-        <f aca="false">C14</f>
-        <v>2</v>
-      </c>
-      <c r="G14" s="8"/>
-      <c r="H14" s="9" t="n">
-        <f aca="false">F14+F16</f>
-        <v>17</v>
-      </c>
-      <c r="K14" s="7" t="n">
-        <f aca="false">H14</f>
-        <v>17</v>
-      </c>
-      <c r="L14" s="8"/>
-      <c r="M14" s="9" t="n">
-        <f aca="false">K14+K16</f>
-        <v>36</v>
-      </c>
-      <c r="P14" s="7" t="n">
-        <f aca="false">M14</f>
-        <v>36</v>
-      </c>
-      <c r="Q14" s="8"/>
-      <c r="R14" s="9" t="n">
-        <f aca="false">P14+P16</f>
-        <v>46</v>
-      </c>
-      <c r="Z14" s="7" t="n">
-        <f aca="false">MAX(R14,W20)</f>
-        <v>46</v>
-      </c>
-      <c r="AA14" s="8"/>
-      <c r="AB14" s="9" t="n">
-        <f aca="false">Z14+Z16</f>
-        <v>48</v>
-      </c>
+      <c r="A14" s="5"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="0"/>
+      <c r="E14" s="0"/>
+      <c r="F14" s="0"/>
+      <c r="G14" s="0"/>
+      <c r="H14" s="0"/>
+      <c r="I14" s="0"/>
+      <c r="J14" s="0"/>
+      <c r="K14" s="0"/>
+      <c r="L14" s="0"/>
+      <c r="M14" s="0"/>
+      <c r="N14" s="0"/>
+      <c r="O14" s="0"/>
+      <c r="P14" s="0"/>
+      <c r="Q14" s="0"/>
+      <c r="R14" s="0"/>
+      <c r="S14" s="0"/>
+      <c r="T14" s="0"/>
+      <c r="U14" s="0"/>
+      <c r="V14" s="0"/>
+      <c r="W14" s="0"/>
+      <c r="X14" s="0"/>
+      <c r="Y14" s="0"/>
+      <c r="Z14" s="0"/>
+      <c r="AA14" s="0"/>
+      <c r="AB14" s="0"/>
+      <c r="AC14" s="0"/>
+      <c r="AD14" s="0"/>
     </row>
     <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="B15" s="10"/>
-      <c r="C15" s="10"/>
-      <c r="D15" s="35"/>
-      <c r="E15" s="35"/>
-      <c r="F15" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="G15" s="10"/>
-      <c r="H15" s="10"/>
-      <c r="I15" s="35"/>
-      <c r="J15" s="36"/>
-      <c r="K15" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="L15" s="10"/>
-      <c r="M15" s="10"/>
-      <c r="N15" s="35"/>
-      <c r="O15" s="35"/>
-      <c r="P15" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="Q15" s="10"/>
-      <c r="R15" s="10"/>
-      <c r="S15" s="35"/>
-      <c r="T15" s="35"/>
-      <c r="U15" s="35"/>
-      <c r="V15" s="35"/>
-      <c r="W15" s="35"/>
-      <c r="X15" s="35"/>
-      <c r="Y15" s="35"/>
-      <c r="Z15" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="AA15" s="10"/>
-      <c r="AB15" s="10"/>
+      <c r="A15" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="0"/>
+      <c r="E15" s="0"/>
+      <c r="F15" s="0"/>
+      <c r="G15" s="0"/>
+      <c r="H15" s="0"/>
+      <c r="I15" s="0"/>
+      <c r="J15" s="0"/>
+      <c r="K15" s="0"/>
+      <c r="L15" s="0"/>
+      <c r="M15" s="0"/>
+      <c r="N15" s="0"/>
+      <c r="O15" s="0"/>
+      <c r="P15" s="0"/>
+      <c r="Q15" s="0"/>
+      <c r="R15" s="0"/>
+      <c r="S15" s="0"/>
+      <c r="T15" s="0"/>
+      <c r="U15" s="0"/>
+      <c r="V15" s="0"/>
+      <c r="W15" s="0"/>
+      <c r="X15" s="0"/>
+      <c r="Y15" s="0"/>
+      <c r="Z15" s="0"/>
+      <c r="AA15" s="0"/>
+      <c r="AB15" s="0"/>
+      <c r="AC15" s="0"/>
+      <c r="AD15" s="0"/>
     </row>
     <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="11" t="n">
-        <f aca="false">VLOOKUP(A15,$A$2:$H$12,8)</f>
-        <v>2</v>
-      </c>
-      <c r="B16" s="12" t="n">
-        <f aca="false">C17-C14</f>
-        <v>0</v>
-      </c>
-      <c r="C16" s="13" t="n">
-        <f aca="false">MIN(F14,F20,F26)-C14</f>
-        <v>0</v>
-      </c>
-      <c r="F16" s="11" t="n">
-        <f aca="false">VLOOKUP(F15,$A$2:$H$12,8)</f>
-        <v>15</v>
-      </c>
-      <c r="G16" s="12" t="n">
-        <f aca="false">H17-H14</f>
-        <v>0</v>
-      </c>
-      <c r="H16" s="13" t="n">
-        <f aca="false">K14-H14</f>
-        <v>0</v>
-      </c>
-      <c r="K16" s="11" t="n">
-        <f aca="false">VLOOKUP(K15,$A$2:$H$12,8)</f>
-        <v>19</v>
-      </c>
-      <c r="L16" s="12" t="n">
-        <f aca="false">M17-M14</f>
-        <v>0</v>
-      </c>
-      <c r="M16" s="13" t="n">
-        <f aca="false">P14-M14</f>
-        <v>0</v>
-      </c>
-      <c r="P16" s="11" t="n">
-        <f aca="false">VLOOKUP(P15,$A$2:$H$12,8)</f>
-        <v>10</v>
-      </c>
-      <c r="Q16" s="12" t="n">
-        <f aca="false">R17-R14</f>
-        <v>0</v>
-      </c>
-      <c r="R16" s="13" t="n">
-        <f aca="false">Z14-R14</f>
-        <v>0</v>
-      </c>
-      <c r="Z16" s="11" t="n">
-        <f aca="false">VLOOKUP(Z15,$A$2:$H$12,8)</f>
-        <v>2</v>
-      </c>
-      <c r="AA16" s="12" t="n">
-        <f aca="false">AB17-AB14</f>
-        <v>0</v>
-      </c>
-      <c r="AB16" s="13" t="n">
-        <v>0</v>
-      </c>
+      <c r="A16" s="11"/>
+      <c r="B16" s="12"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="0"/>
+      <c r="E16" s="0"/>
+      <c r="F16" s="0"/>
+      <c r="G16" s="0"/>
+      <c r="H16" s="0"/>
+      <c r="I16" s="0"/>
+      <c r="J16" s="0"/>
+      <c r="K16" s="0"/>
+      <c r="L16" s="0"/>
+      <c r="M16" s="0"/>
+      <c r="N16" s="0"/>
+      <c r="O16" s="0"/>
+      <c r="P16" s="0"/>
+      <c r="Q16" s="0"/>
+      <c r="R16" s="0"/>
+      <c r="S16" s="0"/>
+      <c r="T16" s="0"/>
+      <c r="U16" s="0"/>
+      <c r="V16" s="0"/>
+      <c r="W16" s="0"/>
+      <c r="X16" s="0"/>
+      <c r="Y16" s="0"/>
+      <c r="Z16" s="0"/>
+      <c r="AA16" s="0"/>
+      <c r="AB16" s="0"/>
+      <c r="AC16" s="0"/>
+      <c r="AD16" s="0"/>
     </row>
     <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="14" t="n">
-        <f aca="false">C17-A16</f>
-        <v>0</v>
-      </c>
-      <c r="B17" s="8"/>
-      <c r="C17" s="15" t="n">
-        <f aca="false">MIN(F17,F23,F29)</f>
-        <v>2</v>
-      </c>
-      <c r="D17" s="37"/>
-      <c r="F17" s="14" t="n">
-        <f aca="false">H17-F16</f>
-        <v>2</v>
-      </c>
-      <c r="G17" s="8"/>
-      <c r="H17" s="15" t="n">
-        <f aca="false">K17</f>
-        <v>17</v>
-      </c>
-      <c r="K17" s="14" t="n">
-        <f aca="false">M17-K16</f>
-        <v>17</v>
-      </c>
-      <c r="L17" s="8"/>
-      <c r="M17" s="15" t="n">
-        <f aca="false">P17</f>
-        <v>36</v>
-      </c>
-      <c r="P17" s="14" t="n">
-        <f aca="false">R17-P16</f>
-        <v>36</v>
-      </c>
-      <c r="Q17" s="8"/>
-      <c r="R17" s="15" t="n">
-        <f aca="false">Z17</f>
-        <v>46</v>
-      </c>
-      <c r="Y17" s="38"/>
-      <c r="Z17" s="14" t="n">
-        <f aca="false">AB17-Z16</f>
-        <v>46</v>
-      </c>
-      <c r="AA17" s="8"/>
-      <c r="AB17" s="15" t="n">
-        <f aca="false">AB14</f>
-        <v>48</v>
-      </c>
+      <c r="A17" s="14"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="15"/>
+      <c r="D17" s="0"/>
+      <c r="E17" s="0"/>
+      <c r="F17" s="0"/>
+      <c r="G17" s="0"/>
+      <c r="H17" s="0"/>
+      <c r="I17" s="0"/>
+      <c r="J17" s="0"/>
+      <c r="K17" s="0"/>
+      <c r="L17" s="0"/>
+      <c r="M17" s="0"/>
+      <c r="N17" s="0"/>
+      <c r="O17" s="0"/>
+      <c r="P17" s="0"/>
+      <c r="Q17" s="0"/>
+      <c r="R17" s="0"/>
+      <c r="S17" s="0"/>
+      <c r="T17" s="0"/>
+      <c r="U17" s="0"/>
+      <c r="V17" s="0"/>
+      <c r="W17" s="0"/>
+      <c r="X17" s="0"/>
+      <c r="Y17" s="0"/>
+      <c r="Z17" s="0"/>
+      <c r="AA17" s="0"/>
+      <c r="AB17" s="0"/>
+      <c r="AC17" s="0"/>
+      <c r="AD17" s="0"/>
     </row>
     <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D18" s="39"/>
-      <c r="Y18" s="40"/>
+      <c r="D18" s="0"/>
+      <c r="E18" s="0"/>
+      <c r="F18" s="0"/>
+      <c r="G18" s="0"/>
+      <c r="H18" s="0"/>
+      <c r="I18" s="0"/>
+      <c r="J18" s="0"/>
+      <c r="K18" s="0"/>
+      <c r="L18" s="0"/>
+      <c r="M18" s="0"/>
+      <c r="N18" s="0"/>
+      <c r="O18" s="0"/>
+      <c r="P18" s="0"/>
+      <c r="Q18" s="0"/>
+      <c r="R18" s="0"/>
+      <c r="S18" s="0"/>
+      <c r="T18" s="0"/>
+      <c r="U18" s="0"/>
+      <c r="V18" s="0"/>
+      <c r="W18" s="0"/>
+      <c r="X18" s="0"/>
+      <c r="Y18" s="0"/>
+      <c r="Z18" s="0"/>
+      <c r="AA18" s="0"/>
+      <c r="AB18" s="0"/>
+      <c r="AC18" s="0"/>
+      <c r="AD18" s="0"/>
     </row>
     <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D19" s="39"/>
-      <c r="Y19" s="40"/>
+      <c r="D19" s="0"/>
+      <c r="E19" s="0"/>
+      <c r="F19" s="0"/>
+      <c r="G19" s="0"/>
+      <c r="H19" s="0"/>
+      <c r="I19" s="0"/>
+      <c r="J19" s="0"/>
+      <c r="K19" s="0"/>
+      <c r="L19" s="0"/>
+      <c r="M19" s="0"/>
+      <c r="N19" s="0"/>
+      <c r="O19" s="0"/>
+      <c r="P19" s="0"/>
+      <c r="Q19" s="0"/>
+      <c r="R19" s="0"/>
+      <c r="S19" s="0"/>
+      <c r="T19" s="0"/>
+      <c r="U19" s="0"/>
+      <c r="V19" s="0"/>
+      <c r="W19" s="0"/>
+      <c r="X19" s="0"/>
+      <c r="Y19" s="0"/>
+      <c r="Z19" s="0"/>
+      <c r="AA19" s="0"/>
+      <c r="AB19" s="0"/>
+      <c r="AC19" s="0"/>
+      <c r="AD19" s="0"/>
     </row>
     <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D20" s="39"/>
-      <c r="F20" s="7" t="n">
-        <f aca="false">C14</f>
-        <v>2</v>
-      </c>
-      <c r="G20" s="8"/>
-      <c r="H20" s="9" t="n">
-        <f aca="false">F20+F22</f>
-        <v>9</v>
-      </c>
-      <c r="K20" s="7" t="n">
-        <f aca="false">H20</f>
-        <v>9</v>
-      </c>
-      <c r="L20" s="8"/>
-      <c r="M20" s="9" t="n">
-        <f aca="false">K20+K22</f>
-        <v>24</v>
-      </c>
-      <c r="P20" s="7" t="n">
-        <f aca="false">MAX(M20,M26)</f>
-        <v>24</v>
-      </c>
-      <c r="Q20" s="8"/>
-      <c r="R20" s="9" t="n">
-        <f aca="false">P20+P22</f>
-        <v>31</v>
-      </c>
-      <c r="U20" s="7" t="n">
-        <f aca="false">MAX(R20,R26)</f>
-        <v>31</v>
-      </c>
-      <c r="V20" s="8"/>
-      <c r="W20" s="9" t="n">
-        <f aca="false">U20+U22</f>
-        <v>41</v>
-      </c>
-      <c r="Y20" s="40"/>
+      <c r="D20" s="0"/>
+      <c r="E20" s="0"/>
+      <c r="F20" s="0"/>
+      <c r="G20" s="0"/>
+      <c r="H20" s="0"/>
+      <c r="I20" s="0"/>
+      <c r="J20" s="0"/>
+      <c r="K20" s="0"/>
+      <c r="L20" s="0"/>
+      <c r="M20" s="0"/>
+      <c r="N20" s="0"/>
+      <c r="O20" s="0"/>
+      <c r="P20" s="0"/>
+      <c r="Q20" s="0"/>
+      <c r="R20" s="0"/>
+      <c r="S20" s="0"/>
+      <c r="T20" s="0"/>
+      <c r="U20" s="0"/>
+      <c r="V20" s="0"/>
+      <c r="W20" s="0"/>
+      <c r="X20" s="0"/>
+      <c r="Y20" s="0"/>
+      <c r="Z20" s="0"/>
+      <c r="AA20" s="0"/>
+      <c r="AB20" s="0"/>
+      <c r="AC20" s="0"/>
+      <c r="AD20" s="0"/>
     </row>
     <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D21" s="39"/>
-      <c r="E21" s="35"/>
-      <c r="F21" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="G21" s="10"/>
-      <c r="H21" s="10"/>
-      <c r="I21" s="35"/>
-      <c r="J21" s="36"/>
-      <c r="K21" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="L21" s="10"/>
-      <c r="M21" s="10"/>
-      <c r="N21" s="35"/>
-      <c r="O21" s="35"/>
-      <c r="P21" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q21" s="10"/>
-      <c r="R21" s="10"/>
-      <c r="S21" s="35"/>
-      <c r="T21" s="35"/>
-      <c r="U21" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="V21" s="10"/>
-      <c r="W21" s="10"/>
-      <c r="X21" s="35"/>
-      <c r="Y21" s="40"/>
+      <c r="D21" s="0"/>
+      <c r="E21" s="0"/>
+      <c r="F21" s="0"/>
+      <c r="G21" s="0"/>
+      <c r="H21" s="0"/>
+      <c r="I21" s="0"/>
+      <c r="J21" s="0"/>
+      <c r="K21" s="0"/>
+      <c r="L21" s="0"/>
+      <c r="M21" s="0"/>
+      <c r="N21" s="0"/>
+      <c r="O21" s="0"/>
+      <c r="P21" s="0"/>
+      <c r="Q21" s="0"/>
+      <c r="R21" s="0"/>
+      <c r="S21" s="0"/>
+      <c r="T21" s="0"/>
+      <c r="U21" s="0"/>
+      <c r="V21" s="0"/>
+      <c r="W21" s="0"/>
+      <c r="X21" s="0"/>
+      <c r="Y21" s="0"/>
+      <c r="Z21" s="0"/>
+      <c r="AA21" s="0"/>
+      <c r="AB21" s="0"/>
+      <c r="AC21" s="0"/>
+      <c r="AD21" s="0"/>
     </row>
     <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D22" s="40"/>
-      <c r="F22" s="11" t="n">
-        <f aca="false">VLOOKUP(F21,$A$2:$H$12,8)</f>
-        <v>7</v>
-      </c>
-      <c r="G22" s="12" t="n">
-        <f aca="false">H23-H20</f>
-        <v>5</v>
-      </c>
-      <c r="H22" s="13" t="n">
-        <f aca="false">K20-H20</f>
-        <v>0</v>
-      </c>
-      <c r="K22" s="11" t="n">
-        <f aca="false">VLOOKUP(K21,$A$2:$H$12,8)</f>
-        <v>15</v>
-      </c>
-      <c r="L22" s="12" t="n">
-        <f aca="false">M23-M20</f>
-        <v>5</v>
-      </c>
-      <c r="M22" s="13" t="n">
-        <f aca="false">P20-M20</f>
-        <v>0</v>
-      </c>
-      <c r="P22" s="11" t="n">
-        <f aca="false">VLOOKUP(P21,$A$2:$H$12,8)</f>
-        <v>7</v>
-      </c>
-      <c r="Q22" s="12" t="n">
-        <f aca="false">R23-R20</f>
-        <v>5</v>
-      </c>
-      <c r="R22" s="13" t="n">
-        <f aca="false">U20-R20</f>
-        <v>0</v>
-      </c>
-      <c r="U22" s="11" t="n">
-        <f aca="false">VLOOKUP(U21,$A$2:$H$12,8)</f>
-        <v>10</v>
-      </c>
-      <c r="V22" s="12" t="n">
-        <f aca="false">W23-W20</f>
-        <v>5</v>
-      </c>
-      <c r="W22" s="13" t="n">
-        <f aca="false">Z14-W20</f>
-        <v>5</v>
-      </c>
+      <c r="D22" s="0"/>
+      <c r="E22" s="0"/>
+      <c r="F22" s="0"/>
+      <c r="G22" s="0"/>
+      <c r="H22" s="0"/>
+      <c r="I22" s="0"/>
+      <c r="J22" s="0"/>
+      <c r="K22" s="0"/>
+      <c r="L22" s="0"/>
+      <c r="M22" s="0"/>
+      <c r="N22" s="0"/>
+      <c r="O22" s="0"/>
+      <c r="P22" s="0"/>
+      <c r="Q22" s="0"/>
+      <c r="R22" s="0"/>
+      <c r="S22" s="0"/>
+      <c r="T22" s="0"/>
+      <c r="U22" s="0"/>
+      <c r="V22" s="0"/>
+      <c r="W22" s="0"/>
+      <c r="X22" s="0"/>
+      <c r="Y22" s="0"/>
+      <c r="Z22" s="0"/>
+      <c r="AA22" s="0"/>
+      <c r="AB22" s="0"/>
+      <c r="AC22" s="0"/>
+      <c r="AD22" s="0"/>
     </row>
     <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D23" s="40"/>
-      <c r="F23" s="14" t="n">
-        <f aca="false">H23-F22</f>
-        <v>7</v>
-      </c>
-      <c r="G23" s="8"/>
-      <c r="H23" s="15" t="n">
-        <f aca="false">K23</f>
-        <v>14</v>
-      </c>
-      <c r="K23" s="14" t="n">
-        <f aca="false">M23-K22</f>
-        <v>14</v>
-      </c>
-      <c r="L23" s="8"/>
-      <c r="M23" s="15" t="n">
-        <f aca="false">P23</f>
-        <v>29</v>
-      </c>
-      <c r="O23" s="38"/>
-      <c r="P23" s="14" t="n">
-        <f aca="false">R23-P22</f>
-        <v>29</v>
-      </c>
-      <c r="Q23" s="8"/>
-      <c r="R23" s="15" t="n">
-        <f aca="false">U23</f>
-        <v>36</v>
-      </c>
-      <c r="U23" s="14" t="n">
-        <f aca="false">W23-U22</f>
-        <v>36</v>
-      </c>
-      <c r="V23" s="8"/>
-      <c r="W23" s="15" t="n">
-        <f aca="false">Z17</f>
-        <v>46</v>
-      </c>
+      <c r="D23" s="0"/>
+      <c r="E23" s="0"/>
+      <c r="F23" s="0"/>
+      <c r="G23" s="0"/>
+      <c r="H23" s="0"/>
+      <c r="I23" s="0"/>
+      <c r="J23" s="0"/>
+      <c r="K23" s="0"/>
+      <c r="L23" s="0"/>
+      <c r="M23" s="0"/>
+      <c r="N23" s="0"/>
+      <c r="O23" s="0"/>
+      <c r="P23" s="0"/>
+      <c r="Q23" s="0"/>
+      <c r="R23" s="0"/>
+      <c r="S23" s="0"/>
+      <c r="T23" s="0"/>
+      <c r="U23" s="0"/>
+      <c r="V23" s="0"/>
+      <c r="W23" s="0"/>
+      <c r="X23" s="0"/>
+      <c r="Y23" s="0"/>
+      <c r="Z23" s="0"/>
+      <c r="AA23" s="0"/>
+      <c r="AB23" s="0"/>
+      <c r="AC23" s="0"/>
+      <c r="AD23" s="0"/>
     </row>
     <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D24" s="40"/>
-      <c r="O24" s="40"/>
+      <c r="D24" s="0"/>
+      <c r="E24" s="0"/>
+      <c r="F24" s="0"/>
+      <c r="G24" s="0"/>
+      <c r="H24" s="0"/>
+      <c r="I24" s="0"/>
+      <c r="J24" s="0"/>
+      <c r="K24" s="0"/>
+      <c r="L24" s="0"/>
+      <c r="M24" s="0"/>
+      <c r="N24" s="0"/>
+      <c r="O24" s="0"/>
+      <c r="P24" s="0"/>
+      <c r="Q24" s="0"/>
+      <c r="R24" s="0"/>
+      <c r="S24" s="0"/>
+      <c r="T24" s="0"/>
+      <c r="U24" s="0"/>
+      <c r="V24" s="0"/>
+      <c r="W24" s="0"/>
+      <c r="X24" s="0"/>
+      <c r="Y24" s="0"/>
+      <c r="Z24" s="0"/>
+      <c r="AA24" s="0"/>
+      <c r="AB24" s="0"/>
+      <c r="AC24" s="0"/>
+      <c r="AD24" s="0"/>
     </row>
     <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D25" s="40"/>
-      <c r="O25" s="40"/>
+      <c r="D25" s="0"/>
+      <c r="E25" s="0"/>
+      <c r="F25" s="0"/>
+      <c r="G25" s="0"/>
+      <c r="H25" s="0"/>
+      <c r="I25" s="0"/>
+      <c r="J25" s="0"/>
+      <c r="K25" s="0"/>
+      <c r="L25" s="0"/>
+      <c r="M25" s="0"/>
+      <c r="N25" s="0"/>
+      <c r="O25" s="0"/>
+      <c r="P25" s="0"/>
+      <c r="Q25" s="0"/>
+      <c r="R25" s="0"/>
+      <c r="S25" s="0"/>
+      <c r="T25" s="0"/>
+      <c r="U25" s="0"/>
+      <c r="V25" s="0"/>
+      <c r="W25" s="0"/>
+      <c r="X25" s="0"/>
+      <c r="Y25" s="0"/>
+      <c r="Z25" s="0"/>
+      <c r="AA25" s="0"/>
+      <c r="AB25" s="0"/>
+      <c r="AC25" s="0"/>
+      <c r="AD25" s="0"/>
     </row>
     <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D26" s="40"/>
-      <c r="F26" s="7" t="n">
-        <f aca="false">C14</f>
-        <v>2</v>
-      </c>
-      <c r="G26" s="8"/>
-      <c r="H26" s="9" t="n">
-        <f aca="false">F26+F28</f>
-        <v>13</v>
-      </c>
-      <c r="K26" s="7" t="n">
-        <f aca="false">H26</f>
-        <v>13</v>
-      </c>
-      <c r="L26" s="8"/>
-      <c r="M26" s="9" t="n">
-        <f aca="false">K26+K28</f>
-        <v>23</v>
-      </c>
-      <c r="O26" s="40"/>
+      <c r="D26" s="0"/>
+      <c r="E26" s="0"/>
+      <c r="F26" s="0"/>
+      <c r="G26" s="0"/>
+      <c r="H26" s="0"/>
+      <c r="I26" s="0"/>
+      <c r="J26" s="0"/>
+      <c r="K26" s="0"/>
+      <c r="L26" s="0"/>
+      <c r="M26" s="0"/>
+      <c r="N26" s="0"/>
+      <c r="O26" s="0"/>
+      <c r="P26" s="0"/>
+      <c r="Q26" s="0"/>
+      <c r="R26" s="0"/>
+      <c r="S26" s="0"/>
+      <c r="T26" s="0"/>
+      <c r="U26" s="0"/>
+      <c r="V26" s="0"/>
+      <c r="W26" s="0"/>
+      <c r="X26" s="0"/>
+      <c r="Y26" s="0"/>
+      <c r="Z26" s="0"/>
+      <c r="AA26" s="0"/>
+      <c r="AB26" s="0"/>
+      <c r="AC26" s="0"/>
+      <c r="AD26" s="0"/>
     </row>
     <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D27" s="41"/>
-      <c r="E27" s="35"/>
-      <c r="F27" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="G27" s="10"/>
-      <c r="H27" s="10"/>
-      <c r="I27" s="35"/>
-      <c r="J27" s="36"/>
-      <c r="K27" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="L27" s="10"/>
-      <c r="M27" s="10"/>
-      <c r="N27" s="35"/>
-      <c r="O27" s="40"/>
+      <c r="D27" s="0"/>
+      <c r="E27" s="0"/>
+      <c r="F27" s="0"/>
+      <c r="G27" s="0"/>
+      <c r="H27" s="0"/>
+      <c r="I27" s="0"/>
+      <c r="J27" s="0"/>
+      <c r="K27" s="0"/>
+      <c r="L27" s="0"/>
+      <c r="M27" s="0"/>
+      <c r="N27" s="0"/>
+      <c r="O27" s="0"/>
+      <c r="P27" s="0"/>
+      <c r="Q27" s="0"/>
+      <c r="R27" s="0"/>
+      <c r="S27" s="0"/>
+      <c r="T27" s="0"/>
+      <c r="U27" s="0"/>
+      <c r="V27" s="0"/>
+      <c r="W27" s="0"/>
+      <c r="X27" s="0"/>
+      <c r="Y27" s="0"/>
+      <c r="Z27" s="0"/>
+      <c r="AA27" s="0"/>
+      <c r="AB27" s="0"/>
+      <c r="AC27" s="0"/>
+      <c r="AD27" s="0"/>
     </row>
     <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F28" s="11" t="n">
-        <f aca="false">VLOOKUP(F27,$A$2:$H$12,8)</f>
-        <v>11</v>
-      </c>
-      <c r="G28" s="12" t="n">
-        <f aca="false">H29-H26</f>
-        <v>6</v>
-      </c>
-      <c r="H28" s="13" t="n">
-        <f aca="false">K26-H26</f>
-        <v>0</v>
-      </c>
-      <c r="K28" s="11" t="n">
-        <f aca="false">VLOOKUP(K27,$A$2:$H$12,8)</f>
-        <v>10</v>
-      </c>
-      <c r="L28" s="12" t="n">
-        <f aca="false">M29-M26</f>
-        <v>6</v>
-      </c>
-      <c r="M28" s="13" t="n">
-        <f aca="false">P20-M26</f>
-        <v>1</v>
-      </c>
+      <c r="D28" s="0"/>
+      <c r="E28" s="0"/>
+      <c r="F28" s="0"/>
+      <c r="G28" s="0"/>
+      <c r="H28" s="0"/>
+      <c r="I28" s="0"/>
+      <c r="J28" s="0"/>
+      <c r="K28" s="0"/>
+      <c r="L28" s="0"/>
+      <c r="M28" s="0"/>
+      <c r="N28" s="0"/>
+      <c r="O28" s="0"/>
+      <c r="P28" s="0"/>
+      <c r="Q28" s="0"/>
+      <c r="R28" s="0"/>
+      <c r="S28" s="0"/>
+      <c r="T28" s="0"/>
+      <c r="U28" s="0"/>
+      <c r="V28" s="0"/>
+      <c r="W28" s="0"/>
+      <c r="X28" s="0"/>
+      <c r="Y28" s="0"/>
+      <c r="Z28" s="0"/>
+      <c r="AA28" s="0"/>
+      <c r="AB28" s="0"/>
+      <c r="AC28" s="0"/>
+      <c r="AD28" s="0"/>
     </row>
     <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F29" s="14" t="n">
-        <f aca="false">H29-F28</f>
-        <v>8</v>
-      </c>
-      <c r="G29" s="8"/>
-      <c r="H29" s="15" t="n">
-        <f aca="false">K29</f>
-        <v>19</v>
-      </c>
-      <c r="K29" s="14" t="n">
-        <f aca="false">M29-K28</f>
-        <v>19</v>
-      </c>
-      <c r="L29" s="8"/>
-      <c r="M29" s="15" t="n">
-        <f aca="false">P23</f>
-        <v>29</v>
-      </c>
+      <c r="D29" s="0"/>
+      <c r="E29" s="0"/>
+      <c r="F29" s="0"/>
+      <c r="G29" s="0"/>
+      <c r="H29" s="0"/>
+      <c r="I29" s="0"/>
+      <c r="J29" s="0"/>
+      <c r="K29" s="0"/>
+      <c r="L29" s="0"/>
+      <c r="M29" s="0"/>
+      <c r="N29" s="0"/>
+      <c r="O29" s="0"/>
+      <c r="P29" s="0"/>
+      <c r="Q29" s="0"/>
+      <c r="R29" s="0"/>
+      <c r="S29" s="0"/>
+      <c r="T29" s="0"/>
+      <c r="U29" s="0"/>
+      <c r="V29" s="0"/>
+      <c r="W29" s="0"/>
+      <c r="X29" s="0"/>
+      <c r="Y29" s="0"/>
+      <c r="Z29" s="0"/>
+      <c r="AA29" s="0"/>
+      <c r="AB29" s="0"/>
+      <c r="AC29" s="0"/>
+      <c r="AD29" s="0"/>
+    </row>
+    <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D30" s="0"/>
+      <c r="E30" s="0"/>
+      <c r="F30" s="0"/>
+      <c r="G30" s="0"/>
+      <c r="H30" s="0"/>
+      <c r="I30" s="0"/>
+      <c r="J30" s="0"/>
+      <c r="K30" s="0"/>
+      <c r="L30" s="0"/>
+      <c r="M30" s="0"/>
+      <c r="N30" s="0"/>
+      <c r="O30" s="0"/>
+      <c r="P30" s="0"/>
+      <c r="Q30" s="0"/>
+      <c r="R30" s="0"/>
+      <c r="S30" s="0"/>
+      <c r="T30" s="0"/>
+      <c r="U30" s="0"/>
+      <c r="V30" s="0"/>
+      <c r="W30" s="0"/>
+      <c r="X30" s="0"/>
+      <c r="Y30" s="0"/>
+      <c r="Z30" s="0"/>
+      <c r="AA30" s="0"/>
+      <c r="AB30" s="0"/>
+      <c r="AC30" s="0"/>
+      <c r="AD30" s="0"/>
+    </row>
+    <row r="31" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D31" s="0"/>
+      <c r="E31" s="0"/>
+      <c r="F31" s="0"/>
+      <c r="G31" s="0"/>
+      <c r="H31" s="0"/>
+      <c r="I31" s="0"/>
+      <c r="J31" s="0"/>
+      <c r="K31" s="0"/>
+      <c r="L31" s="0"/>
+      <c r="M31" s="0"/>
+      <c r="N31" s="0"/>
+      <c r="O31" s="0"/>
+      <c r="P31" s="0"/>
+      <c r="Q31" s="0"/>
+      <c r="R31" s="0"/>
+      <c r="S31" s="0"/>
+      <c r="T31" s="0"/>
+      <c r="U31" s="0"/>
+      <c r="V31" s="0"/>
+      <c r="W31" s="0"/>
+      <c r="X31" s="0"/>
+      <c r="Y31" s="0"/>
+      <c r="Z31" s="0"/>
+      <c r="AA31" s="0"/>
+      <c r="AB31" s="0"/>
+      <c r="AC31" s="0"/>
+      <c r="AD31" s="0"/>
+    </row>
+    <row r="32" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D32" s="0"/>
+      <c r="E32" s="0"/>
+      <c r="F32" s="0"/>
+      <c r="G32" s="0"/>
+      <c r="H32" s="0"/>
+      <c r="I32" s="0"/>
+      <c r="J32" s="0"/>
+      <c r="K32" s="0"/>
+      <c r="L32" s="0"/>
+      <c r="M32" s="0"/>
+      <c r="N32" s="0"/>
+      <c r="O32" s="0"/>
+      <c r="P32" s="0"/>
+      <c r="Q32" s="0"/>
+      <c r="R32" s="0"/>
+      <c r="S32" s="0"/>
+      <c r="T32" s="0"/>
+      <c r="U32" s="0"/>
+      <c r="V32" s="0"/>
+      <c r="W32" s="0"/>
+      <c r="X32" s="0"/>
+      <c r="Y32" s="0"/>
+      <c r="Z32" s="0"/>
+      <c r="AA32" s="0"/>
+      <c r="AB32" s="0"/>
+      <c r="AC32" s="0"/>
+      <c r="AD32" s="0"/>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="2">
     <mergeCell ref="B1:D1"/>
-    <mergeCell ref="E1:G1"/>
     <mergeCell ref="A15:C15"/>
-    <mergeCell ref="F15:H15"/>
-    <mergeCell ref="K15:M15"/>
-    <mergeCell ref="P15:R15"/>
-    <mergeCell ref="Z15:AB15"/>
-    <mergeCell ref="F21:H21"/>
-    <mergeCell ref="K21:M21"/>
-    <mergeCell ref="P21:R21"/>
-    <mergeCell ref="U21:W21"/>
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="K27:M27"/>
   </mergeCells>
-  <conditionalFormatting sqref="G16 G22 G28 L16 L22 L28 Q22 Q16 V22 AA16 B16">
+  <conditionalFormatting sqref="B16">
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>0</formula>
     </cfRule>
@@ -8597,287 +8776,287 @@
   <dimension ref="A1:G1048576"/>
   <sheetFormatPr defaultColWidth="10.6796875" defaultRowHeight="12.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="42" width="8.84"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="30" width="23.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="30" width="23.96"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="30" width="11.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="30" width="32.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="38" width="8.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="34" width="23.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="34" width="23.96"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="34" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="34" width="32.84"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="42" t="s">
+      <c r="A1" s="38" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1" s="39" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="40" t="n">
+        <v>45297</v>
+      </c>
+      <c r="B2" s="38" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2" s="39" t="s">
+        <v>45</v>
+      </c>
+      <c r="E2" s="39" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2" s="41" t="n">
+        <v>45413</v>
+      </c>
+      <c r="G2" s="41" t="n">
+        <v>45414</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="40" t="n">
+        <v>45359</v>
+      </c>
+      <c r="B3" s="38" t="s">
+        <v>47</v>
+      </c>
+      <c r="C3" s="39" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="43" t="s">
+      <c r="D3" s="39" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="44" t="n">
-        <v>45297</v>
-      </c>
-      <c r="B2" s="42" t="s">
+      <c r="E3" s="39" t="s">
         <v>50</v>
       </c>
-      <c r="C2" s="43" t="s">
+    </row>
+    <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="40" t="n">
+        <v>45380</v>
+      </c>
+      <c r="B4" s="38" t="s">
         <v>51</v>
       </c>
-      <c r="E2" s="43" t="s">
+      <c r="C4" s="39" t="s">
         <v>52</v>
       </c>
-      <c r="F2" s="45" t="n">
+      <c r="D4" s="39" t="s">
+        <v>49</v>
+      </c>
+      <c r="E4" s="39" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="40" t="n">
+        <v>45383</v>
+      </c>
+      <c r="B5" s="38" t="s">
+        <v>54</v>
+      </c>
+      <c r="C5" s="39" t="s">
+        <v>55</v>
+      </c>
+      <c r="D5" s="39" t="s">
+        <v>49</v>
+      </c>
+      <c r="E5" s="39" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="40" t="n">
         <v>45413</v>
       </c>
-      <c r="G2" s="45" t="n">
-        <v>45414</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="44" t="n">
-        <v>45359</v>
-      </c>
-      <c r="B3" s="42" t="s">
+      <c r="B6" s="38" t="s">
+        <v>56</v>
+      </c>
+      <c r="C6" s="39" t="s">
+        <v>57</v>
+      </c>
+      <c r="E6" s="39" t="s">
         <v>53</v>
       </c>
-      <c r="C3" s="43" t="s">
-        <v>54</v>
-      </c>
-      <c r="D3" s="43" t="s">
-        <v>55</v>
-      </c>
-      <c r="E3" s="43" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="44" t="n">
-        <v>45380</v>
-      </c>
-      <c r="B4" s="42" t="s">
-        <v>57</v>
-      </c>
-      <c r="C4" s="43" t="s">
+    </row>
+    <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="40" t="n">
+        <v>45421</v>
+      </c>
+      <c r="B7" s="38" t="s">
         <v>58</v>
       </c>
-      <c r="D4" s="43" t="s">
-        <v>55</v>
-      </c>
-      <c r="E4" s="43" t="s">
+      <c r="C7" s="39" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="44" t="n">
-        <v>45383</v>
-      </c>
-      <c r="B5" s="42" t="s">
+      <c r="D7" s="39" t="s">
         <v>60</v>
       </c>
-      <c r="C5" s="43" t="s">
+      <c r="E7" s="39" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="40" t="n">
+        <v>45432</v>
+      </c>
+      <c r="B8" s="38" t="s">
         <v>61</v>
       </c>
-      <c r="D5" s="43" t="s">
-        <v>55</v>
-      </c>
-      <c r="E5" s="43" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="44" t="n">
-        <v>45413</v>
-      </c>
-      <c r="B6" s="42" t="s">
+      <c r="C8" s="39" t="s">
         <v>62</v>
       </c>
-      <c r="C6" s="43" t="s">
+      <c r="D8" s="39" t="s">
+        <v>49</v>
+      </c>
+      <c r="E8" s="39" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="40" t="n">
+        <v>45442</v>
+      </c>
+      <c r="B9" s="38" t="s">
         <v>63</v>
       </c>
-      <c r="E6" s="43" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="44" t="n">
-        <v>45421</v>
-      </c>
-      <c r="B7" s="42" t="s">
+      <c r="C9" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="C7" s="43" t="s">
+      <c r="D9" s="39" t="s">
+        <v>60</v>
+      </c>
+      <c r="E9" s="39" t="s">
         <v>65</v>
       </c>
-      <c r="D7" s="43" t="s">
+    </row>
+    <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="40" t="n">
+        <v>45519</v>
+      </c>
+      <c r="B10" s="38" t="s">
         <v>66</v>
       </c>
-      <c r="E7" s="43" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="44" t="n">
-        <v>45432</v>
-      </c>
-      <c r="B8" s="42" t="s">
+      <c r="C10" s="39" t="s">
         <v>67</v>
       </c>
-      <c r="C8" s="43" t="s">
+      <c r="D10" s="39" t="s">
+        <v>60</v>
+      </c>
+      <c r="E10" s="39" t="s">
         <v>68</v>
       </c>
-      <c r="D8" s="43" t="s">
-        <v>55</v>
-      </c>
-      <c r="E8" s="43" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="44" t="n">
-        <v>45442</v>
-      </c>
-      <c r="B9" s="42" t="s">
+    </row>
+    <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="40" t="n">
+        <v>45555</v>
+      </c>
+      <c r="B11" s="38" t="s">
         <v>69</v>
       </c>
-      <c r="C9" s="43" t="s">
+      <c r="C11" s="39" t="s">
         <v>70</v>
       </c>
-      <c r="D9" s="43" t="s">
-        <v>66</v>
-      </c>
-      <c r="E9" s="43" t="s">
+      <c r="D11" s="39" t="s">
+        <v>49</v>
+      </c>
+      <c r="E11" s="39" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="44" t="n">
-        <v>45519</v>
-      </c>
-      <c r="B10" s="42" t="s">
+    <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="40" t="n">
+        <v>45568</v>
+      </c>
+      <c r="B12" s="38" t="s">
         <v>72</v>
       </c>
-      <c r="C10" s="43" t="s">
+      <c r="C12" s="39" t="s">
         <v>73</v>
       </c>
-      <c r="D10" s="43" t="s">
-        <v>66</v>
-      </c>
-      <c r="E10" s="43" t="s">
+      <c r="D12" s="39" t="s">
+        <v>60</v>
+      </c>
+      <c r="E12" s="39" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="40" t="n">
+        <v>45596</v>
+      </c>
+      <c r="B13" s="38" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="44" t="n">
-        <v>45555</v>
-      </c>
-      <c r="B11" s="42" t="s">
+      <c r="C13" s="39" t="s">
         <v>75</v>
       </c>
-      <c r="C11" s="43" t="s">
+      <c r="D13" s="39" t="s">
+        <v>60</v>
+      </c>
+      <c r="E13" s="38" t="s">
         <v>76</v>
       </c>
-      <c r="D11" s="43" t="s">
-        <v>55</v>
-      </c>
-      <c r="E11" s="43" t="s">
+    </row>
+    <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="41" t="n">
+        <v>45597</v>
+      </c>
+      <c r="B14" s="38" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="44" t="n">
-        <v>45568</v>
-      </c>
-      <c r="B12" s="42" t="s">
+      <c r="C14" s="39" t="s">
+        <v>75</v>
+      </c>
+      <c r="D14" s="39" t="s">
+        <v>49</v>
+      </c>
+      <c r="E14" s="39" t="s">
         <v>78</v>
       </c>
-      <c r="C12" s="43" t="s">
+    </row>
+    <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="41" t="n">
+        <v>45616</v>
+      </c>
+      <c r="B15" s="38" t="s">
         <v>79</v>
       </c>
-      <c r="D12" s="43" t="s">
-        <v>66</v>
-      </c>
-      <c r="E12" s="43" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="44" t="n">
-        <v>45596</v>
-      </c>
-      <c r="B13" s="42" t="s">
+      <c r="C15" s="39" t="s">
         <v>80</v>
       </c>
-      <c r="C13" s="43" t="s">
+      <c r="E15" s="39" t="s">
         <v>81</v>
       </c>
-      <c r="D13" s="43" t="s">
-        <v>66</v>
-      </c>
-      <c r="E13" s="42" t="s">
+    </row>
+    <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="41" t="n">
+        <v>45651</v>
+      </c>
+      <c r="B16" s="38" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="45" t="n">
-        <v>45597</v>
-      </c>
-      <c r="B14" s="42" t="s">
+      <c r="C16" s="39" t="s">
         <v>83</v>
       </c>
-      <c r="C14" s="43" t="s">
-        <v>81</v>
-      </c>
-      <c r="D14" s="43" t="s">
-        <v>55</v>
-      </c>
-      <c r="E14" s="43" t="s">
+      <c r="D16" s="39" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="41" t="n">
+        <v>45652</v>
+      </c>
+      <c r="B17" s="38" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="45" t="n">
-        <v>45616</v>
-      </c>
-      <c r="B15" s="42" t="s">
-        <v>85</v>
-      </c>
-      <c r="C15" s="43" t="s">
-        <v>86</v>
-      </c>
-      <c r="E15" s="43" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="45" t="n">
-        <v>45651</v>
-      </c>
-      <c r="B16" s="42" t="s">
-        <v>88</v>
-      </c>
-      <c r="C16" s="43" t="s">
-        <v>89</v>
-      </c>
-      <c r="D16" s="43" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="45" t="n">
-        <v>45652</v>
-      </c>
-      <c r="B17" s="42" t="s">
-        <v>90</v>
-      </c>
-      <c r="C17" s="43" t="s">
-        <v>89</v>
-      </c>
-      <c r="D17" s="43" t="s">
-        <v>66</v>
-      </c>
-      <c r="E17" s="43" t="s">
-        <v>59</v>
-      </c>
-      <c r="F17" s="43" t="s">
+      <c r="C17" s="39" t="s">
+        <v>83</v>
+      </c>
+      <c r="D17" s="39" t="s">
+        <v>60</v>
+      </c>
+      <c r="E17" s="39" t="s">
+        <v>53</v>
+      </c>
+      <c r="F17" s="39" t="s">
         <v>12</v>
       </c>
     </row>

--- a/Übungen/Netzplan_Übung.xlsx
+++ b/Übungen/Netzplan_Übung.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Übung1" sheetId="1" state="visible" r:id="rId3"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="85">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -450,7 +450,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="9">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -514,6 +514,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin">
+        <color rgb="FFFF8000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFFF8000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin">
+        <color rgb="FFFF8000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="20">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -540,7 +560,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="45">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -691,6 +711,18 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -1007,7 +1039,9 @@
   <sheetFormatPr defaultColWidth="3.859375" defaultRowHeight="12.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4.57"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="9" min="2" style="1" width="3.86"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="7" min="2" style="1" width="3.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="4.17"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="3.86"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="3.5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="4.11"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="3.86"/>
@@ -6113,19 +6147,31 @@
       <c r="CR11" s="0"/>
     </row>
     <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="5"/>
+      <c r="A12" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="B12" s="6"/>
-      <c r="C12" s="7"/>
+      <c r="C12" s="7" t="n">
+        <v>15</v>
+      </c>
       <c r="D12" s="0"/>
       <c r="E12" s="0"/>
-      <c r="F12" s="0"/>
-      <c r="G12" s="0"/>
-      <c r="H12" s="0"/>
+      <c r="F12" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="G12" s="6"/>
+      <c r="H12" s="7" t="n">
+        <v>21</v>
+      </c>
       <c r="I12" s="0"/>
       <c r="J12" s="0"/>
-      <c r="K12" s="0"/>
-      <c r="L12" s="0"/>
-      <c r="M12" s="0"/>
+      <c r="K12" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="L12" s="6"/>
+      <c r="M12" s="7" t="n">
+        <v>28</v>
+      </c>
       <c r="N12" s="0"/>
       <c r="O12" s="0"/>
       <c r="P12" s="0"/>
@@ -6133,9 +6179,13 @@
       <c r="R12" s="0"/>
       <c r="S12" s="0"/>
       <c r="T12" s="0"/>
-      <c r="U12" s="0"/>
-      <c r="V12" s="0"/>
-      <c r="W12" s="0"/>
+      <c r="U12" s="5" t="n">
+        <v>59</v>
+      </c>
+      <c r="V12" s="6"/>
+      <c r="W12" s="7" t="n">
+        <v>63</v>
+      </c>
       <c r="X12" s="0"/>
       <c r="Y12" s="0"/>
       <c r="Z12" s="0"/>
@@ -6216,26 +6266,32 @@
       </c>
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
-      <c r="D13" s="0"/>
-      <c r="E13" s="0"/>
-      <c r="F13" s="0"/>
-      <c r="G13" s="0"/>
-      <c r="H13" s="0"/>
-      <c r="I13" s="0"/>
-      <c r="J13" s="0"/>
-      <c r="K13" s="0"/>
-      <c r="L13" s="0"/>
-      <c r="M13" s="0"/>
-      <c r="N13" s="0"/>
-      <c r="O13" s="0"/>
-      <c r="P13" s="0"/>
-      <c r="Q13" s="0"/>
-      <c r="R13" s="0"/>
-      <c r="S13" s="0"/>
-      <c r="T13" s="0"/>
-      <c r="U13" s="0"/>
-      <c r="V13" s="0"/>
-      <c r="W13" s="0"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="9"/>
+      <c r="J13" s="9"/>
+      <c r="K13" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="L13" s="8"/>
+      <c r="M13" s="8"/>
+      <c r="N13" s="9"/>
+      <c r="O13" s="9"/>
+      <c r="P13" s="9"/>
+      <c r="Q13" s="9"/>
+      <c r="R13" s="9"/>
+      <c r="S13" s="9"/>
+      <c r="T13" s="9"/>
+      <c r="U13" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="V13" s="8"/>
+      <c r="W13" s="8"/>
       <c r="X13" s="0"/>
       <c r="Y13" s="0"/>
       <c r="Z13" s="0"/>
@@ -6311,19 +6367,37 @@
       <c r="CR13" s="0"/>
     </row>
     <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="11"/>
-      <c r="B14" s="12"/>
-      <c r="C14" s="13"/>
+      <c r="A14" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="B14" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="13" t="n">
+        <v>0</v>
+      </c>
       <c r="D14" s="0"/>
       <c r="E14" s="0"/>
-      <c r="F14" s="0"/>
-      <c r="G14" s="0"/>
-      <c r="H14" s="0"/>
+      <c r="F14" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="G14" s="12" t="n">
+        <v>31</v>
+      </c>
+      <c r="H14" s="13" t="n">
+        <v>0</v>
+      </c>
       <c r="I14" s="0"/>
       <c r="J14" s="0"/>
-      <c r="K14" s="0"/>
-      <c r="L14" s="0"/>
-      <c r="M14" s="0"/>
+      <c r="K14" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="L14" s="12" t="n">
+        <v>31</v>
+      </c>
+      <c r="M14" s="13" t="n">
+        <v>31</v>
+      </c>
       <c r="N14" s="0"/>
       <c r="O14" s="0"/>
       <c r="P14" s="0"/>
@@ -6331,9 +6405,15 @@
       <c r="R14" s="0"/>
       <c r="S14" s="0"/>
       <c r="T14" s="0"/>
-      <c r="U14" s="0"/>
-      <c r="V14" s="0"/>
-      <c r="W14" s="0"/>
+      <c r="U14" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="V14" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" s="13" t="n">
+        <v>0</v>
+      </c>
       <c r="X14" s="0"/>
       <c r="Y14" s="0"/>
       <c r="Z14" s="0"/>
@@ -6409,29 +6489,45 @@
       <c r="CR14" s="0"/>
     </row>
     <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="14"/>
+      <c r="A15" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="B15" s="6"/>
-      <c r="C15" s="15"/>
-      <c r="D15" s="0"/>
+      <c r="C15" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="D15" s="16"/>
       <c r="E15" s="0"/>
-      <c r="F15" s="0"/>
-      <c r="G15" s="0"/>
-      <c r="H15" s="0"/>
+      <c r="F15" s="14" t="n">
+        <v>46</v>
+      </c>
+      <c r="G15" s="6"/>
+      <c r="H15" s="15" t="n">
+        <v>52</v>
+      </c>
       <c r="I15" s="0"/>
       <c r="J15" s="0"/>
-      <c r="K15" s="0"/>
-      <c r="L15" s="0"/>
-      <c r="M15" s="0"/>
+      <c r="K15" s="14" t="n">
+        <v>52</v>
+      </c>
+      <c r="L15" s="6"/>
+      <c r="M15" s="15" t="n">
+        <v>59</v>
+      </c>
       <c r="N15" s="0"/>
       <c r="O15" s="0"/>
       <c r="P15" s="0"/>
       <c r="Q15" s="0"/>
       <c r="R15" s="0"/>
-      <c r="S15" s="0"/>
-      <c r="T15" s="0"/>
-      <c r="U15" s="0"/>
-      <c r="V15" s="0"/>
-      <c r="W15" s="0"/>
+      <c r="S15" s="17"/>
+      <c r="T15" s="18"/>
+      <c r="U15" s="14" t="n">
+        <v>59</v>
+      </c>
+      <c r="V15" s="6"/>
+      <c r="W15" s="15" t="n">
+        <v>63</v>
+      </c>
       <c r="X15" s="0"/>
       <c r="Y15" s="0"/>
       <c r="Z15" s="0"/>
@@ -6507,7 +6603,8 @@
       <c r="CR15" s="0"/>
     </row>
     <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D16" s="0"/>
+      <c r="C16" s="38"/>
+      <c r="D16" s="17"/>
       <c r="E16" s="0"/>
       <c r="F16" s="0"/>
       <c r="G16" s="0"/>
@@ -6522,7 +6619,7 @@
       <c r="P16" s="0"/>
       <c r="Q16" s="0"/>
       <c r="R16" s="0"/>
-      <c r="S16" s="0"/>
+      <c r="S16" s="17"/>
       <c r="T16" s="0"/>
       <c r="U16" s="0"/>
       <c r="V16" s="0"/>
@@ -6602,7 +6699,8 @@
       <c r="CR16" s="0"/>
     </row>
     <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D17" s="0"/>
+      <c r="C17" s="38"/>
+      <c r="D17" s="17"/>
       <c r="E17" s="0"/>
       <c r="F17" s="0"/>
       <c r="G17" s="0"/>
@@ -6617,7 +6715,7 @@
       <c r="P17" s="0"/>
       <c r="Q17" s="0"/>
       <c r="R17" s="0"/>
-      <c r="S17" s="0"/>
+      <c r="S17" s="17"/>
       <c r="T17" s="0"/>
       <c r="U17" s="0"/>
       <c r="V17" s="0"/>
@@ -6697,22 +6795,35 @@
       <c r="CR17" s="0"/>
     </row>
     <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D18" s="0"/>
+      <c r="C18" s="38"/>
+      <c r="D18" s="17"/>
       <c r="E18" s="0"/>
-      <c r="F18" s="0"/>
-      <c r="G18" s="0"/>
-      <c r="H18" s="0"/>
+      <c r="F18" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="G18" s="6"/>
+      <c r="H18" s="7" t="n">
+        <v>29</v>
+      </c>
       <c r="I18" s="0"/>
       <c r="J18" s="0"/>
-      <c r="K18" s="0"/>
-      <c r="L18" s="0"/>
-      <c r="M18" s="0"/>
+      <c r="K18" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="L18" s="6"/>
+      <c r="M18" s="7" t="n">
+        <v>44</v>
+      </c>
       <c r="N18" s="0"/>
       <c r="O18" s="0"/>
-      <c r="P18" s="0"/>
-      <c r="Q18" s="0"/>
-      <c r="R18" s="0"/>
-      <c r="S18" s="0"/>
+      <c r="P18" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="Q18" s="6"/>
+      <c r="R18" s="7" t="n">
+        <v>59</v>
+      </c>
+      <c r="S18" s="17"/>
       <c r="T18" s="0"/>
       <c r="U18" s="0"/>
       <c r="V18" s="0"/>
@@ -6792,22 +6903,29 @@
       <c r="CR18" s="0"/>
     </row>
     <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D19" s="0"/>
-      <c r="E19" s="0"/>
-      <c r="F19" s="0"/>
-      <c r="G19" s="0"/>
-      <c r="H19" s="0"/>
-      <c r="I19" s="0"/>
-      <c r="J19" s="0"/>
-      <c r="K19" s="0"/>
-      <c r="L19" s="0"/>
-      <c r="M19" s="0"/>
-      <c r="N19" s="0"/>
-      <c r="O19" s="0"/>
-      <c r="P19" s="0"/>
-      <c r="Q19" s="0"/>
-      <c r="R19" s="0"/>
-      <c r="S19" s="0"/>
+      <c r="C19" s="38"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="G19" s="8"/>
+      <c r="H19" s="8"/>
+      <c r="I19" s="9"/>
+      <c r="J19" s="9"/>
+      <c r="K19" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="L19" s="8"/>
+      <c r="M19" s="8"/>
+      <c r="N19" s="9"/>
+      <c r="O19" s="9"/>
+      <c r="P19" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q19" s="8"/>
+      <c r="R19" s="8"/>
+      <c r="S19" s="19"/>
       <c r="T19" s="0"/>
       <c r="U19" s="0"/>
       <c r="V19" s="0"/>
@@ -6887,21 +7005,40 @@
       <c r="CR19" s="0"/>
     </row>
     <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C20" s="38"/>
       <c r="D20" s="0"/>
       <c r="E20" s="0"/>
-      <c r="F20" s="0"/>
-      <c r="G20" s="0"/>
-      <c r="H20" s="0"/>
+      <c r="F20" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="G20" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="13" t="n">
+        <v>0</v>
+      </c>
       <c r="I20" s="0"/>
       <c r="J20" s="0"/>
-      <c r="K20" s="0"/>
-      <c r="L20" s="0"/>
-      <c r="M20" s="0"/>
+      <c r="K20" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="L20" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="13" t="n">
+        <v>0</v>
+      </c>
       <c r="N20" s="0"/>
       <c r="O20" s="0"/>
-      <c r="P20" s="0"/>
-      <c r="Q20" s="0"/>
-      <c r="R20" s="0"/>
+      <c r="P20" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q20" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" s="13" t="n">
+        <v>0</v>
+      </c>
       <c r="S20" s="0"/>
       <c r="T20" s="0"/>
       <c r="U20" s="0"/>
@@ -6982,21 +7119,34 @@
       <c r="CR20" s="0"/>
     </row>
     <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C21" s="38"/>
       <c r="D21" s="0"/>
       <c r="E21" s="0"/>
-      <c r="F21" s="0"/>
-      <c r="G21" s="0"/>
-      <c r="H21" s="0"/>
+      <c r="F21" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="G21" s="6"/>
+      <c r="H21" s="15" t="n">
+        <v>29</v>
+      </c>
       <c r="I21" s="0"/>
       <c r="J21" s="0"/>
-      <c r="K21" s="0"/>
-      <c r="L21" s="0"/>
-      <c r="M21" s="0"/>
+      <c r="K21" s="14" t="n">
+        <v>29</v>
+      </c>
+      <c r="L21" s="6"/>
+      <c r="M21" s="15" t="n">
+        <v>44</v>
+      </c>
       <c r="N21" s="0"/>
-      <c r="O21" s="0"/>
-      <c r="P21" s="0"/>
-      <c r="Q21" s="0"/>
-      <c r="R21" s="0"/>
+      <c r="O21" s="39"/>
+      <c r="P21" s="14" t="n">
+        <v>44</v>
+      </c>
+      <c r="Q21" s="6"/>
+      <c r="R21" s="15" t="n">
+        <v>59</v>
+      </c>
       <c r="S21" s="0"/>
       <c r="T21" s="0"/>
       <c r="U21" s="0"/>
@@ -7077,6 +7227,7 @@
       <c r="CR21" s="0"/>
     </row>
     <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C22" s="38"/>
       <c r="D22" s="0"/>
       <c r="E22" s="0"/>
       <c r="F22" s="0"/>
@@ -7088,7 +7239,7 @@
       <c r="L22" s="0"/>
       <c r="M22" s="0"/>
       <c r="N22" s="0"/>
-      <c r="O22" s="0"/>
+      <c r="O22" s="40"/>
       <c r="P22" s="0"/>
       <c r="Q22" s="0"/>
       <c r="R22" s="0"/>
@@ -7172,6 +7323,7 @@
       <c r="CR22" s="0"/>
     </row>
     <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C23" s="38"/>
       <c r="D23" s="0"/>
       <c r="E23" s="0"/>
       <c r="F23" s="0"/>
@@ -7183,7 +7335,7 @@
       <c r="L23" s="0"/>
       <c r="M23" s="0"/>
       <c r="N23" s="0"/>
-      <c r="O23" s="0"/>
+      <c r="O23" s="40"/>
       <c r="P23" s="0"/>
       <c r="Q23" s="0"/>
       <c r="R23" s="0"/>
@@ -7267,18 +7419,27 @@
       <c r="CR23" s="0"/>
     </row>
     <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C24" s="38"/>
       <c r="D24" s="0"/>
       <c r="E24" s="0"/>
-      <c r="F24" s="0"/>
-      <c r="G24" s="0"/>
-      <c r="H24" s="0"/>
+      <c r="F24" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="G24" s="6"/>
+      <c r="H24" s="7" t="n">
+        <v>21</v>
+      </c>
       <c r="I24" s="0"/>
       <c r="J24" s="0"/>
-      <c r="K24" s="0"/>
-      <c r="L24" s="0"/>
-      <c r="M24" s="0"/>
+      <c r="K24" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="L24" s="6"/>
+      <c r="M24" s="7" t="n">
+        <v>35</v>
+      </c>
       <c r="N24" s="0"/>
-      <c r="O24" s="0"/>
+      <c r="O24" s="40"/>
       <c r="P24" s="0"/>
       <c r="Q24" s="0"/>
       <c r="R24" s="0"/>
@@ -7362,18 +7523,23 @@
       <c r="CR24" s="0"/>
     </row>
     <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D25" s="0"/>
-      <c r="E25" s="0"/>
-      <c r="F25" s="0"/>
-      <c r="G25" s="0"/>
-      <c r="H25" s="0"/>
-      <c r="I25" s="0"/>
-      <c r="J25" s="0"/>
-      <c r="K25" s="0"/>
-      <c r="L25" s="0"/>
-      <c r="M25" s="0"/>
-      <c r="N25" s="0"/>
-      <c r="O25" s="0"/>
+      <c r="C25" s="38"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="9"/>
+      <c r="F25" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="G25" s="8"/>
+      <c r="H25" s="8"/>
+      <c r="I25" s="9"/>
+      <c r="J25" s="9"/>
+      <c r="K25" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="L25" s="8"/>
+      <c r="M25" s="8"/>
+      <c r="N25" s="9"/>
+      <c r="O25" s="40"/>
       <c r="P25" s="0"/>
       <c r="Q25" s="0"/>
       <c r="R25" s="0"/>
@@ -7459,14 +7625,26 @@
     <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D26" s="0"/>
       <c r="E26" s="0"/>
-      <c r="F26" s="0"/>
-      <c r="G26" s="0"/>
-      <c r="H26" s="0"/>
+      <c r="F26" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="G26" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="H26" s="13" t="n">
+        <v>0</v>
+      </c>
       <c r="I26" s="0"/>
       <c r="J26" s="0"/>
-      <c r="K26" s="0"/>
-      <c r="L26" s="0"/>
-      <c r="M26" s="0"/>
+      <c r="K26" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="L26" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="M26" s="13" t="n">
+        <v>9</v>
+      </c>
       <c r="N26" s="0"/>
       <c r="O26" s="0"/>
       <c r="P26" s="0"/>
@@ -7554,14 +7732,22 @@
     <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D27" s="0"/>
       <c r="E27" s="0"/>
-      <c r="F27" s="0"/>
-      <c r="G27" s="0"/>
-      <c r="H27" s="0"/>
+      <c r="F27" s="14" t="n">
+        <v>24</v>
+      </c>
+      <c r="G27" s="6"/>
+      <c r="H27" s="15" t="n">
+        <v>30</v>
+      </c>
       <c r="I27" s="0"/>
       <c r="J27" s="0"/>
-      <c r="K27" s="0"/>
-      <c r="L27" s="0"/>
-      <c r="M27" s="0"/>
+      <c r="K27" s="14" t="n">
+        <v>30</v>
+      </c>
+      <c r="L27" s="6"/>
+      <c r="M27" s="15" t="n">
+        <v>44</v>
+      </c>
       <c r="N27" s="0"/>
       <c r="O27" s="0"/>
       <c r="P27" s="0"/>
@@ -7860,11 +8046,19 @@
     </row>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="10">
     <mergeCell ref="B1:D1"/>
     <mergeCell ref="A13:C13"/>
+    <mergeCell ref="F13:H13"/>
+    <mergeCell ref="K13:M13"/>
+    <mergeCell ref="U13:W13"/>
+    <mergeCell ref="F19:H19"/>
+    <mergeCell ref="K19:M19"/>
+    <mergeCell ref="P19:R19"/>
+    <mergeCell ref="F25:H25"/>
+    <mergeCell ref="K25:M25"/>
   </mergeCells>
-  <conditionalFormatting sqref="B14">
+  <conditionalFormatting sqref="B14 G14 G20 G26 L14 L20 L26 Q20 V14">
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>0</formula>
     </cfRule>
@@ -7890,7 +8084,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="1" style="34" width="3.86"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="3.86"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="34" width="3.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="34" width="6.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="34" width="4.47"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="64" min="13" style="34" width="3.86"/>
   </cols>
   <sheetData>
@@ -8184,24 +8378,32 @@
       <c r="O13" s="0"/>
     </row>
     <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="5"/>
+      <c r="A14" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="B14" s="6"/>
       <c r="C14" s="7"/>
       <c r="D14" s="0"/>
       <c r="E14" s="0"/>
-      <c r="F14" s="0"/>
-      <c r="G14" s="0"/>
-      <c r="H14" s="0"/>
+      <c r="F14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="6"/>
+      <c r="H14" s="7"/>
       <c r="I14" s="0"/>
       <c r="J14" s="0"/>
-      <c r="K14" s="0"/>
-      <c r="L14" s="0"/>
-      <c r="M14" s="0"/>
+      <c r="K14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="6"/>
+      <c r="M14" s="7"/>
       <c r="N14" s="0"/>
       <c r="O14" s="0"/>
-      <c r="P14" s="0"/>
-      <c r="Q14" s="0"/>
-      <c r="R14" s="0"/>
+      <c r="P14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="6"/>
+      <c r="R14" s="7"/>
       <c r="S14" s="0"/>
       <c r="T14" s="0"/>
       <c r="U14" s="0"/>
@@ -8209,9 +8411,11 @@
       <c r="W14" s="0"/>
       <c r="X14" s="0"/>
       <c r="Y14" s="0"/>
-      <c r="Z14" s="0"/>
-      <c r="AA14" s="0"/>
-      <c r="AB14" s="0"/>
+      <c r="Z14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="6"/>
+      <c r="AB14" s="7"/>
       <c r="AC14" s="0"/>
       <c r="AD14" s="0"/>
     </row>
@@ -8221,31 +8425,39 @@
       </c>
       <c r="B15" s="8"/>
       <c r="C15" s="8"/>
-      <c r="D15" s="0"/>
-      <c r="E15" s="0"/>
-      <c r="F15" s="0"/>
-      <c r="G15" s="0"/>
-      <c r="H15" s="0"/>
-      <c r="I15" s="0"/>
-      <c r="J15" s="0"/>
-      <c r="K15" s="0"/>
-      <c r="L15" s="0"/>
-      <c r="M15" s="0"/>
-      <c r="N15" s="0"/>
-      <c r="O15" s="0"/>
-      <c r="P15" s="0"/>
-      <c r="Q15" s="0"/>
-      <c r="R15" s="0"/>
-      <c r="S15" s="0"/>
-      <c r="T15" s="0"/>
-      <c r="U15" s="0"/>
-      <c r="V15" s="0"/>
-      <c r="W15" s="0"/>
-      <c r="X15" s="0"/>
-      <c r="Y15" s="0"/>
-      <c r="Z15" s="0"/>
-      <c r="AA15" s="0"/>
-      <c r="AB15" s="0"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="G15" s="8"/>
+      <c r="H15" s="8"/>
+      <c r="I15" s="9"/>
+      <c r="J15" s="9"/>
+      <c r="K15" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="L15" s="8"/>
+      <c r="M15" s="8"/>
+      <c r="N15" s="9"/>
+      <c r="O15" s="9"/>
+      <c r="P15" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q15" s="8"/>
+      <c r="R15" s="8"/>
+      <c r="S15" s="9"/>
+      <c r="T15" s="9"/>
+      <c r="U15" s="9"/>
+      <c r="V15" s="9"/>
+      <c r="W15" s="9"/>
+      <c r="X15" s="9"/>
+      <c r="Y15" s="9"/>
+      <c r="Z15" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA15" s="8"/>
+      <c r="AB15" s="8"/>
       <c r="AC15" s="0"/>
       <c r="AD15" s="0"/>
     </row>
@@ -8255,19 +8467,19 @@
       <c r="C16" s="13"/>
       <c r="D16" s="0"/>
       <c r="E16" s="0"/>
-      <c r="F16" s="0"/>
-      <c r="G16" s="0"/>
-      <c r="H16" s="0"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="12"/>
+      <c r="H16" s="13"/>
       <c r="I16" s="0"/>
       <c r="J16" s="0"/>
-      <c r="K16" s="0"/>
-      <c r="L16" s="0"/>
-      <c r="M16" s="0"/>
+      <c r="K16" s="11"/>
+      <c r="L16" s="12"/>
+      <c r="M16" s="13"/>
       <c r="N16" s="0"/>
       <c r="O16" s="0"/>
-      <c r="P16" s="0"/>
-      <c r="Q16" s="0"/>
-      <c r="R16" s="0"/>
+      <c r="P16" s="11"/>
+      <c r="Q16" s="12"/>
+      <c r="R16" s="13"/>
       <c r="S16" s="0"/>
       <c r="T16" s="0"/>
       <c r="U16" s="0"/>
@@ -8275,9 +8487,9 @@
       <c r="W16" s="0"/>
       <c r="X16" s="0"/>
       <c r="Y16" s="0"/>
-      <c r="Z16" s="0"/>
-      <c r="AA16" s="0"/>
-      <c r="AB16" s="0"/>
+      <c r="Z16" s="11"/>
+      <c r="AA16" s="12"/>
+      <c r="AB16" s="13"/>
       <c r="AC16" s="0"/>
       <c r="AD16" s="0"/>
     </row>
@@ -8285,36 +8497,37 @@
       <c r="A17" s="14"/>
       <c r="B17" s="6"/>
       <c r="C17" s="15"/>
-      <c r="D17" s="0"/>
+      <c r="D17" s="16"/>
       <c r="E17" s="0"/>
-      <c r="F17" s="0"/>
-      <c r="G17" s="0"/>
-      <c r="H17" s="0"/>
+      <c r="F17" s="14"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="15"/>
       <c r="I17" s="0"/>
       <c r="J17" s="0"/>
-      <c r="K17" s="0"/>
-      <c r="L17" s="0"/>
-      <c r="M17" s="0"/>
+      <c r="K17" s="14"/>
+      <c r="L17" s="6"/>
+      <c r="M17" s="15"/>
       <c r="N17" s="0"/>
       <c r="O17" s="0"/>
-      <c r="P17" s="0"/>
-      <c r="Q17" s="0"/>
-      <c r="R17" s="0"/>
+      <c r="P17" s="14"/>
+      <c r="Q17" s="6"/>
+      <c r="R17" s="15"/>
       <c r="S17" s="0"/>
       <c r="T17" s="0"/>
       <c r="U17" s="0"/>
       <c r="V17" s="0"/>
       <c r="W17" s="0"/>
-      <c r="X17" s="0"/>
+      <c r="X17" s="17"/>
       <c r="Y17" s="0"/>
-      <c r="Z17" s="0"/>
-      <c r="AA17" s="0"/>
-      <c r="AB17" s="0"/>
+      <c r="Z17" s="14"/>
+      <c r="AA17" s="6"/>
+      <c r="AB17" s="15"/>
       <c r="AC17" s="0"/>
       <c r="AD17" s="0"/>
     </row>
     <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D18" s="0"/>
+      <c r="C18" s="38"/>
+      <c r="D18" s="17"/>
       <c r="E18" s="0"/>
       <c r="F18" s="0"/>
       <c r="G18" s="0"/>
@@ -8334,7 +8547,7 @@
       <c r="U18" s="0"/>
       <c r="V18" s="0"/>
       <c r="W18" s="0"/>
-      <c r="X18" s="0"/>
+      <c r="X18" s="17"/>
       <c r="Y18" s="0"/>
       <c r="Z18" s="0"/>
       <c r="AA18" s="0"/>
@@ -8343,7 +8556,8 @@
       <c r="AD18" s="0"/>
     </row>
     <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D19" s="0"/>
+      <c r="C19" s="38"/>
+      <c r="D19" s="17"/>
       <c r="E19" s="0"/>
       <c r="F19" s="0"/>
       <c r="G19" s="0"/>
@@ -8363,7 +8577,7 @@
       <c r="U19" s="0"/>
       <c r="V19" s="0"/>
       <c r="W19" s="0"/>
-      <c r="X19" s="0"/>
+      <c r="X19" s="17"/>
       <c r="Y19" s="0"/>
       <c r="Z19" s="0"/>
       <c r="AA19" s="0"/>
@@ -8372,27 +8586,34 @@
       <c r="AD19" s="0"/>
     </row>
     <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D20" s="0"/>
+      <c r="C20" s="38"/>
+      <c r="D20" s="17"/>
       <c r="E20" s="0"/>
-      <c r="F20" s="0"/>
-      <c r="G20" s="0"/>
-      <c r="H20" s="0"/>
+      <c r="F20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="6"/>
+      <c r="H20" s="7"/>
       <c r="I20" s="0"/>
       <c r="J20" s="0"/>
-      <c r="K20" s="0"/>
-      <c r="L20" s="0"/>
-      <c r="M20" s="0"/>
+      <c r="K20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="6"/>
+      <c r="M20" s="7"/>
       <c r="N20" s="0"/>
       <c r="O20" s="0"/>
-      <c r="P20" s="0"/>
-      <c r="Q20" s="0"/>
-      <c r="R20" s="0"/>
+      <c r="P20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="6"/>
+      <c r="R20" s="7"/>
       <c r="S20" s="0"/>
       <c r="T20" s="0"/>
       <c r="U20" s="0"/>
       <c r="V20" s="0"/>
       <c r="W20" s="0"/>
-      <c r="X20" s="0"/>
+      <c r="X20" s="17"/>
       <c r="Y20" s="0"/>
       <c r="Z20" s="0"/>
       <c r="AA20" s="0"/>
@@ -8401,27 +8622,34 @@
       <c r="AD20" s="0"/>
     </row>
     <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D21" s="0"/>
-      <c r="E21" s="0"/>
-      <c r="F21" s="0"/>
-      <c r="G21" s="0"/>
-      <c r="H21" s="0"/>
-      <c r="I21" s="0"/>
-      <c r="J21" s="0"/>
-      <c r="K21" s="0"/>
-      <c r="L21" s="0"/>
-      <c r="M21" s="0"/>
-      <c r="N21" s="0"/>
-      <c r="O21" s="0"/>
-      <c r="P21" s="0"/>
-      <c r="Q21" s="0"/>
-      <c r="R21" s="0"/>
-      <c r="S21" s="0"/>
-      <c r="T21" s="0"/>
-      <c r="U21" s="0"/>
-      <c r="V21" s="0"/>
-      <c r="W21" s="0"/>
-      <c r="X21" s="0"/>
+      <c r="C21" s="38"/>
+      <c r="D21" s="17"/>
+      <c r="E21" s="9"/>
+      <c r="F21" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="G21" s="8"/>
+      <c r="H21" s="8"/>
+      <c r="I21" s="9"/>
+      <c r="J21" s="9"/>
+      <c r="K21" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="L21" s="8"/>
+      <c r="M21" s="8"/>
+      <c r="N21" s="9"/>
+      <c r="O21" s="9"/>
+      <c r="P21" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q21" s="8"/>
+      <c r="R21" s="8"/>
+      <c r="S21" s="9"/>
+      <c r="T21" s="9"/>
+      <c r="U21" s="9"/>
+      <c r="V21" s="9"/>
+      <c r="W21" s="9"/>
+      <c r="X21" s="19"/>
       <c r="Y21" s="0"/>
       <c r="Z21" s="0"/>
       <c r="AA21" s="0"/>
@@ -8430,21 +8658,22 @@
       <c r="AD21" s="0"/>
     </row>
     <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C22" s="38"/>
       <c r="D22" s="0"/>
       <c r="E22" s="0"/>
-      <c r="F22" s="0"/>
-      <c r="G22" s="0"/>
-      <c r="H22" s="0"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="12"/>
+      <c r="H22" s="13"/>
       <c r="I22" s="0"/>
       <c r="J22" s="0"/>
-      <c r="K22" s="0"/>
-      <c r="L22" s="0"/>
-      <c r="M22" s="0"/>
+      <c r="K22" s="11"/>
+      <c r="L22" s="12"/>
+      <c r="M22" s="13"/>
       <c r="N22" s="0"/>
-      <c r="O22" s="0"/>
-      <c r="P22" s="0"/>
-      <c r="Q22" s="0"/>
-      <c r="R22" s="0"/>
+      <c r="O22" s="9"/>
+      <c r="P22" s="11"/>
+      <c r="Q22" s="12"/>
+      <c r="R22" s="13"/>
       <c r="S22" s="0"/>
       <c r="T22" s="0"/>
       <c r="U22" s="0"/>
@@ -8459,21 +8688,22 @@
       <c r="AD22" s="0"/>
     </row>
     <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C23" s="38"/>
       <c r="D23" s="0"/>
       <c r="E23" s="0"/>
-      <c r="F23" s="0"/>
-      <c r="G23" s="0"/>
-      <c r="H23" s="0"/>
+      <c r="F23" s="14"/>
+      <c r="G23" s="6"/>
+      <c r="H23" s="15"/>
       <c r="I23" s="0"/>
       <c r="J23" s="0"/>
-      <c r="K23" s="0"/>
-      <c r="L23" s="0"/>
-      <c r="M23" s="0"/>
-      <c r="N23" s="0"/>
+      <c r="K23" s="14"/>
+      <c r="L23" s="6"/>
+      <c r="M23" s="15"/>
+      <c r="N23" s="17"/>
       <c r="O23" s="0"/>
-      <c r="P23" s="0"/>
-      <c r="Q23" s="0"/>
-      <c r="R23" s="0"/>
+      <c r="P23" s="14"/>
+      <c r="Q23" s="6"/>
+      <c r="R23" s="15"/>
       <c r="S23" s="0"/>
       <c r="T23" s="0"/>
       <c r="U23" s="0"/>
@@ -8488,6 +8718,7 @@
       <c r="AD23" s="0"/>
     </row>
     <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C24" s="38"/>
       <c r="D24" s="0"/>
       <c r="E24" s="0"/>
       <c r="F24" s="0"/>
@@ -8498,7 +8729,7 @@
       <c r="K24" s="0"/>
       <c r="L24" s="0"/>
       <c r="M24" s="0"/>
-      <c r="N24" s="0"/>
+      <c r="N24" s="17"/>
       <c r="O24" s="0"/>
       <c r="P24" s="0"/>
       <c r="Q24" s="0"/>
@@ -8517,6 +8748,7 @@
       <c r="AD24" s="0"/>
     </row>
     <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C25" s="38"/>
       <c r="D25" s="0"/>
       <c r="E25" s="0"/>
       <c r="F25" s="0"/>
@@ -8527,7 +8759,7 @@
       <c r="K25" s="0"/>
       <c r="L25" s="0"/>
       <c r="M25" s="0"/>
-      <c r="N25" s="0"/>
+      <c r="N25" s="17"/>
       <c r="O25" s="0"/>
       <c r="P25" s="0"/>
       <c r="Q25" s="0"/>
@@ -8546,17 +8778,22 @@
       <c r="AD25" s="0"/>
     </row>
     <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C26" s="38"/>
       <c r="D26" s="0"/>
       <c r="E26" s="0"/>
-      <c r="F26" s="0"/>
-      <c r="G26" s="0"/>
-      <c r="H26" s="0"/>
+      <c r="F26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="6"/>
+      <c r="H26" s="7"/>
       <c r="I26" s="0"/>
       <c r="J26" s="0"/>
-      <c r="K26" s="0"/>
-      <c r="L26" s="0"/>
-      <c r="M26" s="0"/>
-      <c r="N26" s="0"/>
+      <c r="K26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" s="6"/>
+      <c r="M26" s="7"/>
+      <c r="N26" s="17"/>
       <c r="O26" s="0"/>
       <c r="P26" s="0"/>
       <c r="Q26" s="0"/>
@@ -8575,17 +8812,22 @@
       <c r="AD26" s="0"/>
     </row>
     <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D27" s="0"/>
-      <c r="E27" s="0"/>
-      <c r="F27" s="0"/>
-      <c r="G27" s="0"/>
-      <c r="H27" s="0"/>
-      <c r="I27" s="0"/>
-      <c r="J27" s="0"/>
-      <c r="K27" s="0"/>
-      <c r="L27" s="0"/>
-      <c r="M27" s="0"/>
-      <c r="N27" s="0"/>
+      <c r="C27" s="38"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="9"/>
+      <c r="F27" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="G27" s="8"/>
+      <c r="H27" s="8"/>
+      <c r="I27" s="9"/>
+      <c r="J27" s="9"/>
+      <c r="K27" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="L27" s="8"/>
+      <c r="M27" s="8"/>
+      <c r="N27" s="19"/>
       <c r="O27" s="0"/>
       <c r="P27" s="0"/>
       <c r="Q27" s="0"/>
@@ -8606,14 +8848,14 @@
     <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D28" s="0"/>
       <c r="E28" s="0"/>
-      <c r="F28" s="0"/>
-      <c r="G28" s="0"/>
-      <c r="H28" s="0"/>
+      <c r="F28" s="11"/>
+      <c r="G28" s="12"/>
+      <c r="H28" s="13"/>
       <c r="I28" s="0"/>
       <c r="J28" s="0"/>
-      <c r="K28" s="0"/>
-      <c r="L28" s="0"/>
-      <c r="M28" s="0"/>
+      <c r="K28" s="11"/>
+      <c r="L28" s="12"/>
+      <c r="M28" s="13"/>
       <c r="N28" s="0"/>
       <c r="O28" s="0"/>
       <c r="P28" s="0"/>
@@ -8635,14 +8877,14 @@
     <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D29" s="0"/>
       <c r="E29" s="0"/>
-      <c r="F29" s="0"/>
-      <c r="G29" s="0"/>
-      <c r="H29" s="0"/>
+      <c r="F29" s="14"/>
+      <c r="G29" s="6"/>
+      <c r="H29" s="15"/>
       <c r="I29" s="0"/>
       <c r="J29" s="0"/>
-      <c r="K29" s="0"/>
-      <c r="L29" s="0"/>
-      <c r="M29" s="0"/>
+      <c r="K29" s="14"/>
+      <c r="L29" s="6"/>
+      <c r="M29" s="15"/>
       <c r="N29" s="0"/>
       <c r="O29" s="0"/>
       <c r="P29" s="0"/>
@@ -8749,12 +8991,26 @@
       <c r="AD32" s="0"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="11">
     <mergeCell ref="B1:D1"/>
     <mergeCell ref="A15:C15"/>
+    <mergeCell ref="F15:H15"/>
+    <mergeCell ref="K15:M15"/>
+    <mergeCell ref="P15:R15"/>
+    <mergeCell ref="Z15:AB15"/>
+    <mergeCell ref="F21:H21"/>
+    <mergeCell ref="K21:M21"/>
+    <mergeCell ref="P21:R21"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="K27:M27"/>
   </mergeCells>
-  <conditionalFormatting sqref="B16">
+  <conditionalFormatting sqref="B16 G16 G22 G28">
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L16 L22 L28 Q16 Q22 AB16">
+    <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8776,7 +9032,7 @@
   <dimension ref="A1:G1048576"/>
   <sheetFormatPr defaultColWidth="10.6796875" defaultRowHeight="12.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="38" width="8.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="41" width="8.84"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="34" width="23.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="34" width="23.96"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="34" width="11.53"/>
@@ -8784,279 +9040,279 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="41" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="39" t="s">
+      <c r="B1" s="42" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="40" t="n">
+      <c r="A2" s="43" t="n">
         <v>45297</v>
       </c>
-      <c r="B2" s="38" t="s">
+      <c r="B2" s="41" t="s">
         <v>44</v>
       </c>
-      <c r="C2" s="39" t="s">
+      <c r="C2" s="42" t="s">
         <v>45</v>
       </c>
-      <c r="E2" s="39" t="s">
+      <c r="E2" s="42" t="s">
         <v>46</v>
       </c>
-      <c r="F2" s="41" t="n">
+      <c r="F2" s="44" t="n">
         <v>45413</v>
       </c>
-      <c r="G2" s="41" t="n">
+      <c r="G2" s="44" t="n">
         <v>45414</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="40" t="n">
+      <c r="A3" s="43" t="n">
         <v>45359</v>
       </c>
-      <c r="B3" s="38" t="s">
+      <c r="B3" s="41" t="s">
         <v>47</v>
       </c>
-      <c r="C3" s="39" t="s">
+      <c r="C3" s="42" t="s">
         <v>48</v>
       </c>
-      <c r="D3" s="39" t="s">
+      <c r="D3" s="42" t="s">
         <v>49</v>
       </c>
-      <c r="E3" s="39" t="s">
+      <c r="E3" s="42" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="40" t="n">
+      <c r="A4" s="43" t="n">
         <v>45380</v>
       </c>
-      <c r="B4" s="38" t="s">
+      <c r="B4" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="C4" s="39" t="s">
+      <c r="C4" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="D4" s="39" t="s">
+      <c r="D4" s="42" t="s">
         <v>49</v>
       </c>
-      <c r="E4" s="39" t="s">
+      <c r="E4" s="42" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="40" t="n">
+      <c r="A5" s="43" t="n">
         <v>45383</v>
       </c>
-      <c r="B5" s="38" t="s">
+      <c r="B5" s="41" t="s">
         <v>54</v>
       </c>
-      <c r="C5" s="39" t="s">
+      <c r="C5" s="42" t="s">
         <v>55</v>
       </c>
-      <c r="D5" s="39" t="s">
+      <c r="D5" s="42" t="s">
         <v>49</v>
       </c>
-      <c r="E5" s="39" t="s">
+      <c r="E5" s="42" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="40" t="n">
+      <c r="A6" s="43" t="n">
         <v>45413</v>
       </c>
-      <c r="B6" s="38" t="s">
+      <c r="B6" s="41" t="s">
         <v>56</v>
       </c>
-      <c r="C6" s="39" t="s">
+      <c r="C6" s="42" t="s">
         <v>57</v>
       </c>
-      <c r="E6" s="39" t="s">
+      <c r="E6" s="42" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="40" t="n">
+      <c r="A7" s="43" t="n">
         <v>45421</v>
       </c>
-      <c r="B7" s="38" t="s">
+      <c r="B7" s="41" t="s">
         <v>58</v>
       </c>
-      <c r="C7" s="39" t="s">
+      <c r="C7" s="42" t="s">
         <v>59</v>
       </c>
-      <c r="D7" s="39" t="s">
+      <c r="D7" s="42" t="s">
         <v>60</v>
       </c>
-      <c r="E7" s="39" t="s">
+      <c r="E7" s="42" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="40" t="n">
+      <c r="A8" s="43" t="n">
         <v>45432</v>
       </c>
-      <c r="B8" s="38" t="s">
+      <c r="B8" s="41" t="s">
         <v>61</v>
       </c>
-      <c r="C8" s="39" t="s">
+      <c r="C8" s="42" t="s">
         <v>62</v>
       </c>
-      <c r="D8" s="39" t="s">
+      <c r="D8" s="42" t="s">
         <v>49</v>
       </c>
-      <c r="E8" s="39" t="s">
+      <c r="E8" s="42" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="40" t="n">
+      <c r="A9" s="43" t="n">
         <v>45442</v>
       </c>
-      <c r="B9" s="38" t="s">
+      <c r="B9" s="41" t="s">
         <v>63</v>
       </c>
-      <c r="C9" s="39" t="s">
+      <c r="C9" s="42" t="s">
         <v>64</v>
       </c>
-      <c r="D9" s="39" t="s">
+      <c r="D9" s="42" t="s">
         <v>60</v>
       </c>
-      <c r="E9" s="39" t="s">
+      <c r="E9" s="42" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="40" t="n">
+      <c r="A10" s="43" t="n">
         <v>45519</v>
       </c>
-      <c r="B10" s="38" t="s">
+      <c r="B10" s="41" t="s">
         <v>66</v>
       </c>
-      <c r="C10" s="39" t="s">
+      <c r="C10" s="42" t="s">
         <v>67</v>
       </c>
-      <c r="D10" s="39" t="s">
+      <c r="D10" s="42" t="s">
         <v>60</v>
       </c>
-      <c r="E10" s="39" t="s">
+      <c r="E10" s="42" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="40" t="n">
+      <c r="A11" s="43" t="n">
         <v>45555</v>
       </c>
-      <c r="B11" s="38" t="s">
+      <c r="B11" s="41" t="s">
         <v>69</v>
       </c>
-      <c r="C11" s="39" t="s">
+      <c r="C11" s="42" t="s">
         <v>70</v>
       </c>
-      <c r="D11" s="39" t="s">
+      <c r="D11" s="42" t="s">
         <v>49</v>
       </c>
-      <c r="E11" s="39" t="s">
+      <c r="E11" s="42" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="40" t="n">
+      <c r="A12" s="43" t="n">
         <v>45568</v>
       </c>
-      <c r="B12" s="38" t="s">
+      <c r="B12" s="41" t="s">
         <v>72</v>
       </c>
-      <c r="C12" s="39" t="s">
+      <c r="C12" s="42" t="s">
         <v>73</v>
       </c>
-      <c r="D12" s="39" t="s">
+      <c r="D12" s="42" t="s">
         <v>60</v>
       </c>
-      <c r="E12" s="39" t="s">
+      <c r="E12" s="42" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="40" t="n">
+      <c r="A13" s="43" t="n">
         <v>45596</v>
       </c>
-      <c r="B13" s="38" t="s">
+      <c r="B13" s="41" t="s">
         <v>74</v>
       </c>
-      <c r="C13" s="39" t="s">
+      <c r="C13" s="42" t="s">
         <v>75</v>
       </c>
-      <c r="D13" s="39" t="s">
+      <c r="D13" s="42" t="s">
         <v>60</v>
       </c>
-      <c r="E13" s="38" t="s">
+      <c r="E13" s="41" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="41" t="n">
+      <c r="A14" s="44" t="n">
         <v>45597</v>
       </c>
-      <c r="B14" s="38" t="s">
+      <c r="B14" s="41" t="s">
         <v>77</v>
       </c>
-      <c r="C14" s="39" t="s">
+      <c r="C14" s="42" t="s">
         <v>75</v>
       </c>
-      <c r="D14" s="39" t="s">
+      <c r="D14" s="42" t="s">
         <v>49</v>
       </c>
-      <c r="E14" s="39" t="s">
+      <c r="E14" s="42" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="41" t="n">
+      <c r="A15" s="44" t="n">
         <v>45616</v>
       </c>
-      <c r="B15" s="38" t="s">
+      <c r="B15" s="41" t="s">
         <v>79</v>
       </c>
-      <c r="C15" s="39" t="s">
+      <c r="C15" s="42" t="s">
         <v>80</v>
       </c>
-      <c r="E15" s="39" t="s">
+      <c r="E15" s="42" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="41" t="n">
+      <c r="A16" s="44" t="n">
         <v>45651</v>
       </c>
-      <c r="B16" s="38" t="s">
+      <c r="B16" s="41" t="s">
         <v>82</v>
       </c>
-      <c r="C16" s="39" t="s">
+      <c r="C16" s="42" t="s">
         <v>83</v>
       </c>
-      <c r="D16" s="39" t="s">
+      <c r="D16" s="42" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="41" t="n">
+      <c r="A17" s="44" t="n">
         <v>45652</v>
       </c>
-      <c r="B17" s="38" t="s">
+      <c r="B17" s="41" t="s">
         <v>84</v>
       </c>
-      <c r="C17" s="39" t="s">
+      <c r="C17" s="42" t="s">
         <v>83</v>
       </c>
-      <c r="D17" s="39" t="s">
+      <c r="D17" s="42" t="s">
         <v>60</v>
       </c>
-      <c r="E17" s="39" t="s">
+      <c r="E17" s="42" t="s">
         <v>53</v>
       </c>
-      <c r="F17" s="39" t="s">
+      <c r="F17" s="42" t="s">
         <v>12</v>
       </c>
     </row>

--- a/Übungen/Netzplan_Übung.xlsx
+++ b/Übungen/Netzplan_Übung.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="89">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -153,6 +153,15 @@
   </si>
   <si>
     <t xml:space="preserve">Auftragegeberpräsi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K%</t>
   </si>
   <si>
     <t xml:space="preserve">Datum</t>
@@ -288,13 +297,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="dd/mm/yy"/>
     <numFmt numFmtId="166" formatCode="@"/>
-    <numFmt numFmtId="167" formatCode="[$-F800]dddd&quot;, &quot;mmmm\ dd&quot;, &quot;yyyy"/>
+    <numFmt numFmtId="167" formatCode="0\ %"/>
+    <numFmt numFmtId="168" formatCode="[$-F800]dddd&quot;, &quot;mmmm\ dd&quot;, &quot;yyyy"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -370,6 +380,12 @@
       <sz val="9"/>
       <name val="Alegreya Sans"/>
       <family val="3"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <charset val="1"/>
     </font>
   </fonts>
@@ -617,7 +633,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="60">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -810,6 +826,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="167" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -838,7 +858,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1017,7 +1037,105 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>250200</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>21240</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>243360</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>147600</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="Form 2"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1609200" y="676080"/>
+          <a:ext cx="6515640" cy="126360"/>
+        </a:xfrm>
+        <a:prstGeom prst="leftRightArrow">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 77273"/>
+            <a:gd name="adj2" fmla="val 237879"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="729fcf"/>
+        </a:solidFill>
+        <a:ln w="0">
+          <a:solidFill>
+            <a:srgbClr val="3465a4"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>360</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>10440</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>51</xdr:col>
+      <xdr:colOff>14400</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>136800</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="Form 3"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6523200" y="1312920"/>
+          <a:ext cx="7351920" cy="126360"/>
+        </a:xfrm>
+        <a:prstGeom prst="leftRightArrow">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 77273"/>
+            <a:gd name="adj2" fmla="val 268410"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="729fcf"/>
+        </a:solidFill>
+        <a:ln w="0">
+          <a:solidFill>
+            <a:srgbClr val="3465a4"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4111,7 +4229,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:BQ29"/>
+  <dimension ref="A1:BQ31"/>
   <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="64" min="1" style="3" width="3.86"/>
@@ -4348,49 +4466,74 @@
       <c r="BJ2" s="10"/>
     </row>
     <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="44" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="44"/>
-      <c r="D3" s="44"/>
-      <c r="E3" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="J3" s="10"/>
-      <c r="L3" s="10"/>
-      <c r="M3" s="10"/>
-      <c r="P3" s="42"/>
-      <c r="Q3" s="42"/>
-      <c r="R3" s="42"/>
-      <c r="S3" s="10"/>
-      <c r="T3" s="10"/>
-      <c r="U3" s="42"/>
-      <c r="V3" s="42"/>
-      <c r="W3" s="42"/>
-      <c r="X3" s="43"/>
-      <c r="Z3" s="10"/>
-      <c r="AA3" s="10"/>
-      <c r="AG3" s="10"/>
-      <c r="AH3" s="10"/>
-      <c r="AL3" s="5"/>
-      <c r="AM3" s="6"/>
-      <c r="AN3" s="10"/>
-      <c r="AO3" s="10"/>
-      <c r="AU3" s="10"/>
-      <c r="AV3" s="10"/>
-      <c r="AW3" s="5"/>
-      <c r="BB3" s="10"/>
-      <c r="BC3" s="10"/>
-      <c r="BG3" s="5"/>
-      <c r="BI3" s="10"/>
-      <c r="BJ3" s="10"/>
+      <c r="A3" s="0"/>
+      <c r="B3" s="0"/>
+      <c r="C3" s="0"/>
+      <c r="D3" s="0"/>
+      <c r="E3" s="0"/>
+      <c r="F3" s="0"/>
+      <c r="G3" s="0"/>
+      <c r="H3" s="0"/>
+      <c r="I3" s="0"/>
+      <c r="J3" s="0"/>
+      <c r="K3" s="0"/>
+      <c r="L3" s="0"/>
+      <c r="M3" s="0"/>
+      <c r="N3" s="0"/>
+      <c r="O3" s="0"/>
+      <c r="P3" s="0"/>
+      <c r="Q3" s="0"/>
+      <c r="R3" s="0"/>
+      <c r="S3" s="0"/>
+      <c r="T3" s="0"/>
+      <c r="U3" s="0"/>
+      <c r="V3" s="0"/>
+      <c r="W3" s="0"/>
+      <c r="X3" s="0"/>
+      <c r="Y3" s="0"/>
+      <c r="Z3" s="0"/>
+      <c r="AA3" s="0"/>
+      <c r="AB3" s="0"/>
+      <c r="AC3" s="0"/>
+      <c r="AD3" s="0"/>
+      <c r="AE3" s="0"/>
+      <c r="AF3" s="0"/>
+      <c r="AG3" s="0"/>
+      <c r="AH3" s="0"/>
+      <c r="AI3" s="0"/>
+      <c r="AJ3" s="0"/>
+      <c r="AK3" s="0"/>
+      <c r="AL3" s="0"/>
+      <c r="AM3" s="0"/>
+      <c r="AN3" s="0"/>
+      <c r="AO3" s="0"/>
+      <c r="AP3" s="0"/>
+      <c r="AQ3" s="0"/>
+      <c r="AR3" s="0"/>
+      <c r="AS3" s="0"/>
+      <c r="AT3" s="0"/>
+      <c r="AU3" s="0"/>
+      <c r="AV3" s="0"/>
+      <c r="AW3" s="0"/>
+      <c r="AX3" s="0"/>
+      <c r="AY3" s="0"/>
+      <c r="AZ3" s="0"/>
+      <c r="BA3" s="0"/>
+      <c r="BB3" s="0"/>
+      <c r="BC3" s="0"/>
+      <c r="BD3" s="0"/>
+      <c r="BE3" s="0"/>
+      <c r="BF3" s="0"/>
+      <c r="BG3" s="0"/>
+      <c r="BH3" s="0"/>
+      <c r="BI3" s="0"/>
+      <c r="BJ3" s="0"/>
+      <c r="BK3" s="0"/>
+      <c r="BL3" s="0"/>
     </row>
     <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B4" s="44" t="s">
         <v>3</v>
@@ -4431,27 +4574,30 @@
     </row>
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B5" s="44" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C5" s="44"/>
       <c r="D5" s="44"/>
       <c r="E5" s="7" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J5" s="10"/>
       <c r="L5" s="10"/>
       <c r="M5" s="10"/>
+      <c r="P5" s="42"/>
+      <c r="Q5" s="42"/>
+      <c r="R5" s="42"/>
       <c r="S5" s="10"/>
       <c r="T5" s="10"/>
-      <c r="Y5" s="42"/>
+      <c r="U5" s="42"/>
+      <c r="V5" s="42"/>
+      <c r="W5" s="42"/>
+      <c r="X5" s="43"/>
       <c r="Z5" s="10"/>
       <c r="AA5" s="10"/>
-      <c r="AB5" s="42"/>
-      <c r="AC5" s="42"/>
-      <c r="AD5" s="43"/>
       <c r="AG5" s="10"/>
       <c r="AH5" s="10"/>
       <c r="AL5" s="5"/>
@@ -4469,10 +4615,10 @@
     </row>
     <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B6" s="44" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C6" s="44"/>
       <c r="D6" s="44"/>
@@ -4506,70 +4652,96 @@
       <c r="BJ6" s="10"/>
     </row>
     <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" s="44" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7" s="44"/>
-      <c r="D7" s="44"/>
-      <c r="E7" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="J7" s="10"/>
-      <c r="L7" s="10"/>
-      <c r="M7" s="10"/>
-      <c r="S7" s="10"/>
-      <c r="T7" s="10"/>
-      <c r="Y7" s="42"/>
-      <c r="Z7" s="10"/>
-      <c r="AA7" s="10"/>
-      <c r="AB7" s="42"/>
-      <c r="AC7" s="42"/>
-      <c r="AD7" s="42"/>
-      <c r="AE7" s="43"/>
-      <c r="AG7" s="10"/>
-      <c r="AH7" s="10"/>
-      <c r="AL7" s="5"/>
-      <c r="AM7" s="6"/>
-      <c r="AN7" s="10"/>
-      <c r="AO7" s="10"/>
-      <c r="AU7" s="10"/>
-      <c r="AV7" s="10"/>
-      <c r="AW7" s="5"/>
-      <c r="BB7" s="10"/>
-      <c r="BC7" s="10"/>
-      <c r="BG7" s="5"/>
-      <c r="BI7" s="10"/>
-      <c r="BJ7" s="10"/>
+      <c r="A7" s="0"/>
+      <c r="B7" s="0"/>
+      <c r="C7" s="0"/>
+      <c r="D7" s="0"/>
+      <c r="E7" s="0"/>
+      <c r="F7" s="0"/>
+      <c r="G7" s="0"/>
+      <c r="H7" s="0"/>
+      <c r="I7" s="0"/>
+      <c r="J7" s="0"/>
+      <c r="K7" s="0"/>
+      <c r="L7" s="0"/>
+      <c r="M7" s="0"/>
+      <c r="N7" s="0"/>
+      <c r="O7" s="0"/>
+      <c r="P7" s="0"/>
+      <c r="Q7" s="0"/>
+      <c r="R7" s="0"/>
+      <c r="S7" s="0"/>
+      <c r="T7" s="0"/>
+      <c r="U7" s="0"/>
+      <c r="V7" s="0"/>
+      <c r="W7" s="0"/>
+      <c r="X7" s="0"/>
+      <c r="Y7" s="0"/>
+      <c r="Z7" s="0"/>
+      <c r="AA7" s="0"/>
+      <c r="AB7" s="0"/>
+      <c r="AC7" s="0"/>
+      <c r="AD7" s="0"/>
+      <c r="AE7" s="0"/>
+      <c r="AF7" s="0"/>
+      <c r="AG7" s="0"/>
+      <c r="AH7" s="0"/>
+      <c r="AI7" s="0"/>
+      <c r="AJ7" s="0"/>
+      <c r="AK7" s="0"/>
+      <c r="AL7" s="0"/>
+      <c r="AM7" s="0"/>
+      <c r="AN7" s="0"/>
+      <c r="AO7" s="0"/>
+      <c r="AP7" s="0"/>
+      <c r="AQ7" s="0"/>
+      <c r="AR7" s="0"/>
+      <c r="AS7" s="0"/>
+      <c r="AT7" s="0"/>
+      <c r="AU7" s="0"/>
+      <c r="AV7" s="0"/>
+      <c r="AW7" s="0"/>
+      <c r="AX7" s="0"/>
+      <c r="AY7" s="0"/>
+      <c r="AZ7" s="0"/>
+      <c r="BA7" s="0"/>
+      <c r="BB7" s="0"/>
+      <c r="BC7" s="0"/>
+      <c r="BD7" s="0"/>
+      <c r="BE7" s="0"/>
+      <c r="BF7" s="0"/>
+      <c r="BG7" s="0"/>
+      <c r="BH7" s="0"/>
+      <c r="BI7" s="0"/>
+      <c r="BJ7" s="0"/>
+      <c r="BK7" s="0"/>
+      <c r="BL7" s="0"/>
     </row>
     <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B8" s="44" t="s">
-        <v>2</v>
-      </c>
-      <c r="C8" s="44" t="s">
-        <v>12</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="C8" s="44"/>
       <c r="D8" s="44"/>
-      <c r="E8" s="45" t="n">
-        <v>3</v>
+      <c r="E8" s="7" t="n">
+        <v>4</v>
       </c>
       <c r="J8" s="10"/>
       <c r="L8" s="10"/>
       <c r="M8" s="10"/>
       <c r="S8" s="10"/>
       <c r="T8" s="10"/>
+      <c r="Y8" s="42"/>
       <c r="Z8" s="10"/>
       <c r="AA8" s="10"/>
-      <c r="AE8" s="42"/>
-      <c r="AF8" s="42"/>
+      <c r="AB8" s="42"/>
+      <c r="AC8" s="42"/>
+      <c r="AD8" s="43"/>
       <c r="AG8" s="10"/>
       <c r="AH8" s="10"/>
-      <c r="AI8" s="43"/>
       <c r="AL8" s="5"/>
       <c r="AM8" s="6"/>
       <c r="AN8" s="10"/>
@@ -4584,25 +4756,31 @@
       <c r="BJ8" s="10"/>
     </row>
     <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="46" t="s">
-        <v>42</v>
-      </c>
-      <c r="B9" s="46"/>
-      <c r="C9" s="46"/>
-      <c r="D9" s="46"/>
-      <c r="E9" s="46"/>
+      <c r="A9" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="44" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="44"/>
+      <c r="D9" s="44"/>
+      <c r="E9" s="7" t="n">
+        <v>5</v>
+      </c>
       <c r="J9" s="10"/>
       <c r="L9" s="10"/>
       <c r="M9" s="10"/>
       <c r="S9" s="10"/>
       <c r="T9" s="10"/>
+      <c r="Y9" s="42"/>
       <c r="Z9" s="10"/>
       <c r="AA9" s="10"/>
-      <c r="AE9" s="0"/>
-      <c r="AF9" s="0"/>
+      <c r="AB9" s="42"/>
+      <c r="AC9" s="42"/>
+      <c r="AD9" s="42"/>
+      <c r="AE9" s="43"/>
       <c r="AG9" s="10"/>
       <c r="AH9" s="10"/>
-      <c r="AI9" s="0"/>
       <c r="AL9" s="5"/>
       <c r="AM9" s="6"/>
       <c r="AN9" s="10"/>
@@ -4618,17 +4796,17 @@
     </row>
     <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B10" s="44" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C10" s="44" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D10" s="44"/>
-      <c r="E10" s="7" t="n">
-        <v>6</v>
+      <c r="E10" s="45" t="n">
+        <v>3</v>
       </c>
       <c r="J10" s="10"/>
       <c r="L10" s="10"/>
@@ -4637,21 +4815,15 @@
       <c r="T10" s="10"/>
       <c r="Z10" s="10"/>
       <c r="AA10" s="10"/>
-      <c r="AF10" s="0"/>
+      <c r="AE10" s="42"/>
+      <c r="AF10" s="42"/>
       <c r="AG10" s="10"/>
       <c r="AH10" s="10"/>
-      <c r="AI10" s="0"/>
-      <c r="AJ10" s="0"/>
-      <c r="AK10" s="42"/>
+      <c r="AI10" s="43"/>
       <c r="AL10" s="5"/>
       <c r="AM10" s="6"/>
       <c r="AN10" s="10"/>
       <c r="AO10" s="10"/>
-      <c r="AP10" s="42"/>
-      <c r="AQ10" s="43"/>
-      <c r="AR10" s="47"/>
-      <c r="AS10" s="47"/>
-      <c r="AT10" s="47"/>
       <c r="AU10" s="10"/>
       <c r="AV10" s="10"/>
       <c r="AW10" s="5"/>
@@ -4662,19 +4834,13 @@
       <c r="BJ10" s="10"/>
     </row>
     <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11" s="44" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" s="44" t="s">
-        <v>9</v>
-      </c>
-      <c r="D11" s="44"/>
-      <c r="E11" s="7" t="n">
-        <v>2</v>
-      </c>
+      <c r="A11" s="46" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11" s="46"/>
+      <c r="C11" s="46"/>
+      <c r="D11" s="46"/>
+      <c r="E11" s="46"/>
       <c r="J11" s="10"/>
       <c r="L11" s="10"/>
       <c r="M11" s="10"/>
@@ -4682,367 +4848,451 @@
       <c r="T11" s="10"/>
       <c r="Z11" s="10"/>
       <c r="AA11" s="10"/>
+      <c r="AE11" s="0"/>
+      <c r="AF11" s="0"/>
       <c r="AG11" s="10"/>
       <c r="AH11" s="10"/>
+      <c r="AI11" s="0"/>
       <c r="AL11" s="5"/>
       <c r="AM11" s="6"/>
       <c r="AN11" s="10"/>
       <c r="AO11" s="10"/>
-      <c r="AR11" s="0"/>
-      <c r="AS11" s="0"/>
       <c r="AU11" s="10"/>
       <c r="AV11" s="10"/>
       <c r="AW11" s="5"/>
-      <c r="AX11" s="42"/>
-      <c r="AY11" s="42"/>
       <c r="BB11" s="10"/>
       <c r="BC11" s="10"/>
       <c r="BG11" s="5"/>
       <c r="BI11" s="10"/>
       <c r="BJ11" s="10"/>
     </row>
-    <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" s="44" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="44" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" s="44"/>
+      <c r="E12" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="J12" s="10"/>
+      <c r="L12" s="10"/>
+      <c r="M12" s="10"/>
+      <c r="S12" s="10"/>
+      <c r="T12" s="10"/>
+      <c r="Z12" s="10"/>
+      <c r="AA12" s="10"/>
+      <c r="AF12" s="0"/>
+      <c r="AG12" s="10"/>
+      <c r="AH12" s="10"/>
+      <c r="AI12" s="0"/>
+      <c r="AJ12" s="0"/>
+      <c r="AK12" s="42"/>
+      <c r="AL12" s="5"/>
+      <c r="AM12" s="6"/>
+      <c r="AN12" s="10"/>
+      <c r="AO12" s="10"/>
+      <c r="AP12" s="42"/>
+      <c r="AQ12" s="43"/>
+      <c r="AR12" s="47"/>
+      <c r="AS12" s="47"/>
+      <c r="AT12" s="47"/>
+      <c r="AU12" s="10"/>
+      <c r="AV12" s="10"/>
+      <c r="AW12" s="5"/>
+      <c r="BB12" s="10"/>
+      <c r="BC12" s="10"/>
+      <c r="BG12" s="5"/>
+      <c r="BI12" s="10"/>
+      <c r="BJ12" s="10"/>
+    </row>
     <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="B13" s="14"/>
-      <c r="C13" s="15" t="n">
+      <c r="A13" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B13" s="44" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="44" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" s="44"/>
+      <c r="E13" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="J13" s="10"/>
+      <c r="L13" s="10"/>
+      <c r="M13" s="10"/>
+      <c r="S13" s="10"/>
+      <c r="T13" s="10"/>
+      <c r="Z13" s="10"/>
+      <c r="AA13" s="10"/>
+      <c r="AG13" s="10"/>
+      <c r="AH13" s="10"/>
+      <c r="AL13" s="5"/>
+      <c r="AM13" s="6"/>
+      <c r="AN13" s="10"/>
+      <c r="AO13" s="10"/>
+      <c r="AR13" s="0"/>
+      <c r="AS13" s="0"/>
+      <c r="AU13" s="10"/>
+      <c r="AV13" s="10"/>
+      <c r="AW13" s="5"/>
+      <c r="AX13" s="42"/>
+      <c r="AY13" s="42"/>
+      <c r="BB13" s="10"/>
+      <c r="BC13" s="10"/>
+      <c r="BG13" s="5"/>
+      <c r="BI13" s="10"/>
+      <c r="BJ13" s="10"/>
+    </row>
+    <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="B15" s="14"/>
+      <c r="C15" s="15" t="n">
         <v>6</v>
       </c>
-      <c r="F13" s="13" t="n">
+      <c r="F15" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="G13" s="14"/>
-      <c r="H13" s="15" t="n">
+      <c r="G15" s="14"/>
+      <c r="H15" s="15" t="n">
         <v>13</v>
       </c>
-      <c r="K13" s="13" t="n">
+      <c r="K15" s="13" t="n">
         <v>13</v>
       </c>
-      <c r="L13" s="14"/>
-      <c r="M13" s="15" t="n">
+      <c r="L15" s="14"/>
+      <c r="M15" s="15" t="n">
         <v>17</v>
       </c>
-      <c r="P13" s="13" t="n">
+      <c r="P15" s="13" t="n">
         <v>17</v>
       </c>
-      <c r="Q13" s="14"/>
-      <c r="R13" s="15" t="n">
+      <c r="Q15" s="14"/>
+      <c r="R15" s="15" t="n">
         <v>20</v>
       </c>
-      <c r="U13" s="13" t="n">
+      <c r="U15" s="13" t="n">
         <v>24</v>
       </c>
-      <c r="V13" s="14"/>
-      <c r="W13" s="15" t="n">
+      <c r="V15" s="14"/>
+      <c r="W15" s="15" t="n">
         <v>26</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="16" t="s">
+    <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="B14" s="16"/>
-      <c r="C14" s="16"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="16" t="s">
+      <c r="B16" s="16"/>
+      <c r="C16" s="16"/>
+      <c r="D16" s="17"/>
+      <c r="E16" s="17"/>
+      <c r="F16" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="G14" s="16"/>
-      <c r="H14" s="16"/>
-      <c r="I14" s="17"/>
-      <c r="J14" s="17"/>
-      <c r="K14" s="16" t="s">
+      <c r="G16" s="16"/>
+      <c r="H16" s="16"/>
+      <c r="I16" s="17"/>
+      <c r="J16" s="17"/>
+      <c r="K16" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="17"/>
-      <c r="O14" s="17"/>
-      <c r="P14" s="16" t="s">
+      <c r="L16" s="16"/>
+      <c r="M16" s="16"/>
+      <c r="N16" s="17"/>
+      <c r="O16" s="17"/>
+      <c r="P16" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="Q14" s="16"/>
-      <c r="R14" s="16"/>
-      <c r="S14" s="17"/>
-      <c r="T14" s="17"/>
-      <c r="U14" s="16" t="s">
+      <c r="Q16" s="16"/>
+      <c r="R16" s="16"/>
+      <c r="S16" s="17"/>
+      <c r="T16" s="17"/>
+      <c r="U16" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="V14" s="16"/>
-      <c r="W14" s="16"/>
-    </row>
-    <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="19" t="n">
+      <c r="V16" s="16"/>
+      <c r="W16" s="16"/>
+    </row>
+    <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="B15" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="19" t="n">
+      <c r="B17" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="19" t="n">
         <v>7</v>
       </c>
-      <c r="G15" s="20" t="n">
+      <c r="G17" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="H15" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" s="19" t="n">
+      <c r="H17" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="L15" s="20" t="n">
+      <c r="L17" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="M15" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" s="19" t="n">
+      <c r="M17" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="Q15" s="20" t="n">
+      <c r="Q17" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="R15" s="21" t="n">
+      <c r="R17" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="U15" s="19" t="n">
+      <c r="U17" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="V15" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" s="21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="B16" s="14"/>
-      <c r="C16" s="23" t="n">
+      <c r="V17" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="B18" s="14"/>
+      <c r="C18" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="D16" s="24"/>
-      <c r="F16" s="22" t="n">
+      <c r="D18" s="24"/>
+      <c r="F18" s="22" t="n">
         <v>10</v>
       </c>
-      <c r="G16" s="14"/>
-      <c r="H16" s="23" t="n">
+      <c r="G18" s="14"/>
+      <c r="H18" s="23" t="n">
         <v>17</v>
       </c>
-      <c r="K16" s="22" t="n">
+      <c r="K18" s="22" t="n">
         <v>17</v>
       </c>
-      <c r="L16" s="14"/>
-      <c r="M16" s="23" t="n">
+      <c r="L18" s="14"/>
+      <c r="M18" s="23" t="n">
         <v>21</v>
       </c>
-      <c r="P16" s="22" t="n">
+      <c r="P18" s="22" t="n">
         <v>21</v>
       </c>
-      <c r="Q16" s="14"/>
-      <c r="R16" s="23" t="n">
+      <c r="Q18" s="14"/>
+      <c r="R18" s="23" t="n">
         <v>24</v>
       </c>
-      <c r="S16" s="25"/>
-      <c r="T16" s="26"/>
-      <c r="U16" s="22" t="n">
+      <c r="S18" s="25"/>
+      <c r="T18" s="26"/>
+      <c r="U18" s="22" t="n">
         <v>24</v>
       </c>
-      <c r="V16" s="14"/>
-      <c r="W16" s="23" t="n">
+      <c r="V18" s="14"/>
+      <c r="W18" s="23" t="n">
         <v>26</v>
       </c>
-    </row>
-    <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D17" s="25"/>
-      <c r="S17" s="25"/>
-    </row>
-    <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D18" s="25"/>
-      <c r="S18" s="25"/>
     </row>
     <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D19" s="25"/>
-      <c r="F19" s="13" t="n">
-        <v>6</v>
-      </c>
-      <c r="G19" s="14"/>
-      <c r="H19" s="15" t="n">
-        <v>13</v>
-      </c>
-      <c r="K19" s="13" t="n">
-        <v>13</v>
-      </c>
-      <c r="L19" s="14"/>
-      <c r="M19" s="15" t="n">
-        <v>17</v>
-      </c>
-      <c r="P19" s="13" t="n">
-        <v>18</v>
-      </c>
-      <c r="Q19" s="14"/>
-      <c r="R19" s="15" t="n">
-        <v>24</v>
-      </c>
       <c r="S19" s="25"/>
     </row>
     <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D20" s="25"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="16" t="s">
+      <c r="S20" s="25"/>
+    </row>
+    <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D21" s="25"/>
+      <c r="F21" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="G21" s="14"/>
+      <c r="H21" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="K21" s="13" t="n">
+        <v>13</v>
+      </c>
+      <c r="L21" s="14"/>
+      <c r="M21" s="15" t="n">
+        <v>17</v>
+      </c>
+      <c r="P21" s="13" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q21" s="14"/>
+      <c r="R21" s="15" t="n">
+        <v>24</v>
+      </c>
+      <c r="S21" s="25"/>
+    </row>
+    <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D22" s="25"/>
+      <c r="E22" s="17"/>
+      <c r="F22" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="G20" s="16"/>
-      <c r="H20" s="16"/>
-      <c r="I20" s="17"/>
-      <c r="J20" s="17"/>
-      <c r="K20" s="16" t="s">
+      <c r="G22" s="16"/>
+      <c r="H22" s="16"/>
+      <c r="I22" s="17"/>
+      <c r="J22" s="17"/>
+      <c r="K22" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="17"/>
-      <c r="O20" s="17"/>
-      <c r="P20" s="16" t="s">
+      <c r="L22" s="16"/>
+      <c r="M22" s="16"/>
+      <c r="N22" s="17"/>
+      <c r="O22" s="17"/>
+      <c r="P22" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="Q20" s="16"/>
-      <c r="R20" s="16"/>
-      <c r="S20" s="27"/>
-    </row>
-    <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F21" s="19" t="n">
+      <c r="Q22" s="16"/>
+      <c r="R22" s="16"/>
+      <c r="S22" s="27"/>
+    </row>
+    <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F23" s="19" t="n">
         <v>7</v>
       </c>
-      <c r="G21" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" s="19" t="n">
+      <c r="G23" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="L21" s="20" t="n">
+      <c r="L23" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="M21" s="21" t="n">
+      <c r="M23" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="P21" s="19" t="n">
+      <c r="P23" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="Q21" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" s="21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F22" s="22" t="n">
+      <c r="Q23" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F24" s="22" t="n">
         <v>6</v>
       </c>
-      <c r="G22" s="14"/>
-      <c r="H22" s="23" t="n">
+      <c r="G24" s="14"/>
+      <c r="H24" s="23" t="n">
         <v>13</v>
       </c>
-      <c r="I22" s="24"/>
-      <c r="K22" s="22" t="n">
+      <c r="I24" s="24"/>
+      <c r="K24" s="22" t="n">
         <v>14</v>
       </c>
-      <c r="L22" s="14"/>
-      <c r="M22" s="23" t="n">
+      <c r="L24" s="14"/>
+      <c r="M24" s="23" t="n">
         <v>18</v>
       </c>
-      <c r="N22" s="25"/>
-      <c r="O22" s="26"/>
-      <c r="P22" s="22" t="n">
+      <c r="N24" s="25"/>
+      <c r="O24" s="26"/>
+      <c r="P24" s="22" t="n">
         <v>18</v>
       </c>
-      <c r="Q22" s="14"/>
-      <c r="R22" s="23" t="n">
+      <c r="Q24" s="14"/>
+      <c r="R24" s="23" t="n">
         <v>24</v>
       </c>
-    </row>
-    <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I23" s="25"/>
-      <c r="N23" s="25"/>
-    </row>
-    <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I24" s="25"/>
-      <c r="N24" s="25"/>
     </row>
     <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I25" s="25"/>
-      <c r="K25" s="13" t="n">
-        <v>13</v>
-      </c>
-      <c r="L25" s="14"/>
-      <c r="M25" s="15" t="n">
-        <v>18</v>
-      </c>
       <c r="N25" s="25"/>
     </row>
     <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I26" s="25"/>
-      <c r="J26" s="17"/>
-      <c r="K26" s="16" t="s">
+      <c r="N26" s="25"/>
+    </row>
+    <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I27" s="25"/>
+      <c r="K27" s="13" t="n">
+        <v>13</v>
+      </c>
+      <c r="L27" s="14"/>
+      <c r="M27" s="15" t="n">
+        <v>18</v>
+      </c>
+      <c r="N27" s="25"/>
+    </row>
+    <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I28" s="25"/>
+      <c r="J28" s="17"/>
+      <c r="K28" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
-      <c r="N26" s="27"/>
-    </row>
-    <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K27" s="19" t="n">
+      <c r="L28" s="16"/>
+      <c r="M28" s="16"/>
+      <c r="N28" s="27"/>
+    </row>
+    <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K29" s="19" t="n">
         <v>5</v>
       </c>
-      <c r="L27" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" s="21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K28" s="22" t="n">
+      <c r="L29" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K30" s="22" t="n">
         <v>13</v>
       </c>
-      <c r="L28" s="14"/>
-      <c r="M28" s="23" t="n">
+      <c r="L30" s="14"/>
+      <c r="M30" s="23" t="n">
         <v>18</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="31" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="B1:D1"/>
-    <mergeCell ref="A9:E9"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="K14:M14"/>
-    <mergeCell ref="P14:R14"/>
-    <mergeCell ref="U14:W14"/>
-    <mergeCell ref="F20:H20"/>
-    <mergeCell ref="K20:M20"/>
-    <mergeCell ref="P20:R20"/>
-    <mergeCell ref="K26:M26"/>
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="F16:H16"/>
+    <mergeCell ref="K16:M16"/>
+    <mergeCell ref="P16:R16"/>
+    <mergeCell ref="U16:W16"/>
+    <mergeCell ref="F22:H22"/>
+    <mergeCell ref="K22:M22"/>
+    <mergeCell ref="P22:R22"/>
+    <mergeCell ref="K28:M28"/>
   </mergeCells>
-  <conditionalFormatting sqref="B15 G15 G21 L15 L21 L27 Q15 Q21 V15">
+  <conditionalFormatting sqref="B17 G17 G23 L17 L23 L29 Q17 Q23 V17">
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E8:E9">
+  <conditionalFormatting sqref="E10:E11">
     <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
       <formula>0</formula>
     </cfRule>
@@ -5066,7 +5316,9 @@
   <dimension ref="A1:DI1048576"/>
   <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="57" min="1" style="3" width="3.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="1" style="3" width="3.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="3" width="4.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="57" min="8" style="3" width="3.86"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="96" min="58" style="3" width="3.83"/>
   </cols>
   <sheetData>
@@ -5079,9 +5331,15 @@
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
+      <c r="E1" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>45</v>
+      </c>
       <c r="H1" s="2" t="s">
         <v>2</v>
       </c>
@@ -5519,11 +5777,18 @@
       <c r="D2" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
+      <c r="E2" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="F2" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2" s="48" t="n">
+        <v>1</v>
+      </c>
       <c r="H2" s="7" t="n">
-        <v>15</v>
+        <f aca="false">ROUNDUP(E2/(F2*G2),0)</f>
+        <v>5</v>
       </c>
       <c r="J2" s="42"/>
       <c r="K2" s="42"/>
@@ -5581,11 +5846,18 @@
       </c>
       <c r="C3" s="8"/>
       <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
+      <c r="E3" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="F3" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" s="48" t="n">
+        <v>0.5</v>
+      </c>
       <c r="H3" s="7" t="n">
-        <v>6</v>
+        <f aca="false">ROUNDUP(E3/(F3*G3),0)</f>
+        <v>12</v>
       </c>
       <c r="L3" s="10"/>
       <c r="O3" s="10"/>
@@ -5629,11 +5901,18 @@
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
+      <c r="E4" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="F4" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="48" t="n">
+        <v>1.5</v>
+      </c>
       <c r="H4" s="7" t="n">
-        <v>14</v>
+        <f aca="false">ROUNDUP(E4/(F4*G4),0)</f>
+        <v>10</v>
       </c>
       <c r="L4" s="10"/>
       <c r="O4" s="10"/>
@@ -5683,10 +5962,17 @@
       </c>
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
+      <c r="E5" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="F5" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="48" t="n">
+        <v>1</v>
+      </c>
       <c r="H5" s="7" t="n">
+        <f aca="false">ROUNDUP(E5/(F5*G5),0)</f>
         <v>6</v>
       </c>
       <c r="L5" s="10"/>
@@ -5731,11 +6017,18 @@
       </c>
       <c r="C6" s="8"/>
       <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
+      <c r="E6" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="F6" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="48" t="n">
+        <v>1.75</v>
+      </c>
       <c r="H6" s="7" t="n">
-        <v>15</v>
+        <f aca="false">ROUNDUP(E6/(F6*G6),0)</f>
+        <v>9</v>
       </c>
       <c r="L6" s="10"/>
       <c r="O6" s="10"/>
@@ -5773,11 +6066,18 @@
       </c>
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
+      <c r="E7" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="F7" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="48" t="n">
+        <v>0.75</v>
+      </c>
       <c r="H7" s="7" t="n">
-        <v>14</v>
+        <f aca="false">ROUNDUP(E7/(F7*G7),0)</f>
+        <v>19</v>
       </c>
       <c r="L7" s="10"/>
       <c r="O7" s="10"/>
@@ -5817,11 +6117,18 @@
         <v>12</v>
       </c>
       <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
+      <c r="E8" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="F8" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="48" t="n">
+        <v>0.5</v>
+      </c>
       <c r="H8" s="7" t="n">
-        <v>7</v>
+        <f aca="false">ROUNDUP(E8/(F8*G8),0)</f>
+        <v>14</v>
       </c>
       <c r="L8" s="10"/>
       <c r="O8" s="10"/>
@@ -5859,11 +6166,18 @@
       </c>
       <c r="C9" s="8"/>
       <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
+      <c r="E9" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="F9" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="48" t="n">
+        <v>1.5</v>
+      </c>
       <c r="H9" s="7" t="n">
-        <v>15</v>
+        <f aca="false">ROUNDUP(E9/(F9*G9),0)</f>
+        <v>10</v>
       </c>
       <c r="L9" s="10"/>
       <c r="O9" s="10"/>
@@ -5899,11 +6213,18 @@
       <c r="B10" s="8"/>
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
+      <c r="E10" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F10" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G10" s="48" t="n">
+        <v>1</v>
+      </c>
       <c r="H10" s="7" t="n">
-        <v>4</v>
+        <f aca="false">ROUNDUP(E10/(F10*G10),0)</f>
+        <v>2</v>
       </c>
       <c r="L10" s="10"/>
       <c r="O10" s="10"/>
@@ -5940,34 +6261,34 @@
       <c r="B12" s="14"/>
       <c r="C12" s="15" t="n">
         <f aca="false">A12+A14</f>
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F12" s="13" t="n">
         <f aca="false">$C$12</f>
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="G12" s="14"/>
       <c r="H12" s="15" t="n">
         <f aca="false">F12+F14</f>
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="K12" s="13" t="n">
         <f aca="false">H12</f>
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="L12" s="14"/>
       <c r="M12" s="15" t="n">
         <f aca="false">K12+K14</f>
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="U12" s="13" t="n">
         <f aca="false">MAX(M12,R18)</f>
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="V12" s="14"/>
       <c r="W12" s="15" t="n">
         <f aca="false">U12+U14</f>
-        <v>63</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6006,7 +6327,7 @@
     <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="19" t="n">
         <f aca="false">VLOOKUP(A13,$A$2:$H$10,8)</f>
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="B14" s="20" t="n">
         <f aca="false">C15-C12</f>
@@ -6018,11 +6339,11 @@
       </c>
       <c r="F14" s="19" t="n">
         <f aca="false">VLOOKUP(F13,$A$2:$H$10,8)</f>
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G14" s="20" t="n">
         <f aca="false">H15-H12</f>
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="H14" s="21" t="n">
         <f aca="false">K12-H12</f>
@@ -6030,19 +6351,19 @@
       </c>
       <c r="K14" s="19" t="n">
         <f aca="false">VLOOKUP(K13,$A$2:$H$10,8)</f>
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="L14" s="20" t="n">
         <f aca="false">M15-M12</f>
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="M14" s="21" t="n">
         <f aca="false">U12-M12</f>
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="U14" s="19" t="n">
         <f aca="false">VLOOKUP(U13,$A$2:$H$10,8)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="V14" s="20" t="n">
         <f aca="false">W15-W12</f>
@@ -6060,37 +6381,37 @@
       <c r="B15" s="14"/>
       <c r="C15" s="23" t="n">
         <f aca="false">MIN(F15,F21,F27)</f>
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="D15" s="24"/>
       <c r="F15" s="22" t="n">
         <f aca="false">H15-F14</f>
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="G15" s="14"/>
       <c r="H15" s="23" t="n">
         <f aca="false">K15</f>
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="K15" s="22" t="n">
         <f aca="false">M15-K14</f>
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="L15" s="14"/>
       <c r="M15" s="23" t="n">
         <f aca="false">U12</f>
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="S15" s="25"/>
       <c r="T15" s="26"/>
       <c r="U15" s="22" t="n">
         <f aca="false">W15-U14</f>
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="V15" s="14"/>
       <c r="W15" s="23" t="n">
         <f aca="false">W12</f>
-        <v>63</v>
+        <v>42</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6108,30 +6429,30 @@
       <c r="D18" s="25"/>
       <c r="F18" s="13" t="n">
         <f aca="false">$C$12</f>
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="G18" s="14"/>
       <c r="H18" s="15" t="n">
         <f aca="false">F18+F20</f>
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="K18" s="13" t="n">
         <f aca="false">H18</f>
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="L18" s="14"/>
       <c r="M18" s="15" t="n">
         <f aca="false">K18+K20</f>
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="P18" s="13" t="n">
         <f aca="false">MAX(M18,M24)</f>
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="Q18" s="14"/>
       <c r="R18" s="15" t="n">
         <f aca="false">P18+P20</f>
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="S18" s="25"/>
     </row>
@@ -6164,11 +6485,11 @@
       <c r="C20" s="25"/>
       <c r="F20" s="19" t="n">
         <f aca="false">VLOOKUP(F19,$A$2:$H$10,8)</f>
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G20" s="20" t="n">
         <f aca="false">H21-H18</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H20" s="21" t="n">
         <f aca="false">K18-H18</f>
@@ -6176,19 +6497,19 @@
       </c>
       <c r="K20" s="19" t="n">
         <f aca="false">VLOOKUP(K19,$A$2:$H$10,8)</f>
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="L20" s="20" t="n">
         <f aca="false">M21-M18</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M20" s="21" t="n">
         <f aca="false">P18-M18</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P20" s="19" t="n">
         <f aca="false">VLOOKUP(P19,$A$2:$H$10,8)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Q20" s="20" t="n">
         <f aca="false">R21-R18</f>
@@ -6203,62 +6524,62 @@
       <c r="C21" s="25"/>
       <c r="F21" s="22" t="n">
         <f aca="false">H21-F20</f>
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G21" s="14"/>
       <c r="H21" s="23" t="n">
         <f aca="false">K21</f>
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="K21" s="22" t="n">
         <f aca="false">M21-K20</f>
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="L21" s="14"/>
       <c r="M21" s="23" t="n">
         <f aca="false">P21</f>
-        <v>44</v>
-      </c>
-      <c r="O21" s="48"/>
+        <v>30</v>
+      </c>
+      <c r="O21" s="49"/>
       <c r="P21" s="22" t="n">
         <f aca="false">R21-P20</f>
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="Q21" s="14"/>
       <c r="R21" s="23" t="n">
         <f aca="false">U15</f>
-        <v>59</v>
+        <v>40</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C22" s="25"/>
-      <c r="O22" s="49"/>
+      <c r="O22" s="50"/>
     </row>
     <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C23" s="25"/>
-      <c r="O23" s="49"/>
+      <c r="O23" s="50"/>
     </row>
     <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C24" s="25"/>
       <c r="F24" s="13" t="n">
         <f aca="false">$C$12</f>
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="G24" s="14"/>
       <c r="H24" s="15" t="n">
         <f aca="false">F24+F26</f>
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="K24" s="13" t="n">
         <f aca="false">H24</f>
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="L24" s="14"/>
       <c r="M24" s="15" t="n">
         <f aca="false">K24+K26</f>
-        <v>35</v>
-      </c>
-      <c r="O24" s="49"/>
+        <v>30</v>
+      </c>
+      <c r="O24" s="50"/>
     </row>
     <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C25" s="25"/>
@@ -6277,7 +6598,7 @@
       <c r="L25" s="16"/>
       <c r="M25" s="16"/>
       <c r="N25" s="17"/>
-      <c r="O25" s="49"/>
+      <c r="O25" s="50"/>
     </row>
     <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F26" s="19" t="n">
@@ -6286,7 +6607,7 @@
       </c>
       <c r="G26" s="20" t="n">
         <f aca="false">H27-H24</f>
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H26" s="21" t="n">
         <f aca="false">K24-H24</f>
@@ -6294,35 +6615,35 @@
       </c>
       <c r="K26" s="19" t="n">
         <f aca="false">VLOOKUP(K25,$A$2:$H$10,8)</f>
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="L26" s="20" t="n">
         <f aca="false">M27-M24</f>
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M26" s="21" t="n">
         <f aca="false">P18-M24</f>
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F27" s="22" t="n">
         <f aca="false">H27-F26</f>
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="G27" s="14"/>
       <c r="H27" s="23" t="n">
         <f aca="false">K27</f>
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="K27" s="22" t="n">
         <f aca="false">M27-K26</f>
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="L27" s="14"/>
       <c r="M27" s="23" t="n">
         <f aca="false">P21</f>
-        <v>44</v>
+        <v>30</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -6355,6 +6676,7 @@
     <oddHeader>&amp;C&amp;A</oddHeader>
     <oddFooter>&amp;CSeite &amp;P</oddFooter>
   </headerFooter>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -6385,67 +6707,67 @@
       <c r="E1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="50" t="n">
+      <c r="G1" s="51" t="n">
         <v>45775</v>
       </c>
-      <c r="H1" s="50" t="n">
+      <c r="H1" s="51" t="n">
         <v>45776</v>
       </c>
-      <c r="I1" s="50" t="n">
+      <c r="I1" s="51" t="n">
         <v>45777</v>
       </c>
-      <c r="J1" s="51" t="n">
+      <c r="J1" s="52" t="n">
         <v>45778</v>
       </c>
-      <c r="K1" s="50" t="n">
+      <c r="K1" s="51" t="n">
         <v>45779</v>
       </c>
-      <c r="L1" s="52" t="n">
+      <c r="L1" s="53" t="n">
         <v>45780</v>
       </c>
-      <c r="M1" s="52" t="n">
+      <c r="M1" s="53" t="n">
         <v>45781</v>
       </c>
-      <c r="N1" s="50" t="n">
+      <c r="N1" s="51" t="n">
         <v>45782</v>
       </c>
-      <c r="O1" s="50" t="n">
+      <c r="O1" s="51" t="n">
         <v>45783</v>
       </c>
-      <c r="P1" s="50" t="n">
+      <c r="P1" s="51" t="n">
         <v>45784</v>
       </c>
-      <c r="Q1" s="50" t="n">
+      <c r="Q1" s="51" t="n">
         <v>45785</v>
       </c>
-      <c r="R1" s="50" t="n">
+      <c r="R1" s="51" t="n">
         <v>45786</v>
       </c>
-      <c r="S1" s="52" t="n">
+      <c r="S1" s="53" t="n">
         <v>45787</v>
       </c>
-      <c r="T1" s="52" t="n">
+      <c r="T1" s="53" t="n">
         <v>45788</v>
       </c>
-      <c r="U1" s="50" t="n">
+      <c r="U1" s="51" t="n">
         <v>45789</v>
       </c>
-      <c r="V1" s="50" t="n">
+      <c r="V1" s="51" t="n">
         <v>45790</v>
       </c>
-      <c r="W1" s="50" t="n">
+      <c r="W1" s="51" t="n">
         <v>45791</v>
       </c>
-      <c r="X1" s="50" t="n">
+      <c r="X1" s="51" t="n">
         <v>45792</v>
       </c>
-      <c r="Y1" s="50" t="n">
+      <c r="Y1" s="51" t="n">
         <v>45793</v>
       </c>
-      <c r="Z1" s="52" t="n">
+      <c r="Z1" s="53" t="n">
         <v>45794</v>
       </c>
-      <c r="AA1" s="52" t="n">
+      <c r="AA1" s="53" t="n">
         <v>45795</v>
       </c>
     </row>
@@ -6459,16 +6781,16 @@
       <c r="E2" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="51"/>
-      <c r="L2" s="52"/>
-      <c r="M2" s="52"/>
-      <c r="S2" s="52"/>
-      <c r="T2" s="52"/>
-      <c r="Z2" s="52"/>
-      <c r="AA2" s="52"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="54"/>
+      <c r="I2" s="54"/>
+      <c r="J2" s="52"/>
+      <c r="L2" s="53"/>
+      <c r="M2" s="53"/>
+      <c r="S2" s="53"/>
+      <c r="T2" s="53"/>
+      <c r="Z2" s="53"/>
+      <c r="AA2" s="53"/>
     </row>
     <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
@@ -6482,14 +6804,14 @@
       <c r="E3" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="J3" s="51"/>
-      <c r="K3" s="54"/>
-      <c r="L3" s="52"/>
-      <c r="M3" s="52"/>
-      <c r="S3" s="52"/>
-      <c r="T3" s="52"/>
-      <c r="Z3" s="52"/>
-      <c r="AA3" s="52"/>
+      <c r="J3" s="52"/>
+      <c r="K3" s="55"/>
+      <c r="L3" s="53"/>
+      <c r="M3" s="53"/>
+      <c r="S3" s="53"/>
+      <c r="T3" s="53"/>
+      <c r="Z3" s="53"/>
+      <c r="AA3" s="53"/>
     </row>
     <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
@@ -6503,14 +6825,14 @@
       <c r="E4" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="J4" s="51"/>
-      <c r="K4" s="54"/>
-      <c r="L4" s="52"/>
-      <c r="M4" s="52"/>
-      <c r="S4" s="52"/>
-      <c r="T4" s="52"/>
-      <c r="Z4" s="52"/>
-      <c r="AA4" s="52"/>
+      <c r="J4" s="52"/>
+      <c r="K4" s="55"/>
+      <c r="L4" s="53"/>
+      <c r="M4" s="53"/>
+      <c r="S4" s="53"/>
+      <c r="T4" s="53"/>
+      <c r="Z4" s="53"/>
+      <c r="AA4" s="53"/>
     </row>
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
@@ -6524,15 +6846,15 @@
       <c r="E5" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="J5" s="51"/>
-      <c r="K5" s="53"/>
-      <c r="L5" s="52"/>
-      <c r="M5" s="52"/>
-      <c r="N5" s="53"/>
-      <c r="S5" s="52"/>
-      <c r="T5" s="52"/>
-      <c r="Z5" s="52"/>
-      <c r="AA5" s="52"/>
+      <c r="J5" s="52"/>
+      <c r="K5" s="54"/>
+      <c r="L5" s="53"/>
+      <c r="M5" s="53"/>
+      <c r="N5" s="54"/>
+      <c r="S5" s="53"/>
+      <c r="T5" s="53"/>
+      <c r="Z5" s="53"/>
+      <c r="AA5" s="53"/>
     </row>
     <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
@@ -6546,14 +6868,14 @@
       <c r="E6" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="J6" s="51"/>
-      <c r="L6" s="52"/>
-      <c r="M6" s="52"/>
-      <c r="N6" s="54"/>
-      <c r="S6" s="52"/>
-      <c r="T6" s="52"/>
-      <c r="Z6" s="52"/>
-      <c r="AA6" s="52"/>
+      <c r="J6" s="52"/>
+      <c r="L6" s="53"/>
+      <c r="M6" s="53"/>
+      <c r="N6" s="55"/>
+      <c r="S6" s="53"/>
+      <c r="T6" s="53"/>
+      <c r="Z6" s="53"/>
+      <c r="AA6" s="53"/>
     </row>
     <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
@@ -6567,15 +6889,15 @@
       <c r="E7" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="J7" s="51"/>
-      <c r="L7" s="52"/>
-      <c r="M7" s="52"/>
-      <c r="O7" s="53"/>
-      <c r="P7" s="53"/>
-      <c r="S7" s="52"/>
-      <c r="T7" s="52"/>
-      <c r="Z7" s="52"/>
-      <c r="AA7" s="52"/>
+      <c r="J7" s="52"/>
+      <c r="L7" s="53"/>
+      <c r="M7" s="53"/>
+      <c r="O7" s="54"/>
+      <c r="P7" s="54"/>
+      <c r="S7" s="53"/>
+      <c r="T7" s="53"/>
+      <c r="Z7" s="53"/>
+      <c r="AA7" s="53"/>
     </row>
     <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
@@ -6591,14 +6913,14 @@
       <c r="E8" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="J8" s="51"/>
-      <c r="L8" s="52"/>
-      <c r="M8" s="52"/>
-      <c r="N8" s="54"/>
-      <c r="S8" s="52"/>
-      <c r="T8" s="52"/>
-      <c r="Z8" s="52"/>
-      <c r="AA8" s="52"/>
+      <c r="J8" s="52"/>
+      <c r="L8" s="53"/>
+      <c r="M8" s="53"/>
+      <c r="N8" s="55"/>
+      <c r="S8" s="53"/>
+      <c r="T8" s="53"/>
+      <c r="Z8" s="53"/>
+      <c r="AA8" s="53"/>
     </row>
     <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
@@ -6614,14 +6936,14 @@
       <c r="E9" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="J9" s="51"/>
-      <c r="L9" s="52"/>
-      <c r="M9" s="52"/>
-      <c r="Q9" s="53"/>
-      <c r="S9" s="52"/>
-      <c r="T9" s="52"/>
-      <c r="Z9" s="52"/>
-      <c r="AA9" s="52"/>
+      <c r="J9" s="52"/>
+      <c r="L9" s="53"/>
+      <c r="M9" s="53"/>
+      <c r="Q9" s="54"/>
+      <c r="S9" s="53"/>
+      <c r="T9" s="53"/>
+      <c r="Z9" s="53"/>
+      <c r="AA9" s="53"/>
     </row>
     <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
@@ -6635,14 +6957,14 @@
       <c r="E10" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="J10" s="51"/>
-      <c r="L10" s="52"/>
-      <c r="M10" s="52"/>
-      <c r="O10" s="54"/>
-      <c r="S10" s="52"/>
-      <c r="T10" s="52"/>
-      <c r="Z10" s="52"/>
-      <c r="AA10" s="52"/>
+      <c r="J10" s="52"/>
+      <c r="L10" s="53"/>
+      <c r="M10" s="53"/>
+      <c r="O10" s="55"/>
+      <c r="S10" s="53"/>
+      <c r="T10" s="53"/>
+      <c r="Z10" s="53"/>
+      <c r="AA10" s="53"/>
     </row>
     <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="s">
@@ -6656,14 +6978,14 @@
       <c r="E11" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="J11" s="51"/>
-      <c r="L11" s="52"/>
-      <c r="M11" s="52"/>
-      <c r="R11" s="53"/>
-      <c r="S11" s="52"/>
-      <c r="T11" s="52"/>
-      <c r="Z11" s="52"/>
-      <c r="AA11" s="52"/>
+      <c r="J11" s="52"/>
+      <c r="L11" s="53"/>
+      <c r="M11" s="53"/>
+      <c r="R11" s="54"/>
+      <c r="S11" s="53"/>
+      <c r="T11" s="53"/>
+      <c r="Z11" s="53"/>
+      <c r="AA11" s="53"/>
     </row>
     <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
@@ -6679,16 +7001,16 @@
       <c r="E12" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="J12" s="51"/>
-      <c r="L12" s="52"/>
-      <c r="M12" s="52"/>
-      <c r="S12" s="52"/>
-      <c r="T12" s="52"/>
-      <c r="U12" s="53"/>
-      <c r="V12" s="53"/>
-      <c r="W12" s="53"/>
-      <c r="Z12" s="52"/>
-      <c r="AA12" s="52"/>
+      <c r="J12" s="52"/>
+      <c r="L12" s="53"/>
+      <c r="M12" s="53"/>
+      <c r="S12" s="53"/>
+      <c r="T12" s="53"/>
+      <c r="U12" s="54"/>
+      <c r="V12" s="54"/>
+      <c r="W12" s="54"/>
+      <c r="Z12" s="53"/>
+      <c r="AA12" s="53"/>
     </row>
     <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7117,7 +7439,7 @@
   <dimension ref="A1:G1048576"/>
   <sheetFormatPr defaultColWidth="10.6796875" defaultRowHeight="12.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="55" width="8.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="56" width="8.84"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="3" width="23.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="3" width="23.96"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="3" width="11.53"/>
@@ -7125,279 +7447,279 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="55" t="s">
-        <v>43</v>
-      </c>
-      <c r="B1" s="56" t="s">
-        <v>44</v>
+      <c r="A1" s="56" t="s">
+        <v>46</v>
+      </c>
+      <c r="B1" s="57" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="57" t="n">
+      <c r="A2" s="58" t="n">
         <v>45297</v>
       </c>
-      <c r="B2" s="55" t="s">
-        <v>45</v>
-      </c>
-      <c r="C2" s="56" t="s">
-        <v>46</v>
-      </c>
-      <c r="E2" s="56" t="s">
-        <v>47</v>
-      </c>
-      <c r="F2" s="58" t="n">
+      <c r="B2" s="56" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2" s="57" t="s">
+        <v>49</v>
+      </c>
+      <c r="E2" s="57" t="s">
+        <v>50</v>
+      </c>
+      <c r="F2" s="59" t="n">
         <v>45413</v>
       </c>
-      <c r="G2" s="58" t="n">
+      <c r="G2" s="59" t="n">
         <v>45414</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="57" t="n">
+      <c r="A3" s="58" t="n">
         <v>45359</v>
       </c>
-      <c r="B3" s="55" t="s">
-        <v>48</v>
-      </c>
-      <c r="C3" s="56" t="s">
-        <v>49</v>
-      </c>
-      <c r="D3" s="56" t="s">
-        <v>50</v>
-      </c>
-      <c r="E3" s="56" t="s">
+      <c r="B3" s="56" t="s">
         <v>51</v>
       </c>
+      <c r="C3" s="57" t="s">
+        <v>52</v>
+      </c>
+      <c r="D3" s="57" t="s">
+        <v>53</v>
+      </c>
+      <c r="E3" s="57" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="57" t="n">
+      <c r="A4" s="58" t="n">
         <v>45380</v>
       </c>
-      <c r="B4" s="55" t="s">
-        <v>52</v>
-      </c>
-      <c r="C4" s="56" t="s">
+      <c r="B4" s="56" t="s">
+        <v>55</v>
+      </c>
+      <c r="C4" s="57" t="s">
+        <v>56</v>
+      </c>
+      <c r="D4" s="57" t="s">
         <v>53</v>
       </c>
-      <c r="D4" s="56" t="s">
-        <v>50</v>
-      </c>
-      <c r="E4" s="56" t="s">
-        <v>54</v>
+      <c r="E4" s="57" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="57" t="n">
+      <c r="A5" s="58" t="n">
         <v>45383</v>
       </c>
-      <c r="B5" s="55" t="s">
-        <v>55</v>
-      </c>
-      <c r="C5" s="56" t="s">
-        <v>56</v>
-      </c>
-      <c r="D5" s="56" t="s">
-        <v>50</v>
-      </c>
-      <c r="E5" s="56" t="s">
-        <v>54</v>
+      <c r="B5" s="56" t="s">
+        <v>58</v>
+      </c>
+      <c r="C5" s="57" t="s">
+        <v>59</v>
+      </c>
+      <c r="D5" s="57" t="s">
+        <v>53</v>
+      </c>
+      <c r="E5" s="57" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="57" t="n">
+      <c r="A6" s="58" t="n">
         <v>45413</v>
       </c>
-      <c r="B6" s="55" t="s">
+      <c r="B6" s="56" t="s">
+        <v>60</v>
+      </c>
+      <c r="C6" s="57" t="s">
+        <v>61</v>
+      </c>
+      <c r="E6" s="57" t="s">
         <v>57</v>
       </c>
-      <c r="C6" s="56" t="s">
-        <v>58</v>
-      </c>
-      <c r="E6" s="56" t="s">
-        <v>54</v>
-      </c>
     </row>
     <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="57" t="n">
+      <c r="A7" s="58" t="n">
         <v>45421</v>
       </c>
-      <c r="B7" s="55" t="s">
-        <v>59</v>
-      </c>
-      <c r="C7" s="56" t="s">
-        <v>60</v>
-      </c>
-      <c r="D7" s="56" t="s">
-        <v>61</v>
-      </c>
-      <c r="E7" s="56" t="s">
-        <v>54</v>
+      <c r="B7" s="56" t="s">
+        <v>62</v>
+      </c>
+      <c r="C7" s="57" t="s">
+        <v>63</v>
+      </c>
+      <c r="D7" s="57" t="s">
+        <v>64</v>
+      </c>
+      <c r="E7" s="57" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="57" t="n">
+      <c r="A8" s="58" t="n">
         <v>45432</v>
       </c>
-      <c r="B8" s="55" t="s">
-        <v>62</v>
-      </c>
-      <c r="C8" s="56" t="s">
-        <v>63</v>
-      </c>
-      <c r="D8" s="56" t="s">
-        <v>50</v>
-      </c>
-      <c r="E8" s="56" t="s">
-        <v>54</v>
+      <c r="B8" s="56" t="s">
+        <v>65</v>
+      </c>
+      <c r="C8" s="57" t="s">
+        <v>66</v>
+      </c>
+      <c r="D8" s="57" t="s">
+        <v>53</v>
+      </c>
+      <c r="E8" s="57" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="57" t="n">
+      <c r="A9" s="58" t="n">
         <v>45442</v>
       </c>
-      <c r="B9" s="55" t="s">
+      <c r="B9" s="56" t="s">
+        <v>67</v>
+      </c>
+      <c r="C9" s="57" t="s">
+        <v>68</v>
+      </c>
+      <c r="D9" s="57" t="s">
         <v>64</v>
       </c>
-      <c r="C9" s="56" t="s">
-        <v>65</v>
-      </c>
-      <c r="D9" s="56" t="s">
-        <v>61</v>
-      </c>
-      <c r="E9" s="56" t="s">
-        <v>66</v>
+      <c r="E9" s="57" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="57" t="n">
+      <c r="A10" s="58" t="n">
         <v>45519</v>
       </c>
-      <c r="B10" s="55" t="s">
-        <v>67</v>
-      </c>
-      <c r="C10" s="56" t="s">
-        <v>68</v>
-      </c>
-      <c r="D10" s="56" t="s">
-        <v>61</v>
-      </c>
-      <c r="E10" s="56" t="s">
-        <v>69</v>
+      <c r="B10" s="56" t="s">
+        <v>70</v>
+      </c>
+      <c r="C10" s="57" t="s">
+        <v>71</v>
+      </c>
+      <c r="D10" s="57" t="s">
+        <v>64</v>
+      </c>
+      <c r="E10" s="57" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="57" t="n">
+      <c r="A11" s="58" t="n">
         <v>45555</v>
       </c>
-      <c r="B11" s="55" t="s">
-        <v>70</v>
-      </c>
-      <c r="C11" s="56" t="s">
-        <v>71</v>
-      </c>
-      <c r="D11" s="56" t="s">
-        <v>50</v>
-      </c>
-      <c r="E11" s="56" t="s">
-        <v>72</v>
+      <c r="B11" s="56" t="s">
+        <v>73</v>
+      </c>
+      <c r="C11" s="57" t="s">
+        <v>74</v>
+      </c>
+      <c r="D11" s="57" t="s">
+        <v>53</v>
+      </c>
+      <c r="E11" s="57" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="57" t="n">
+      <c r="A12" s="58" t="n">
         <v>45568</v>
       </c>
-      <c r="B12" s="55" t="s">
-        <v>73</v>
-      </c>
-      <c r="C12" s="56" t="s">
-        <v>74</v>
-      </c>
-      <c r="D12" s="56" t="s">
-        <v>61</v>
-      </c>
-      <c r="E12" s="56" t="s">
-        <v>54</v>
+      <c r="B12" s="56" t="s">
+        <v>76</v>
+      </c>
+      <c r="C12" s="57" t="s">
+        <v>77</v>
+      </c>
+      <c r="D12" s="57" t="s">
+        <v>64</v>
+      </c>
+      <c r="E12" s="57" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="57" t="n">
+      <c r="A13" s="58" t="n">
         <v>45596</v>
       </c>
-      <c r="B13" s="55" t="s">
-        <v>75</v>
-      </c>
-      <c r="C13" s="56" t="s">
-        <v>76</v>
-      </c>
-      <c r="D13" s="56" t="s">
-        <v>61</v>
-      </c>
-      <c r="E13" s="55" t="s">
-        <v>77</v>
+      <c r="B13" s="56" t="s">
+        <v>78</v>
+      </c>
+      <c r="C13" s="57" t="s">
+        <v>79</v>
+      </c>
+      <c r="D13" s="57" t="s">
+        <v>64</v>
+      </c>
+      <c r="E13" s="56" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="58" t="n">
+      <c r="A14" s="59" t="n">
         <v>45597</v>
       </c>
-      <c r="B14" s="55" t="s">
-        <v>78</v>
-      </c>
-      <c r="C14" s="56" t="s">
-        <v>76</v>
-      </c>
-      <c r="D14" s="56" t="s">
-        <v>50</v>
-      </c>
-      <c r="E14" s="56" t="s">
+      <c r="B14" s="56" t="s">
+        <v>81</v>
+      </c>
+      <c r="C14" s="57" t="s">
         <v>79</v>
       </c>
+      <c r="D14" s="57" t="s">
+        <v>53</v>
+      </c>
+      <c r="E14" s="57" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="58" t="n">
+      <c r="A15" s="59" t="n">
         <v>45616</v>
       </c>
-      <c r="B15" s="55" t="s">
-        <v>80</v>
-      </c>
-      <c r="C15" s="56" t="s">
-        <v>81</v>
-      </c>
-      <c r="E15" s="56" t="s">
-        <v>82</v>
+      <c r="B15" s="56" t="s">
+        <v>83</v>
+      </c>
+      <c r="C15" s="57" t="s">
+        <v>84</v>
+      </c>
+      <c r="E15" s="57" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="58" t="n">
+      <c r="A16" s="59" t="n">
         <v>45651</v>
       </c>
-      <c r="B16" s="55" t="s">
-        <v>83</v>
-      </c>
-      <c r="C16" s="56" t="s">
-        <v>84</v>
-      </c>
-      <c r="D16" s="56" t="s">
-        <v>54</v>
+      <c r="B16" s="56" t="s">
+        <v>86</v>
+      </c>
+      <c r="C16" s="57" t="s">
+        <v>87</v>
+      </c>
+      <c r="D16" s="57" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="58" t="n">
+      <c r="A17" s="59" t="n">
         <v>45652</v>
       </c>
-      <c r="B17" s="55" t="s">
-        <v>85</v>
-      </c>
-      <c r="C17" s="56" t="s">
-        <v>84</v>
-      </c>
-      <c r="D17" s="56" t="s">
-        <v>61</v>
-      </c>
-      <c r="E17" s="56" t="s">
-        <v>54</v>
-      </c>
-      <c r="F17" s="56" t="s">
+      <c r="B17" s="56" t="s">
+        <v>88</v>
+      </c>
+      <c r="C17" s="57" t="s">
+        <v>87</v>
+      </c>
+      <c r="D17" s="57" t="s">
+        <v>64</v>
+      </c>
+      <c r="E17" s="57" t="s">
+        <v>57</v>
+      </c>
+      <c r="F17" s="57" t="s">
         <v>12</v>
       </c>
     </row>
